--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="15"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="31"/>
   </bookViews>
   <sheets>
     <sheet name="Neue Daten Ep3" sheetId="1" state="visible" r:id="rId3"/>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Neue Daten Ep3" sheetId="1" state="visible" r:id="rId3"/>
@@ -1111,7 +1111,7 @@
     <t xml:space="preserve">408: Talked to S’Ebi once</t>
   </si>
   <si>
-    <t xml:space="preserve">409: Returned equip to S’Ebi</t>
+    <t xml:space="preserve">409: Talked to S’Ebi in hideout</t>
   </si>
   <si>
     <t xml:space="preserve">In Original all keywords from 0 to 114 are used.</t>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="20"/>
   </bookViews>
   <sheets>
     <sheet name="Neue Daten Ep3" sheetId="1" state="visible" r:id="rId3"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2665" uniqueCount="1935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2668" uniqueCount="1936">
   <si>
     <t xml:space="preserve">Map texts</t>
   </si>
@@ -4434,6 +4434,9 @@
   </si>
   <si>
     <t xml:space="preserve">Prisoner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood</t>
   </si>
   <si>
     <t xml:space="preserve">Manyeyes’ castle door</t>
@@ -14456,7 +14459,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="32"/>
@@ -15051,6 +15054,20 @@
         <v>1412</v>
       </c>
       <c r="D35" s="6" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="n">
+        <v>404</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>1365</v>
       </c>
     </row>
@@ -15096,13 +15113,13 @@
         <v>173</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15110,13 +15127,13 @@
         <v>174</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>984</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15124,13 +15141,13 @@
         <v>175</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>984</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15138,13 +15155,13 @@
         <v>176</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>986</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15152,13 +15169,13 @@
         <v>177</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>986</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15166,13 +15183,13 @@
         <v>178</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15180,13 +15197,13 @@
         <v>179</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>995</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15194,13 +15211,13 @@
         <v>180</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>995</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15208,13 +15225,13 @@
         <v>181</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>995</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15222,13 +15239,13 @@
         <v>182</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>995</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15236,13 +15253,13 @@
         <v>183</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>995</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15250,13 +15267,13 @@
         <v>184</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15264,13 +15281,13 @@
         <v>185</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15278,13 +15295,13 @@
         <v>186</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
   </sheetData>
@@ -15330,13 +15347,13 @@
         <v>92</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>978</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15344,13 +15361,13 @@
         <v>93</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>978</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15358,13 +15375,13 @@
         <v>94</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>978</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15372,13 +15389,13 @@
         <v>95</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15386,13 +15403,13 @@
         <v>96</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>1440</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>1441</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>1439</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15400,13 +15417,13 @@
         <v>97</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>1442</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>1441</v>
-      </c>
       <c r="D7" s="6" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15414,13 +15431,13 @@
         <v>98</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>984</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15428,13 +15445,13 @@
         <v>99</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15442,13 +15459,13 @@
         <v>100</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>1446</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>1445</v>
-      </c>
       <c r="D10" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15456,13 +15473,13 @@
         <v>101</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15470,13 +15487,13 @@
         <v>102</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15484,13 +15501,13 @@
         <v>103</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>992</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15498,13 +15515,13 @@
         <v>104</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>992</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15512,13 +15529,13 @@
         <v>105</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>992</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15526,13 +15543,13 @@
         <v>106</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>992</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15540,13 +15557,13 @@
         <v>107</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>992</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15554,13 +15571,13 @@
         <v>108</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>992</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15568,13 +15585,13 @@
         <v>109</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>995</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15582,13 +15599,13 @@
         <v>110</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>995</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15596,13 +15613,13 @@
         <v>111</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15610,13 +15627,13 @@
         <v>112</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15624,13 +15641,13 @@
         <v>113</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15638,13 +15655,13 @@
         <v>114</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15652,13 +15669,13 @@
         <v>115</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15666,13 +15683,13 @@
         <v>116</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15680,13 +15697,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15694,13 +15711,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15708,13 +15725,13 @@
         <v>119</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
   </sheetData>
@@ -15738,7 +15755,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15746,7 +15763,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15754,7 +15771,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15762,7 +15779,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
   </sheetData>
@@ -15790,19 +15807,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
       <c r="G1" s="13" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>438</v>
@@ -15811,7 +15828,7 @@
         <v>434</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>438</v>
@@ -15828,7 +15845,7 @@
         <v>1193</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>4</v>
@@ -15837,7 +15854,7 @@
         <v>1167</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15848,7 +15865,7 @@
         <v>1194</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>4</v>
@@ -15857,7 +15874,7 @@
         <v>1168</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15868,7 +15885,7 @@
         <v>1195</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>4</v>
@@ -15877,7 +15894,7 @@
         <v>1169</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15888,7 +15905,7 @@
         <v>1196</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>4</v>
@@ -15897,7 +15914,7 @@
         <v>1170</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15908,7 +15925,7 @@
         <v>1197</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>4</v>
@@ -15917,7 +15934,7 @@
         <v>1171</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15928,7 +15945,7 @@
         <v>1198</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>4</v>
@@ -15937,7 +15954,7 @@
         <v>1172</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15948,7 +15965,7 @@
         <v>1199</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>4</v>
@@ -15957,7 +15974,7 @@
         <v>1173</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15968,7 +15985,7 @@
         <v>1200</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>4</v>
@@ -15977,7 +15994,7 @@
         <v>1174</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
   </sheetData>
@@ -16012,15 +16029,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="D1" s="13"/>
       <c r="E1" s="13"/>
       <c r="G1" s="13" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
@@ -16028,10 +16045,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="C2" s="52" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="D2" s="53"/>
       <c r="E2" s="54"/>
@@ -16039,291 +16056,291 @@
         <v>439</v>
       </c>
       <c r="H2" s="52" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="I2" s="52" t="s">
         <v>434</v>
       </c>
       <c r="J2" s="52" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="E3" s="55"/>
       <c r="G3" s="1" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16331,147 +16348,147 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16505,32 +16522,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
   </sheetData>
@@ -16558,20 +16575,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="56" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16639,41 +16656,41 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="H15" s="43" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="I15" s="29" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="60" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B16" s="44" t="n">
         <v>0</v>
@@ -16702,7 +16719,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="60" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B17" s="44" t="n">
         <v>125</v>
@@ -16731,7 +16748,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="60" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B18" s="44" t="n">
         <v>100</v>
@@ -16760,7 +16777,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="60" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B19" s="44" t="n">
         <v>100</v>
@@ -16789,7 +16806,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="60" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B20" s="44" t="n">
         <v>75</v>
@@ -16818,7 +16835,7 @@
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="60" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B21" s="44" t="n">
         <v>75</v>
@@ -16847,7 +16864,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="60" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B22" s="44" t="n">
         <v>75</v>
@@ -16876,7 +16893,7 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="61" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B23" s="46" t="n">
         <v>75</v>
@@ -16905,22 +16922,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16928,10 +16945,10 @@
         <v>439</v>
       </c>
       <c r="B32" s="62" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="D32" s="63"/>
       <c r="E32" s="63"/>
@@ -16941,13 +16958,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="44" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="D33" s="64"/>
       <c r="E33" s="64"/>
@@ -16957,13 +16974,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="44" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C34" s="64" t="s">
         <v>1603</v>
-      </c>
-      <c r="B34" s="36" t="s">
-        <v>1601</v>
-      </c>
-      <c r="C34" s="64" t="s">
-        <v>1602</v>
       </c>
       <c r="D34" s="64"/>
       <c r="E34" s="64"/>
@@ -16973,13 +16990,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="44" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="D35" s="64"/>
       <c r="E35" s="64"/>
@@ -16989,13 +17006,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="44" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="C36" s="65" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
@@ -17005,13 +17022,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="44" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="D37" s="64"/>
       <c r="E37" s="64"/>
@@ -17021,13 +17038,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="44" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B38" s="36" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C38" s="64" t="s">
         <v>1609</v>
-      </c>
-      <c r="B38" s="36" t="s">
-        <v>1587</v>
-      </c>
-      <c r="C38" s="64" t="s">
-        <v>1608</v>
       </c>
       <c r="D38" s="64"/>
       <c r="E38" s="64"/>
@@ -17037,13 +17054,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="44" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="C39" s="65" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65"/>
@@ -17056,10 +17073,10 @@
         <v>495</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="C40" s="65" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -17069,13 +17086,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="44" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="C41" s="65" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65"/>
@@ -17085,13 +17102,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="44" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="C42" s="65" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -17101,13 +17118,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="44" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="C43" s="65" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
@@ -17117,13 +17134,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="44" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="C44" s="65" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="D44" s="65"/>
       <c r="E44" s="65"/>
@@ -17133,7 +17150,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="66" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B48" s="66"/>
       <c r="C48" s="66"/>
@@ -17145,17 +17162,17 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="66" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B52" s="66"/>
       <c r="C52" s="66"/>
@@ -17167,12 +17184,12 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="66" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B57" s="66"/>
       <c r="C57" s="66"/>
@@ -17184,72 +17201,72 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="67" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="67" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="67" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H73" s="66" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="I73" s="66"/>
       <c r="J73" s="66"/>
@@ -17257,483 +17274,483 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="67" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="67" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="67" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="67" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="67" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="67" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="67" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="67" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="67" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="67" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="67" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="67" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="67" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="67" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="67" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="67" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="67" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="67" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="67" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="67" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="67" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="67" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="67" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="67" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="67" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="67" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="67" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="67" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="67" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="67" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="67" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="67" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="67" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="67" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="67" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="67" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="67" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="67" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="67" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="67" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="67" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="67" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="67" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="67" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="67" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="67" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="67" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="67" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="67" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="67" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="67" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="67" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="67" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="67" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="67" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="67" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="67" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="67" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="67" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17744,78 +17761,78 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="6" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="67" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="67" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="67" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="67" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="67" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="67" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="67" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="67" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="67" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="67" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="67" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="67" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="67" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
   </sheetData>
@@ -17862,7 +17879,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="66"/>
@@ -17880,10 +17897,10 @@
         <v>439</v>
       </c>
       <c r="D2" s="68" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="E2" s="68" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17894,7 +17911,7 @@
         <v>899</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="D3" s="44" t="n">
         <v>7</v>
@@ -17911,10 +17928,10 @@
         <v>904</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="D4" s="69" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="E4" s="44" t="n">
         <v>6</v>
@@ -17928,10 +17945,10 @@
         <v>904</v>
       </c>
       <c r="C5" s="70" t="s">
+        <v>1765</v>
+      </c>
+      <c r="D5" s="69" t="s">
         <v>1764</v>
-      </c>
-      <c r="D5" s="69" t="s">
-        <v>1763</v>
       </c>
       <c r="E5" s="70" t="n">
         <v>6</v>
@@ -17945,10 +17962,10 @@
         <v>899</v>
       </c>
       <c r="C6" s="70" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="D6" s="72" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="E6" s="70" t="n">
         <v>1</v>
@@ -18038,52 +18055,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
   </sheetData>
@@ -18107,19 +18124,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="73" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
       <c r="D1" s="73"/>
       <c r="E1" s="73" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="F1" s="73"/>
       <c r="G1" s="73"/>
       <c r="H1" s="73"/>
       <c r="I1" s="73" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="J1" s="73"/>
       <c r="K1" s="73"/>
@@ -18135,16 +18152,16 @@
         <v>24</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>21</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18152,10 +18169,10 @@
         <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18163,10 +18180,10 @@
         <v>23</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18174,35 +18191,35 @@
         <v>24</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I6" s="6" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I7" s="6" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I8" s="6" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I9" s="6" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I10" s="6" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
   </sheetData>
@@ -18234,28 +18251,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>1307</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18509,7 +18526,7 @@
         <v>164</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>95</v>
@@ -18591,7 +18608,7 @@
         <v>559</v>
       </c>
       <c r="G15" s="74" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="H15" s="75" t="n">
         <v>45</v>
@@ -18663,7 +18680,7 @@
         <v>1329</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18692,7 +18709,7 @@
         <v>1770</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="H22" s="77" t="s">
         <v>1322</v>
@@ -18711,7 +18728,7 @@
         <v>2023</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="H23" s="77" t="n">
         <f aca="false">J4</f>
@@ -18731,7 +18748,7 @@
         <v>2299</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="H24" s="6" t="e">
         <f aca="false">levelfromexp(H23,VLOOKUP(H22,G2:H10,2,0))</f>
@@ -19115,7 +19132,7 @@
         <v>806</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19123,39 +19140,39 @@
         <v>790</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
   </sheetData>
@@ -19182,7 +19199,7 @@
         <v>103</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19190,7 +19207,7 @@
         <v>104</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19206,7 +19223,7 @@
         <v>106</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19222,7 +19239,7 @@
         <v>108</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
     </row>
   </sheetData>
@@ -19249,7 +19266,7 @@
         <v>760</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19257,7 +19274,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19273,7 +19290,7 @@
         <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19281,7 +19298,7 @@
         <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
     </row>
   </sheetData>
@@ -19308,7 +19325,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19319,7 +19336,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19330,29 +19347,29 @@
         <v>20</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19379,7 +19396,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19398,7 +19415,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19406,10 +19423,10 @@
         <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19417,10 +19434,10 @@
         <v>37</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19428,10 +19445,10 @@
         <v>45</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19442,7 +19459,7 @@
         <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19455,7 +19472,7 @@
         <v>470</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19466,7 +19483,7 @@
         <v>33.34</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19490,7 +19507,7 @@
         <v>457</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19498,7 +19515,7 @@
         <v>472</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19549,7 +19566,7 @@
         <v>0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19565,12 +19582,12 @@
         <v>374</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19583,7 +19600,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>1036</v>
@@ -19596,7 +19613,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19650,12 +19667,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="78" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B1" s="78"/>
       <c r="C1" s="78"/>
       <c r="E1" s="14" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="F1" s="14"/>
       <c r="G1" s="14"/>
@@ -19663,30 +19680,30 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="E2" s="79" t="s">
         <v>439</v>
       </c>
       <c r="F2" s="79" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="G2" s="79" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="H2" s="79" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>1</v>
@@ -19695,7 +19712,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="70" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="F3" s="70" t="n">
         <v>5</v>
@@ -19709,7 +19726,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>6</v>
@@ -19724,7 +19741,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>5</v>
@@ -19739,7 +19756,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>3</v>
@@ -19754,7 +19771,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>2</v>
@@ -19769,7 +19786,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>0</v>
@@ -19778,7 +19795,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="F8" s="80" t="n">
         <f aca="false">SUM(F3:F7)</f>
@@ -19795,7 +19812,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B9" s="6" t="n">
         <v>5</v>
@@ -19806,7 +19823,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>5</v>
@@ -19817,7 +19834,7 @@
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>20</v>
@@ -19826,7 +19843,7 @@
         <v>25</v>
       </c>
       <c r="E11" s="80" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="F11" s="80" t="n">
         <v>10</v>
@@ -19834,7 +19851,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B12" s="6" t="n">
         <v>135</v>
@@ -19843,7 +19860,7 @@
         <v>150</v>
       </c>
       <c r="E12" s="80" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="F12" s="80" t="n">
         <v>7</v>
@@ -19851,7 +19868,7 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B13" s="6" t="n">
         <v>2</v>
@@ -19862,7 +19879,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B14" s="6" t="n">
         <v>5</v>
@@ -19873,7 +19890,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="B15" s="6" t="n">
         <v>15</v>
@@ -19884,7 +19901,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B16" s="6" t="n">
         <v>0</v>
@@ -19895,7 +19912,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="B17" s="6" t="n">
         <v>30</v>
@@ -19904,7 +19921,7 @@
         <v>85</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
@@ -19912,7 +19929,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B18" s="6" t="n">
         <v>0</v>
@@ -19921,21 +19938,21 @@
         <v>25</v>
       </c>
       <c r="E18" s="79" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="F18" s="79" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="G18" s="79" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="H18" s="79" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B19" s="6" t="n">
         <v>0</v>
@@ -19944,7 +19961,7 @@
         <v>99</v>
       </c>
       <c r="E19" s="70" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="F19" s="70" t="n">
         <f aca="false">C3+C26+C34+C41+C48+C55+C63+C70+C77</f>
@@ -19961,7 +19978,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="B20" s="6" t="n">
         <v>0</v>
@@ -19970,7 +19987,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="70" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="F20" s="70" t="n">
         <f aca="false">B4+B29+B66+B71+(F19-B3)*(F11/2)</f>
@@ -19985,12 +20002,12 @@
         <v>300</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B21" s="6" t="n">
         <v>20</v>
@@ -19999,7 +20016,7 @@
         <v>60</v>
       </c>
       <c r="E21" s="70" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="F21" s="70" t="n">
         <f aca="false">B5+B30+B81+(F19-B3)*(F12/2)</f>
@@ -20016,7 +20033,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B22" s="6" t="n">
         <v>0</v>
@@ -20025,7 +20042,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="70" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="F22" s="70" t="n">
         <f aca="false">B6+B37+B50</f>
@@ -20042,7 +20059,7 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="B23" s="6" t="n">
         <v>0</v>
@@ -20051,7 +20068,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="70" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="F23" s="70" t="n">
         <f aca="false">B7+B36+B56+B65+ROUNDDOWN(F25/25,0)</f>
@@ -20066,12 +20083,12 @@
         <v>25</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E24" s="70" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="F24" s="70" t="n">
         <f aca="false">B8+B42+B57+ROUNDDOWN(F29/25,0)</f>
@@ -20086,21 +20103,21 @@
         <v>22</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="E25" s="70" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="F25" s="70" t="n">
         <f aca="false">B9+B44+B64</f>
@@ -20117,7 +20134,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B26" s="6" t="n">
         <v>4</v>
@@ -20126,7 +20143,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="70" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="F26" s="70" t="n">
         <f aca="false">B10+B78</f>
@@ -20143,7 +20160,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B27" s="6" t="n">
         <v>10</v>
@@ -20152,7 +20169,7 @@
         <v>10</v>
       </c>
       <c r="E27" s="70" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="F27" s="70" t="n">
         <f aca="false">B11+B79</f>
@@ -20169,7 +20186,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B28" s="6" t="n">
         <v>20</v>
@@ -20178,7 +20195,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="70" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="F28" s="70" t="n">
         <f aca="false">B12+B49</f>
@@ -20195,7 +20212,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B29" s="6" t="n">
         <v>18</v>
@@ -20204,7 +20221,7 @@
         <v>22</v>
       </c>
       <c r="E29" s="70" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="F29" s="70" t="n">
         <f aca="false">B13+B27+B58</f>
@@ -20221,7 +20238,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="B30" s="6" t="n">
         <v>5</v>
@@ -20230,7 +20247,7 @@
         <v>5</v>
       </c>
       <c r="E30" s="70" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="F30" s="70" t="n">
         <f aca="false">B14+B59+B80</f>
@@ -20247,7 +20264,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E31" s="70" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="F31" s="70" t="n">
         <f aca="false">B15</f>
@@ -20264,7 +20281,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E32" s="70" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="F32" s="70" t="n">
         <f aca="false">B16+B35+B43+B51</f>
@@ -20284,13 +20301,13 @@
         <v>790</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="E33" s="70" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="F33" s="70" t="n">
         <v>30</v>
@@ -20305,7 +20322,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B34" s="6" t="n">
         <v>4</v>
@@ -20314,7 +20331,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="70" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="F34" s="70" t="n">
         <v>0</v>
@@ -20329,7 +20346,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B35" s="6" t="n">
         <v>5</v>
@@ -20338,7 +20355,7 @@
         <v>5</v>
       </c>
       <c r="E35" s="70" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="F35" s="70" t="n">
         <f aca="false">B19+B28</f>
@@ -20354,7 +20371,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B36" s="6" t="n">
         <v>4</v>
@@ -20363,7 +20380,7 @@
         <v>6</v>
       </c>
       <c r="E36" s="70" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="F36" s="70" t="n">
         <v>0</v>
@@ -20379,7 +20396,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B37" s="6" t="n">
         <v>1</v>
@@ -20388,7 +20405,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="70" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="F37" s="70" t="n">
         <v>20</v>
@@ -20403,7 +20420,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E38" s="70" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="F38" s="70" t="n">
         <f aca="false">B22+B45+B60+B84</f>
@@ -20420,7 +20437,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E39" s="70" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="F39" s="70" t="n">
         <f aca="false">B23+B67+B72+B83</f>
@@ -20440,15 +20457,15 @@
         <v>806</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B41" s="6" t="n">
         <v>4</v>
@@ -20459,7 +20476,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B42" s="6" t="n">
         <v>13</v>
@@ -20470,7 +20487,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B43" s="6" t="n">
         <v>5</v>
@@ -20481,7 +20498,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B44" s="6" t="n">
         <v>10</v>
@@ -20492,7 +20509,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B45" s="6" t="n">
         <v>1</v>
@@ -20503,18 +20520,18 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B48" s="6" t="n">
         <v>4</v>
@@ -20525,7 +20542,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B49" s="6" t="n">
         <v>10</v>
@@ -20536,7 +20553,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B50" s="6" t="n">
         <v>1</v>
@@ -20547,7 +20564,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B51" s="6" t="n">
         <v>5</v>
@@ -20558,18 +20575,18 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B55" s="6" t="n">
         <v>4</v>
@@ -20580,7 +20597,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B56" s="6" t="n">
         <v>4</v>
@@ -20591,7 +20608,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B57" s="6" t="n">
         <v>4</v>
@@ -20602,7 +20619,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B58" s="6" t="n">
         <v>10</v>
@@ -20613,7 +20630,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B59" s="6" t="n">
         <v>10</v>
@@ -20624,7 +20641,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B60" s="6" t="n">
         <v>1</v>
@@ -20635,18 +20652,18 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B63" s="6" t="n">
         <v>4</v>
@@ -20657,7 +20674,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B64" s="6" t="n">
         <v>10</v>
@@ -20668,7 +20685,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B65" s="6" t="n">
         <v>9</v>
@@ -20679,7 +20696,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B66" s="6" t="n">
         <v>10</v>
@@ -20690,7 +20707,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="B67" s="6" t="n">
         <v>1</v>
@@ -20701,18 +20718,18 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B70" s="6" t="n">
         <v>3</v>
@@ -20723,7 +20740,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B71" s="6" t="n">
         <v>15</v>
@@ -20734,7 +20751,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="B72" s="6" t="n">
         <v>1</v>
@@ -20745,18 +20762,18 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B77" s="6" t="n">
         <v>5</v>
@@ -20767,7 +20784,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B78" s="6" t="n">
         <v>10</v>
@@ -20778,7 +20795,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B79" s="6" t="n">
         <v>10</v>
@@ -20789,7 +20806,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B80" s="6" t="n">
         <v>10</v>
@@ -20800,7 +20817,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="B81" s="6" t="n">
         <v>25</v>
@@ -20811,7 +20828,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B82" s="6" t="n">
         <v>5</v>
@@ -20822,7 +20839,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="B83" s="6" t="n">
         <v>1</v>
@@ -20833,7 +20850,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B84" s="6" t="n">
         <v>1</v>
@@ -20868,55 +20885,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
     </row>
   </sheetData>
@@ -20956,10 +20973,10 @@
         <v>438</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20967,7 +20984,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>904</v>
@@ -20979,7 +20996,7 @@
         <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20987,7 +21004,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>904</v>
@@ -20999,7 +21016,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -21012,10 +21029,10 @@
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="1" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
     </row>
   </sheetData>
@@ -21443,189 +21460,189 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
   </sheetData>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="14"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="Neue Daten Ep3" sheetId="1" state="visible" r:id="rId3"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2698" uniqueCount="1959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2701" uniqueCount="1960">
   <si>
     <t xml:space="preserve">Map texts</t>
   </si>
@@ -4059,6 +4059,9 @@
   </si>
   <si>
     <t xml:space="preserve">5 Nahrung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294 (X038)</t>
   </si>
   <si>
     <t xml:space="preserve">DoorIndex</t>
@@ -12027,7 +12030,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="23" width="11.43"/>
@@ -13353,6 +13356,17 @@
         <v>1281</v>
       </c>
       <c r="C109" s="6" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="23" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C110" s="6" t="s">
         <v>1289</v>
       </c>
     </row>
@@ -13385,7 +13399,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>442</v>
@@ -13396,7 +13410,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13404,7 +13418,7 @@
         <v>40</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13412,7 +13426,7 @@
         <v>41</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13420,7 +13434,7 @@
         <v>42</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13428,7 +13442,7 @@
         <v>43</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13436,7 +13450,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13444,7 +13458,7 @@
         <v>45</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13452,7 +13466,7 @@
         <v>46</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13460,7 +13474,7 @@
         <v>47</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13468,7 +13482,7 @@
         <v>48</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13476,7 +13490,7 @@
         <v>49</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13484,7 +13498,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13492,7 +13506,7 @@
         <v>51</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13500,7 +13514,7 @@
         <v>52</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13508,7 +13522,7 @@
         <v>53</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13516,7 +13530,7 @@
         <v>54</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13524,7 +13538,7 @@
         <v>55</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13532,7 +13546,7 @@
         <v>56</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13540,7 +13554,7 @@
         <v>57</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13548,7 +13562,7 @@
         <v>58</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13556,7 +13570,7 @@
         <v>59</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13564,7 +13578,7 @@
         <v>60</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13572,7 +13586,7 @@
         <v>61</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13580,7 +13594,7 @@
         <v>62</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13588,7 +13602,7 @@
         <v>63</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
   </sheetData>
@@ -13615,26 +13629,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
   </sheetData>
@@ -13670,80 +13684,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="E1" s="26" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="F1" s="26"/>
       <c r="G1" s="26"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="J4" s="29" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="K4" s="30" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="L4" s="29" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="M4" s="30" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="N4" s="31" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="F5" s="33" t="n">
         <v>75</v>
@@ -13778,13 +13792,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="F6" s="33" t="n">
         <v>150</v>
@@ -13819,13 +13833,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="F7" s="33" t="n">
         <v>180</v>
@@ -13860,13 +13874,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="F8" s="33" t="n">
         <v>100</v>
@@ -13901,13 +13915,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="F9" s="33" t="n">
         <v>125</v>
@@ -13942,13 +13956,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="F10" s="33" t="n">
         <v>90</v>
@@ -13983,10 +13997,10 @@
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="E11" s="32" t="s">
         <v>17</v>
@@ -14024,13 +14038,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="F12" s="33" t="n">
         <v>90</v>
@@ -14065,13 +14079,13 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="F13" s="33" t="n">
         <v>95</v>
@@ -14106,13 +14120,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="F14" s="39" t="n">
         <v>32767</v>
@@ -14147,58 +14161,58 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="F17" s="43" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G17" s="43" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H17" s="43" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="I17" s="43" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="J17" s="43" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="K17" s="29" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="F18" s="44" t="n">
         <v>75</v>
@@ -14225,13 +14239,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="F19" s="44" t="n">
         <v>59850</v>
@@ -14258,13 +14272,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="F20" s="44" t="n">
         <v>150</v>
@@ -14291,7 +14305,7 @@
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E21" s="35" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F21" s="44" t="n">
         <v>600</v>
@@ -14318,7 +14332,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E22" s="35" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="F22" s="44" t="n">
         <v>950</v>
@@ -14345,7 +14359,7 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E23" s="35" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="F23" s="44" t="n">
         <v>1890</v>
@@ -14372,7 +14386,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E24" s="35" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="F24" s="44" t="n">
         <v>4500</v>
@@ -14399,7 +14413,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E25" s="35" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="F25" s="44" t="n">
         <v>12240</v>
@@ -14426,7 +14440,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E26" s="35" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="F26" s="44" t="n">
         <v>29250</v>
@@ -14453,7 +14467,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E27" s="41" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="F27" s="46" t="n">
         <v>113400</v>
@@ -14603,7 +14617,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
   </sheetData>
@@ -14633,7 +14647,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="48" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B1" s="49" t="s">
         <v>442</v>
@@ -14642,10 +14656,10 @@
         <v>986</v>
       </c>
       <c r="D1" s="49" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="E1" s="50" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14653,16 +14667,16 @@
         <v>39</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>913</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14670,16 +14684,16 @@
         <v>153</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>913</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14687,16 +14701,16 @@
         <v>86</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>913</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14704,16 +14718,16 @@
         <v>154</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>913</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14721,16 +14735,16 @@
         <v>374</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14738,16 +14752,16 @@
         <v>375</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>913</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14755,16 +14769,16 @@
         <v>376</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1001</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14772,16 +14786,16 @@
         <v>377</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>995</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14789,16 +14803,16 @@
         <v>378</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>995</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14806,16 +14820,16 @@
         <v>379</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>995</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14823,16 +14837,16 @@
         <v>380</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14840,16 +14854,16 @@
         <v>381</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14857,16 +14871,16 @@
         <v>382</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>1400</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>1399</v>
-      </c>
       <c r="D14" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14874,16 +14888,16 @@
         <v>383</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14891,16 +14905,16 @@
         <v>384</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14908,16 +14922,16 @@
         <v>385</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14925,16 +14939,16 @@
         <v>386</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14942,16 +14956,16 @@
         <v>387</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>1003</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14959,16 +14973,16 @@
         <v>388</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>1003</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14976,16 +14990,16 @@
         <v>389</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>1003</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14993,16 +15007,16 @@
         <v>390</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>1003</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15010,16 +15024,16 @@
         <v>391</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15027,16 +15041,16 @@
         <v>392</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15047,13 +15061,13 @@
         <v>1073</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15061,16 +15075,16 @@
         <v>394</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15078,16 +15092,16 @@
         <v>395</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15098,13 +15112,13 @@
         <v>854</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15112,16 +15126,16 @@
         <v>397</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15129,16 +15143,16 @@
         <v>398</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15146,16 +15160,16 @@
         <v>399</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15163,16 +15177,16 @@
         <v>400</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15180,13 +15194,13 @@
         <v>401</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15194,16 +15208,16 @@
         <v>402</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15211,13 +15225,13 @@
         <v>403</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15225,13 +15239,13 @@
         <v>404</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
   </sheetData>
@@ -15259,7 +15273,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>442</v>
@@ -15268,7 +15282,7 @@
         <v>986</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15276,13 +15290,13 @@
         <v>173</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15290,13 +15304,13 @@
         <v>174</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>995</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15304,13 +15318,13 @@
         <v>175</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>995</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15318,13 +15332,13 @@
         <v>176</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15332,13 +15346,13 @@
         <v>177</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15346,13 +15360,13 @@
         <v>178</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15360,13 +15374,13 @@
         <v>179</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1006</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15374,13 +15388,13 @@
         <v>180</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>1006</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15388,13 +15402,13 @@
         <v>181</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>1006</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15402,13 +15416,13 @@
         <v>182</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>1006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15416,13 +15430,13 @@
         <v>183</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>1006</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15430,13 +15444,13 @@
         <v>184</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15444,13 +15458,13 @@
         <v>185</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>1008</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15458,13 +15472,13 @@
         <v>186</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>1008</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
   </sheetData>
@@ -15493,7 +15507,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B1" s="18" t="s">
         <v>442</v>
@@ -15502,7 +15516,7 @@
         <v>986</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15510,13 +15524,13 @@
         <v>92</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>989</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15524,13 +15538,13 @@
         <v>93</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>989</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15538,13 +15552,13 @@
         <v>94</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>989</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15552,13 +15566,13 @@
         <v>95</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15566,13 +15580,13 @@
         <v>96</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>1464</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>1465</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>1463</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15580,13 +15594,13 @@
         <v>97</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>1466</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>1465</v>
-      </c>
       <c r="D7" s="6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15594,13 +15608,13 @@
         <v>98</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>995</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15608,13 +15622,13 @@
         <v>99</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15622,13 +15636,13 @@
         <v>100</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>1470</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>1469</v>
-      </c>
       <c r="D10" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15636,13 +15650,13 @@
         <v>101</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15650,13 +15664,13 @@
         <v>102</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15664,13 +15678,13 @@
         <v>103</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>1003</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15678,13 +15692,13 @@
         <v>104</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>1003</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15692,13 +15706,13 @@
         <v>105</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>1003</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15706,13 +15720,13 @@
         <v>106</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>1003</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15720,13 +15734,13 @@
         <v>107</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>1003</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15734,13 +15748,13 @@
         <v>108</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>1003</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15748,13 +15762,13 @@
         <v>109</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>1006</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15762,13 +15776,13 @@
         <v>110</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>1006</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15776,13 +15790,13 @@
         <v>111</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>1008</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15790,13 +15804,13 @@
         <v>112</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>1008</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15804,13 +15818,13 @@
         <v>113</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>1008</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15818,13 +15832,13 @@
         <v>114</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>1008</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15832,13 +15846,13 @@
         <v>115</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>1008</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15846,13 +15860,13 @@
         <v>116</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>1008</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15860,13 +15874,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>1008</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15874,13 +15888,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>1008</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15888,13 +15902,13 @@
         <v>119</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>1008</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
   </sheetData>
@@ -15918,7 +15932,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15926,7 +15940,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15934,7 +15948,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15942,7 +15956,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
   </sheetData>
@@ -15970,19 +15984,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
       <c r="G1" s="13" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>446</v>
@@ -15991,7 +16005,7 @@
         <v>442</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>446</v>
@@ -16008,7 +16022,7 @@
         <v>1193</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>4</v>
@@ -16017,7 +16031,7 @@
         <v>1167</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16028,7 +16042,7 @@
         <v>1194</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>4</v>
@@ -16037,7 +16051,7 @@
         <v>1168</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16048,7 +16062,7 @@
         <v>1195</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>4</v>
@@ -16057,7 +16071,7 @@
         <v>1169</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16068,7 +16082,7 @@
         <v>1196</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>4</v>
@@ -16077,7 +16091,7 @@
         <v>1170</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16088,7 +16102,7 @@
         <v>1197</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>4</v>
@@ -16097,7 +16111,7 @@
         <v>1171</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16108,7 +16122,7 @@
         <v>1198</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>4</v>
@@ -16117,7 +16131,7 @@
         <v>1172</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16128,7 +16142,7 @@
         <v>1199</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>4</v>
@@ -16137,7 +16151,7 @@
         <v>1173</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16148,7 +16162,7 @@
         <v>1200</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>4</v>
@@ -16157,7 +16171,7 @@
         <v>1174</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
   </sheetData>
@@ -16192,15 +16206,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="D1" s="13"/>
       <c r="E1" s="13"/>
       <c r="G1" s="13" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
@@ -16208,10 +16222,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="C2" s="52" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="D2" s="53"/>
       <c r="E2" s="54"/>
@@ -16219,291 +16233,291 @@
         <v>447</v>
       </c>
       <c r="H2" s="52" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="I2" s="52" t="s">
         <v>442</v>
       </c>
       <c r="J2" s="52" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="E3" s="55"/>
       <c r="G3" s="1" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16511,147 +16525,147 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16685,32 +16699,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
   </sheetData>
@@ -16738,20 +16752,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="56" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16819,41 +16833,41 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="H15" s="43" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="I15" s="29" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="60" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B16" s="44" t="n">
         <v>0</v>
@@ -16882,7 +16896,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="60" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B17" s="44" t="n">
         <v>125</v>
@@ -16911,7 +16925,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="60" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B18" s="44" t="n">
         <v>100</v>
@@ -16940,7 +16954,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="60" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B19" s="44" t="n">
         <v>100</v>
@@ -16969,7 +16983,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="60" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B20" s="44" t="n">
         <v>75</v>
@@ -16998,7 +17012,7 @@
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="60" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B21" s="44" t="n">
         <v>75</v>
@@ -17027,7 +17041,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="60" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B22" s="44" t="n">
         <v>75</v>
@@ -17056,7 +17070,7 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="61" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B23" s="46" t="n">
         <v>75</v>
@@ -17085,22 +17099,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17108,10 +17122,10 @@
         <v>447</v>
       </c>
       <c r="B32" s="62" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="D32" s="63"/>
       <c r="E32" s="63"/>
@@ -17121,13 +17135,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="44" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="D33" s="64"/>
       <c r="E33" s="64"/>
@@ -17137,13 +17151,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="44" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C34" s="64" t="s">
         <v>1627</v>
-      </c>
-      <c r="B34" s="36" t="s">
-        <v>1625</v>
-      </c>
-      <c r="C34" s="64" t="s">
-        <v>1626</v>
       </c>
       <c r="D34" s="64"/>
       <c r="E34" s="64"/>
@@ -17153,13 +17167,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="44" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="D35" s="64"/>
       <c r="E35" s="64"/>
@@ -17169,13 +17183,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="44" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="C36" s="65" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
@@ -17185,13 +17199,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="44" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="D37" s="64"/>
       <c r="E37" s="64"/>
@@ -17201,13 +17215,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="44" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B38" s="36" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C38" s="64" t="s">
         <v>1633</v>
-      </c>
-      <c r="B38" s="36" t="s">
-        <v>1611</v>
-      </c>
-      <c r="C38" s="64" t="s">
-        <v>1632</v>
       </c>
       <c r="D38" s="64"/>
       <c r="E38" s="64"/>
@@ -17217,13 +17231,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="44" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="C39" s="65" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65"/>
@@ -17236,10 +17250,10 @@
         <v>503</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="C40" s="65" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -17249,13 +17263,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="44" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="C41" s="65" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65"/>
@@ -17265,13 +17279,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="44" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="C42" s="65" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -17281,13 +17295,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="44" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="C43" s="65" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
@@ -17297,13 +17311,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="44" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="C44" s="65" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="D44" s="65"/>
       <c r="E44" s="65"/>
@@ -17313,7 +17327,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="66" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B48" s="66"/>
       <c r="C48" s="66"/>
@@ -17325,17 +17339,17 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="66" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B52" s="66"/>
       <c r="C52" s="66"/>
@@ -17347,12 +17361,12 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="66" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B57" s="66"/>
       <c r="C57" s="66"/>
@@ -17364,72 +17378,72 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="67" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="67" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="67" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H73" s="66" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="I73" s="66"/>
       <c r="J73" s="66"/>
@@ -17437,483 +17451,483 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="67" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="67" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="67" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="67" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="67" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="67" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="67" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="67" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="67" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="67" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="67" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="67" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="67" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="67" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="67" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="67" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="67" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="67" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="67" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="67" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="67" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="67" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="67" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="67" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="67" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="67" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="67" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="67" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="67" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="67" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="67" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="67" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="67" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="67" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="67" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="67" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="67" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="67" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="67" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="67" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="67" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="67" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="67" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="67" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="67" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="67" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="67" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="67" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="67" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="67" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="67" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="67" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="67" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="67" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="67" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="67" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="67" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="67" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17924,78 +17938,78 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="6" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="67" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="67" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="67" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="67" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="67" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="67" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="67" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="67" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="67" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="67" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="67" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="67" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="67" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
   </sheetData>
@@ -18042,7 +18056,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="66"/>
@@ -18060,10 +18074,10 @@
         <v>447</v>
       </c>
       <c r="D2" s="68" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="E2" s="68" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18074,7 +18088,7 @@
         <v>909</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="D3" s="44" t="n">
         <v>7</v>
@@ -18091,10 +18105,10 @@
         <v>914</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="D4" s="69" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="E4" s="44" t="n">
         <v>6</v>
@@ -18108,10 +18122,10 @@
         <v>914</v>
       </c>
       <c r="C5" s="70" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D5" s="69" t="s">
         <v>1788</v>
-      </c>
-      <c r="D5" s="69" t="s">
-        <v>1787</v>
       </c>
       <c r="E5" s="70" t="n">
         <v>6</v>
@@ -18125,10 +18139,10 @@
         <v>909</v>
       </c>
       <c r="C6" s="70" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="D6" s="72" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="E6" s="70" t="n">
         <v>1</v>
@@ -18218,52 +18232,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
   </sheetData>
@@ -18287,19 +18301,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="73" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
       <c r="D1" s="73"/>
       <c r="E1" s="73" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="F1" s="73"/>
       <c r="G1" s="73"/>
       <c r="H1" s="73"/>
       <c r="I1" s="73" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="J1" s="73"/>
       <c r="K1" s="73"/>
@@ -18315,16 +18329,16 @@
         <v>24</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>21</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18332,10 +18346,10 @@
         <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18343,10 +18357,10 @@
         <v>23</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18354,35 +18368,35 @@
         <v>24</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I6" s="6" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I7" s="6" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I8" s="6" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I9" s="6" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I10" s="6" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
   </sheetData>
@@ -18414,28 +18428,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18449,7 +18463,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2" s="6" t="n">
         <v>85</v>
@@ -18479,7 +18493,7 @@
         <v>3</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H3" s="6" t="n">
         <v>110</v>
@@ -18509,7 +18523,7 @@
         <v>9</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>115</v>
@@ -18539,7 +18553,7 @@
         <v>19</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>100</v>
@@ -18569,7 +18583,7 @@
         <v>34</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>105</v>
@@ -18599,7 +18613,7 @@
         <v>55</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>90</v>
@@ -18659,7 +18673,7 @@
         <v>119</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>90</v>
@@ -18689,7 +18703,7 @@
         <v>164</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>95</v>
@@ -18771,7 +18785,7 @@
         <v>559</v>
       </c>
       <c r="G15" s="74" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="H15" s="75" t="n">
         <v>45</v>
@@ -18843,7 +18857,7 @@
         <v>1329</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18872,10 +18886,10 @@
         <v>1770</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="H22" s="77" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18891,7 +18905,7 @@
         <v>2023</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="H23" s="77" t="n">
         <f aca="false">J4</f>
@@ -18911,7 +18925,7 @@
         <v>2299</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="H24" s="6" t="e">
         <f aca="false">levelfromexp(H23,VLOOKUP(H22,G2:H10,2,0))</f>
@@ -19295,7 +19309,7 @@
         <v>816</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19303,39 +19317,39 @@
         <v>800</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
   </sheetData>
@@ -19362,7 +19376,7 @@
         <v>103</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19370,7 +19384,7 @@
         <v>104</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19386,7 +19400,7 @@
         <v>106</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19402,7 +19416,7 @@
         <v>108</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
     </row>
   </sheetData>
@@ -19429,7 +19443,7 @@
         <v>770</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19437,7 +19451,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19453,7 +19467,7 @@
         <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19461,7 +19475,7 @@
         <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
     </row>
   </sheetData>
@@ -19488,7 +19502,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19499,7 +19513,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19510,29 +19524,29 @@
         <v>20</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19559,7 +19573,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19578,7 +19592,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19586,10 +19600,10 @@
         <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19597,10 +19611,10 @@
         <v>37</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19608,10 +19622,10 @@
         <v>45</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19622,7 +19636,7 @@
         <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19635,7 +19649,7 @@
         <v>470</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19646,7 +19660,7 @@
         <v>33.34</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19670,7 +19684,7 @@
         <v>457</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19678,7 +19692,7 @@
         <v>472</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19729,7 +19743,7 @@
         <v>0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19745,12 +19759,12 @@
         <v>374</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19763,7 +19777,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>1047</v>
@@ -19776,7 +19790,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19830,12 +19844,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="78" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="B1" s="78"/>
       <c r="C1" s="78"/>
       <c r="E1" s="14" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="F1" s="14"/>
       <c r="G1" s="14"/>
@@ -19843,30 +19857,30 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="E2" s="79" t="s">
         <v>447</v>
       </c>
       <c r="F2" s="79" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="G2" s="79" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="H2" s="79" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>1</v>
@@ -19875,7 +19889,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="70" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="F3" s="70" t="n">
         <v>5</v>
@@ -19889,7 +19903,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>6</v>
@@ -19904,7 +19918,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>5</v>
@@ -19919,7 +19933,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>3</v>
@@ -19934,7 +19948,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>2</v>
@@ -19949,7 +19963,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>0</v>
@@ -19958,7 +19972,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="F8" s="80" t="n">
         <f aca="false">SUM(F3:F7)</f>
@@ -19975,7 +19989,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="B9" s="6" t="n">
         <v>5</v>
@@ -19986,7 +20000,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>5</v>
@@ -19997,7 +20011,7 @@
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>20</v>
@@ -20006,7 +20020,7 @@
         <v>25</v>
       </c>
       <c r="E11" s="80" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="F11" s="80" t="n">
         <v>10</v>
@@ -20014,7 +20028,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="B12" s="6" t="n">
         <v>135</v>
@@ -20023,7 +20037,7 @@
         <v>150</v>
       </c>
       <c r="E12" s="80" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="F12" s="80" t="n">
         <v>7</v>
@@ -20031,7 +20045,7 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="B13" s="6" t="n">
         <v>2</v>
@@ -20042,7 +20056,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="B14" s="6" t="n">
         <v>5</v>
@@ -20053,7 +20067,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="B15" s="6" t="n">
         <v>15</v>
@@ -20064,7 +20078,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="B16" s="6" t="n">
         <v>0</v>
@@ -20075,7 +20089,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B17" s="6" t="n">
         <v>30</v>
@@ -20084,7 +20098,7 @@
         <v>85</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
@@ -20092,7 +20106,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="B18" s="6" t="n">
         <v>0</v>
@@ -20101,21 +20115,21 @@
         <v>25</v>
       </c>
       <c r="E18" s="79" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="F18" s="79" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="G18" s="79" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="H18" s="79" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B19" s="6" t="n">
         <v>0</v>
@@ -20124,7 +20138,7 @@
         <v>99</v>
       </c>
       <c r="E19" s="70" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="F19" s="70" t="n">
         <f aca="false">C3+C26+C34+C41+C48+C55+C63+C70+C77</f>
@@ -20141,7 +20155,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="B20" s="6" t="n">
         <v>0</v>
@@ -20150,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="70" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="F20" s="70" t="n">
         <f aca="false">B4+B29+B66+B71+(F19-B3)*(F11/2)</f>
@@ -20165,12 +20179,12 @@
         <v>300</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B21" s="6" t="n">
         <v>20</v>
@@ -20179,7 +20193,7 @@
         <v>60</v>
       </c>
       <c r="E21" s="70" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="F21" s="70" t="n">
         <f aca="false">B5+B30+B81+(F19-B3)*(F12/2)</f>
@@ -20196,7 +20210,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="B22" s="6" t="n">
         <v>0</v>
@@ -20205,7 +20219,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="70" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="F22" s="70" t="n">
         <f aca="false">B6+B37+B50</f>
@@ -20222,7 +20236,7 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B23" s="6" t="n">
         <v>0</v>
@@ -20231,7 +20245,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="70" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="F23" s="70" t="n">
         <f aca="false">B7+B36+B56+B65+ROUNDDOWN(F25/25,0)</f>
@@ -20246,12 +20260,12 @@
         <v>25</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E24" s="70" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="F24" s="70" t="n">
         <f aca="false">B8+B42+B57+ROUNDDOWN(F29/25,0)</f>
@@ -20266,21 +20280,21 @@
         <v>22</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="E25" s="70" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="F25" s="70" t="n">
         <f aca="false">B9+B44+B64</f>
@@ -20297,7 +20311,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B26" s="6" t="n">
         <v>4</v>
@@ -20306,7 +20320,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="70" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="F26" s="70" t="n">
         <f aca="false">B10+B78</f>
@@ -20323,7 +20337,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="B27" s="6" t="n">
         <v>10</v>
@@ -20332,7 +20346,7 @@
         <v>10</v>
       </c>
       <c r="E27" s="70" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="F27" s="70" t="n">
         <f aca="false">B11+B79</f>
@@ -20349,7 +20363,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B28" s="6" t="n">
         <v>20</v>
@@ -20358,7 +20372,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="70" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="F28" s="70" t="n">
         <f aca="false">B12+B49</f>
@@ -20375,7 +20389,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="B29" s="6" t="n">
         <v>18</v>
@@ -20384,7 +20398,7 @@
         <v>22</v>
       </c>
       <c r="E29" s="70" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="F29" s="70" t="n">
         <f aca="false">B13+B27+B58</f>
@@ -20401,7 +20415,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B30" s="6" t="n">
         <v>5</v>
@@ -20410,7 +20424,7 @@
         <v>5</v>
       </c>
       <c r="E30" s="70" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="F30" s="70" t="n">
         <f aca="false">B14+B59+B80</f>
@@ -20427,7 +20441,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E31" s="70" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="F31" s="70" t="n">
         <f aca="false">B15</f>
@@ -20444,7 +20458,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E32" s="70" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="F32" s="70" t="n">
         <f aca="false">B16+B35+B43+B51</f>
@@ -20464,13 +20478,13 @@
         <v>800</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="E33" s="70" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="F33" s="70" t="n">
         <v>30</v>
@@ -20485,7 +20499,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B34" s="6" t="n">
         <v>4</v>
@@ -20494,7 +20508,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="70" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="F34" s="70" t="n">
         <v>0</v>
@@ -20509,7 +20523,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="B35" s="6" t="n">
         <v>5</v>
@@ -20518,7 +20532,7 @@
         <v>5</v>
       </c>
       <c r="E35" s="70" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="F35" s="70" t="n">
         <f aca="false">B19+B28</f>
@@ -20534,7 +20548,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B36" s="6" t="n">
         <v>4</v>
@@ -20543,7 +20557,7 @@
         <v>6</v>
       </c>
       <c r="E36" s="70" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="F36" s="70" t="n">
         <v>0</v>
@@ -20559,7 +20573,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B37" s="6" t="n">
         <v>1</v>
@@ -20568,7 +20582,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="70" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="F37" s="70" t="n">
         <v>20</v>
@@ -20583,7 +20597,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E38" s="70" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="F38" s="70" t="n">
         <f aca="false">B22+B45+B60+B84</f>
@@ -20600,7 +20614,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E39" s="70" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="F39" s="70" t="n">
         <f aca="false">B23+B67+B72+B83</f>
@@ -20620,15 +20634,15 @@
         <v>816</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B41" s="6" t="n">
         <v>4</v>
@@ -20639,7 +20653,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="B42" s="6" t="n">
         <v>13</v>
@@ -20650,7 +20664,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="B43" s="6" t="n">
         <v>5</v>
@@ -20661,7 +20675,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="B44" s="6" t="n">
         <v>10</v>
@@ -20672,7 +20686,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="B45" s="6" t="n">
         <v>1</v>
@@ -20683,18 +20697,18 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B48" s="6" t="n">
         <v>4</v>
@@ -20705,7 +20719,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="B49" s="6" t="n">
         <v>10</v>
@@ -20716,7 +20730,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B50" s="6" t="n">
         <v>1</v>
@@ -20727,7 +20741,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="B51" s="6" t="n">
         <v>5</v>
@@ -20738,18 +20752,18 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B55" s="6" t="n">
         <v>4</v>
@@ -20760,7 +20774,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B56" s="6" t="n">
         <v>4</v>
@@ -20771,7 +20785,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="B57" s="6" t="n">
         <v>4</v>
@@ -20782,7 +20796,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="B58" s="6" t="n">
         <v>10</v>
@@ -20793,7 +20807,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="B59" s="6" t="n">
         <v>10</v>
@@ -20804,7 +20818,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="B60" s="6" t="n">
         <v>1</v>
@@ -20815,18 +20829,18 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B63" s="6" t="n">
         <v>4</v>
@@ -20837,7 +20851,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="B64" s="6" t="n">
         <v>10</v>
@@ -20848,7 +20862,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B65" s="6" t="n">
         <v>9</v>
@@ -20859,7 +20873,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="B66" s="6" t="n">
         <v>10</v>
@@ -20870,7 +20884,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B67" s="6" t="n">
         <v>1</v>
@@ -20881,18 +20895,18 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B70" s="6" t="n">
         <v>3</v>
@@ -20903,7 +20917,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="B71" s="6" t="n">
         <v>15</v>
@@ -20914,7 +20928,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B72" s="6" t="n">
         <v>1</v>
@@ -20925,18 +20939,18 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B77" s="6" t="n">
         <v>5</v>
@@ -20947,7 +20961,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B78" s="6" t="n">
         <v>10</v>
@@ -20958,7 +20972,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B79" s="6" t="n">
         <v>10</v>
@@ -20969,7 +20983,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="B80" s="6" t="n">
         <v>10</v>
@@ -20980,7 +20994,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B81" s="6" t="n">
         <v>25</v>
@@ -20991,7 +21005,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B82" s="6" t="n">
         <v>5</v>
@@ -21002,7 +21016,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B83" s="6" t="n">
         <v>1</v>
@@ -21013,7 +21027,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="B84" s="6" t="n">
         <v>1</v>
@@ -21048,55 +21062,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
     </row>
   </sheetData>
@@ -21136,10 +21150,10 @@
         <v>446</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21147,7 +21161,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>914</v>
@@ -21159,7 +21173,7 @@
         <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21167,7 +21181,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>914</v>
@@ -21179,7 +21193,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -21192,10 +21206,10 @@
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="1" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
   </sheetData>
@@ -21625,189 +21639,189 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
     </row>
   </sheetData>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="24"/>
   </bookViews>
   <sheets>
     <sheet name="Neue Daten Ep3" sheetId="1" state="visible" r:id="rId3"/>
@@ -32,22 +32,23 @@
     <sheet name="WallGfx" sheetId="22" state="visible" r:id="rId24"/>
     <sheet name="Overlays" sheetId="23" state="visible" r:id="rId25"/>
     <sheet name="Floors" sheetId="24" state="visible" r:id="rId26"/>
-    <sheet name="Tiles" sheetId="25" state="visible" r:id="rId27"/>
-    <sheet name="SpellChanges" sheetId="26" state="visible" r:id="rId28"/>
-    <sheet name="Quest - Sea Creatures" sheetId="27" state="visible" r:id="rId29"/>
-    <sheet name="SpellDamage" sheetId="28" state="visible" r:id="rId30"/>
-    <sheet name="Black Mountains" sheetId="29" state="visible" r:id="rId31"/>
-    <sheet name="SavegamePatching" sheetId="30" state="visible" r:id="rId32"/>
-    <sheet name="CodeChanges" sheetId="31" state="visible" r:id="rId33"/>
-    <sheet name="Exp Table" sheetId="32" state="visible" r:id="rId34"/>
-    <sheet name="Bosses" sheetId="33" state="visible" r:id="rId35"/>
-    <sheet name="Portraits" sheetId="34" state="visible" r:id="rId36"/>
-    <sheet name="MonsterGfx" sheetId="35" state="visible" r:id="rId37"/>
-    <sheet name="Custom Translate" sheetId="36" state="visible" r:id="rId38"/>
-    <sheet name="Kasimir Stats" sheetId="37" state="visible" r:id="rId39"/>
-    <sheet name="Name Ideas" sheetId="38" state="visible" r:id="rId40"/>
-    <sheet name="CombatBackgrounds" sheetId="39" state="visible" r:id="rId41"/>
-    <sheet name="ElementChanges" sheetId="40" state="visible" r:id="rId42"/>
+    <sheet name="Event Pics" sheetId="25" state="visible" r:id="rId27"/>
+    <sheet name="Tiles" sheetId="26" state="visible" r:id="rId28"/>
+    <sheet name="SpellChanges" sheetId="27" state="visible" r:id="rId29"/>
+    <sheet name="Quest - Sea Creatures" sheetId="28" state="visible" r:id="rId30"/>
+    <sheet name="SpellDamage" sheetId="29" state="visible" r:id="rId31"/>
+    <sheet name="Black Mountains" sheetId="30" state="visible" r:id="rId32"/>
+    <sheet name="SavegamePatching" sheetId="31" state="visible" r:id="rId33"/>
+    <sheet name="CodeChanges" sheetId="32" state="visible" r:id="rId34"/>
+    <sheet name="Exp Table" sheetId="33" state="visible" r:id="rId35"/>
+    <sheet name="Bosses" sheetId="34" state="visible" r:id="rId36"/>
+    <sheet name="Portraits" sheetId="35" state="visible" r:id="rId37"/>
+    <sheet name="MonsterGfx" sheetId="36" state="visible" r:id="rId38"/>
+    <sheet name="Custom Translate" sheetId="37" state="visible" r:id="rId39"/>
+    <sheet name="Kasimir Stats" sheetId="38" state="visible" r:id="rId40"/>
+    <sheet name="Name Ideas" sheetId="39" state="visible" r:id="rId41"/>
+    <sheet name="CombatBackgrounds" sheetId="40" state="visible" r:id="rId42"/>
+    <sheet name="ElementChanges" sheetId="41" state="visible" r:id="rId43"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="true" iterateDelta="0.0001"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="2094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2904" uniqueCount="2100">
   <si>
     <t xml:space="preserve">Map texts</t>
   </si>
@@ -1243,214 +1244,34 @@
     <t xml:space="preserve">440: Morag riddle heared and confirmed in lower right ancient building</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">441: Wall storage 1 closed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (lower right ancient building)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">442: Wall storage 2 closed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (lower right ancient building)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">443: Wall storage 3 closed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (lower right ancient building)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">444: Wall storage 4 closed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (lower right ancient building)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">445: Wall storage 5 closed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (lower right ancient building)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">446: Wall storage 1 has correct letter M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (lower right ancient building)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">447: Wall storage 2 has correct letter O</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (lower right ancient building)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">448: Wall storage 3 has correct letter R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (lower right ancient building)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">449: Wall storage 4 has correct letter A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (lower right ancient building)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">450: Wall storage 5 has correct letter G</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (lower right ancient building)</t>
-    </r>
+    <t xml:space="preserve">441: Wall storage 1 closed (lower right ancient building)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">442: Wall storage 2 closed (lower right ancient building)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">443: Wall storage 3 closed (lower right ancient building)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">444: Wall storage 4 closed (lower right ancient building)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">445: Wall storage 5 closed (lower right ancient building)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">446: Wall storage 1 has correct letter M (lower right ancient building)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447: Wall storage 2 has correct letter O (lower right ancient building)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">448: Wall storage 3 has correct letter R (lower right ancient building)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">449: Wall storage 4 has correct letter A (lower right ancient building)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450: Wall storage 5 has correct letter G (lower right ancient building)</t>
   </si>
   <si>
     <t xml:space="preserve">451: Word MORAG completed</t>
@@ -5255,6 +5076,27 @@
     <t xml:space="preserve">Bright stone bricks (prison floor and ceiling)</t>
   </si>
   <si>
+    <t xml:space="preserve">Map ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feline in front of portal. Arrival in Albion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheera merges with portal. Leaving Albion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Moranian rebels. Entering S’Angrila hideout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rebel’s Hideout</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tileset Graphics (Icon Gfx)</t>
   </si>
   <si>
@@ -6123,9 +5965,6 @@
   </si>
   <si>
     <t xml:space="preserve">Tileset/Labdata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palette</t>
   </si>
   <si>
     <t xml:space="preserve">Schwarzberge - 1 / Black Mountains - 1</t>
@@ -6712,16 +6551,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -7018,11 +6857,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7087,11 +6926,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7111,7 +6950,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7131,23 +6970,23 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="6" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="6" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="7" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="7" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="8" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="9" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="9" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7195,7 +7034,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="20" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="20" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7227,19 +7066,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="26" xfId="20" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="26" xfId="20" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="4" xfId="20" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="4" xfId="20" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7247,11 +7090,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="8" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="7" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="7" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7263,19 +7106,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="13" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="18" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="18" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="21" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="27" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="27" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7287,7 +7130,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="21" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9848,7 +9691,7 @@
       <c r="G10" s="20"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="n">
         <v>157</v>
       </c>
@@ -9875,7 +9718,7 @@
       <c r="G12" s="20"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="n">
         <v>198</v>
       </c>
@@ -9982,7 +9825,7 @@
       <c r="F20" s="19"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="n">
         <v>263</v>
       </c>
@@ -10008,7 +9851,7 @@
       <c r="F22" s="21"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="n">
         <v>421</v>
       </c>
@@ -10176,7 +10019,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>45</v>
       </c>
@@ -10204,7 +10047,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>47</v>
       </c>
@@ -10316,7 +10159,7 @@
       <c r="N20" s="22"/>
       <c r="O20" s="22"/>
     </row>
-    <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>78</v>
       </c>
@@ -10571,7 +10414,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="n">
         <v>141</v>
       </c>
@@ -10593,7 +10436,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="n">
         <v>143</v>
       </c>
@@ -10709,7 +10552,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="n">
         <v>151</v>
       </c>
@@ -10738,7 +10581,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="n">
         <v>153</v>
       </c>
@@ -11899,7 +11742,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>48</v>
       </c>
@@ -11915,7 +11758,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>50</v>
       </c>
@@ -11979,7 +11822,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>58</v>
       </c>
@@ -11995,7 +11838,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>60</v>
       </c>
@@ -12217,7 +12060,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>75</v>
       </c>
@@ -12239,7 +12082,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>77</v>
       </c>
@@ -12302,7 +12145,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>23</v>
       </c>
@@ -12324,7 +12167,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
@@ -12760,7 +12603,7 @@
         <v>112500</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
         <v>1467</v>
       </c>
@@ -12842,7 +12685,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
         <v>1467</v>
       </c>
@@ -13068,7 +12911,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E21" s="35" t="s">
         <v>1478</v>
       </c>
@@ -13122,7 +12965,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E23" s="35" t="s">
         <v>1467</v>
       </c>
@@ -13580,7 +13423,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>379</v>
       </c>
@@ -13614,7 +13457,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="n">
         <v>381</v>
       </c>
@@ -13750,7 +13593,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="n">
         <v>389</v>
       </c>
@@ -13784,7 +13627,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>391</v>
       </c>
@@ -14204,7 +14047,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>182</v>
       </c>
@@ -14232,7 +14075,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>184</v>
       </c>
@@ -14494,7 +14337,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>101</v>
       </c>
@@ -14522,7 +14365,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="n">
         <v>103</v>
       </c>
@@ -14634,7 +14477,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>111</v>
       </c>
@@ -14662,7 +14505,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>113</v>
       </c>
@@ -14873,7 +14716,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
+      <c r="A38" s="1" t="n">
         <v>128</v>
       </c>
       <c r="B38" s="6" t="s">
@@ -14887,7 +14730,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+      <c r="A39" s="1" t="n">
         <v>129</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -14964,6 +14807,91 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.65"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>808</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>456</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>382</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>382</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>481</v>
+      </c>
+      <c r="D4" s="51" t="s">
+        <v>1634</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -14973,19 +14901,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>1628</v>
+        <v>1635</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
       <c r="G1" s="13" t="s">
-        <v>1629</v>
+        <v>1636</v>
       </c>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1630</v>
+        <v>1637</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>460</v>
@@ -14994,7 +14922,7 @@
         <v>456</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1630</v>
+        <v>1637</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>460</v>
@@ -15011,7 +14939,7 @@
         <v>1193</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>4</v>
@@ -15020,7 +14948,7 @@
         <v>1167</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15031,7 +14959,7 @@
         <v>1194</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>4</v>
@@ -15040,7 +14968,7 @@
         <v>1168</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15051,7 +14979,7 @@
         <v>1195</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>4</v>
@@ -15060,7 +14988,7 @@
         <v>1169</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15071,7 +14999,7 @@
         <v>1196</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>4</v>
@@ -15080,7 +15008,7 @@
         <v>1170</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15091,7 +15019,7 @@
         <v>1197</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>4</v>
@@ -15100,7 +15028,7 @@
         <v>1171</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15111,7 +15039,7 @@
         <v>1198</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>4</v>
@@ -15120,7 +15048,7 @@
         <v>1172</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15131,7 +15059,7 @@
         <v>1199</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>4</v>
@@ -15140,7 +15068,7 @@
         <v>1173</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15151,7 +15079,7 @@
         <v>1200</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>4</v>
@@ -15160,510 +15088,13 @@
         <v>1174</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="G1:I1"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:J75"/>
-  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="37.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="17.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="35.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="35.19"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="51" t="s">
-        <v>1632</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>1633</v>
-      </c>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="G1" s="13" t="s">
-        <v>1634</v>
-      </c>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>1635</v>
-      </c>
-      <c r="C2" s="52" t="s">
-        <v>1636</v>
-      </c>
-      <c r="D2" s="53"/>
-      <c r="E2" s="54"/>
-      <c r="G2" s="52" t="s">
-        <v>461</v>
-      </c>
-      <c r="H2" s="52" t="s">
-        <v>1637</v>
-      </c>
-      <c r="I2" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="J2" s="52" t="s">
-        <v>1638</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>1639</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>1640</v>
-      </c>
-      <c r="E3" s="55"/>
-      <c r="G3" s="1" t="s">
-        <v>1641</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>1642</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>1643</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>1644</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>1645</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>1646</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>1647</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>1648</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>1649</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>1650</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>1651</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>1652</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>1653</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>1654</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>1655</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>1656</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>1657</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>1659</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>1660</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>1661</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>1662</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>1663</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>1664</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>1665</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>1666</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>1667</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>1668</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>1669</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>1670</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>1671</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>1672</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>1673</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>1674</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>1676</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>1677</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>1678</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>1679</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>1681</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
-        <v>1682</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
-        <v>1683</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>1684</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>1685</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>1686</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>1687</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>1688</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>1689</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>1691</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>1692</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
-        <v>1694</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
-        <v>1695</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
-        <v>1696</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
-        <v>1697</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
-        <v>1698</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
-        <v>1699</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
-        <v>1701</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
-        <v>1702</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
-        <v>1703</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
-        <v>1704</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="s">
-        <v>1705</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
-        <v>1706</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
-        <v>1707</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
-        <v>1708</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
-        <v>1709</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
-        <v>1711</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
-        <v>1712</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="s">
-        <v>1713</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
-        <v>1714</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="s">
-        <v>1715</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="s">
-        <v>1716</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="s">
-        <v>1717</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="s">
-        <v>1718</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6" t="s">
-        <v>1719</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6" t="s">
-        <v>1720</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6" t="s">
-        <v>1721</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6" t="s">
-        <v>1722</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="6" t="s">
-        <v>1723</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="6" t="s">
-        <v>1724</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6" t="s">
-        <v>1725</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6" t="s">
-        <v>1726</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="6" t="s">
-        <v>1727</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6" t="s">
-        <v>1728</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="6" t="s">
-        <v>1729</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6" t="s">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="6" t="s">
-        <v>1731</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="G1:J1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
@@ -15680,43 +15111,488 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="37.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="37.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="17.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="35.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="35.19"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>1732</v>
-      </c>
+      <c r="A1" s="52" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="G1" s="13" t="s">
+        <v>1641</v>
+      </c>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1733</v>
+        <v>1642</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D2" s="54"/>
+      <c r="E2" s="55"/>
+      <c r="G2" s="53" t="s">
+        <v>461</v>
+      </c>
+      <c r="H2" s="53" t="s">
+        <v>1644</v>
+      </c>
+      <c r="I2" s="53" t="s">
+        <v>456</v>
+      </c>
+      <c r="J2" s="53" t="s">
+        <v>1645</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1734</v>
+        <v>1646</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E3" s="56"/>
+      <c r="G3" s="1" t="s">
+        <v>1648</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>1649</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>1650</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1735</v>
+        <v>1651</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>1652</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>1654</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>1656</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1736</v>
+        <v>1657</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>1658</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="6" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="6" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="6" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="6" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="6" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="6" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="6" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="6" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="6" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="6" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="6" t="s">
         <v>1737</v>
       </c>
     </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="6" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="G1:J1"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -15732,6 +15608,58 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="37.57"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:K150"/>
   <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -15741,27 +15669,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1738</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1739</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="56" t="s">
-        <v>1740</v>
-      </c>
-      <c r="B4" s="57" t="s">
-        <v>1741</v>
+      <c r="A4" s="57" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B4" s="58" t="s">
+        <v>1748</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="B5" s="58" t="n">
+      <c r="B5" s="59" t="n">
         <f aca="false">ROUNDDOWN((A5-50)/5,0)</f>
         <v>-10</v>
       </c>
@@ -15770,7 +15698,7 @@
       <c r="A6" s="35" t="n">
         <v>25</v>
       </c>
-      <c r="B6" s="58" t="n">
+      <c r="B6" s="59" t="n">
         <f aca="false">ROUNDDOWN((A6-50)/5,0)</f>
         <v>-5</v>
       </c>
@@ -15779,7 +15707,7 @@
       <c r="A7" s="35" t="n">
         <v>50</v>
       </c>
-      <c r="B7" s="58" t="n">
+      <c r="B7" s="59" t="n">
         <f aca="false">ROUNDDOWN((A7-50)/5,0)</f>
         <v>0</v>
       </c>
@@ -15788,7 +15716,7 @@
       <c r="A8" s="35" t="n">
         <v>75</v>
       </c>
-      <c r="B8" s="58" t="n">
+      <c r="B8" s="59" t="n">
         <f aca="false">ROUNDDOWN((A8-50)/5,0)</f>
         <v>5</v>
       </c>
@@ -15797,7 +15725,7 @@
       <c r="A9" s="35" t="n">
         <v>100</v>
       </c>
-      <c r="B9" s="58" t="n">
+      <c r="B9" s="59" t="n">
         <f aca="false">ROUNDDOWN((A9-50)/5,0)</f>
         <v>10</v>
       </c>
@@ -15806,57 +15734,57 @@
       <c r="A10" s="35" t="n">
         <v>125</v>
       </c>
-      <c r="B10" s="58" t="n">
+      <c r="B10" s="59" t="n">
         <f aca="false">ROUNDDOWN((A10-50)/5,0)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="41" t="n">
         <v>150</v>
       </c>
-      <c r="B11" s="59" t="n">
+      <c r="B11" s="60" t="n">
         <f aca="false">ROUNDDOWN((A11-50)/5,0)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1742</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>1743</v>
+        <v>1750</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>1744</v>
+        <v>1751</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>1745</v>
+        <v>1752</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>1746</v>
+        <v>1753</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>1747</v>
+        <v>1754</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>1748</v>
+        <v>1755</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>1749</v>
+        <v>1756</v>
       </c>
       <c r="H15" s="43" t="s">
-        <v>1750</v>
+        <v>1757</v>
       </c>
       <c r="I15" s="29" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="61" t="s">
         <v>1751</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="60" t="s">
-        <v>1744</v>
       </c>
       <c r="B16" s="44" t="n">
         <v>0</v>
@@ -15884,8 +15812,8 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="60" t="s">
-        <v>1745</v>
+      <c r="A17" s="61" t="s">
+        <v>1752</v>
       </c>
       <c r="B17" s="44" t="n">
         <v>125</v>
@@ -15913,8 +15841,8 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="60" t="s">
-        <v>1746</v>
+      <c r="A18" s="61" t="s">
+        <v>1753</v>
       </c>
       <c r="B18" s="44" t="n">
         <v>100</v>
@@ -15942,8 +15870,8 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="60" t="s">
-        <v>1747</v>
+      <c r="A19" s="61" t="s">
+        <v>1754</v>
       </c>
       <c r="B19" s="44" t="n">
         <v>100</v>
@@ -15971,8 +15899,8 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="60" t="s">
-        <v>1748</v>
+      <c r="A20" s="61" t="s">
+        <v>1755</v>
       </c>
       <c r="B20" s="44" t="n">
         <v>75</v>
@@ -15999,9 +15927,9 @@
         <v>150</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="60" t="s">
-        <v>1749</v>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="61" t="s">
+        <v>1756</v>
       </c>
       <c r="B21" s="44" t="n">
         <v>75</v>
@@ -16029,8 +15957,8 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="60" t="s">
-        <v>1750</v>
+      <c r="A22" s="61" t="s">
+        <v>1757</v>
       </c>
       <c r="B22" s="44" t="n">
         <v>75</v>
@@ -16057,9 +15985,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="61" t="s">
-        <v>1751</v>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="62" t="s">
+        <v>1758</v>
       </c>
       <c r="B23" s="46" t="n">
         <v>75</v>
@@ -16088,917 +16016,917 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1752</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1753</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1754</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1755</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="62" t="s">
+      <c r="A32" s="63" t="s">
         <v>461</v>
       </c>
-      <c r="B32" s="62" t="s">
-        <v>1756</v>
-      </c>
-      <c r="C32" s="63" t="s">
-        <v>1757</v>
-      </c>
-      <c r="D32" s="63"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="63"/>
-      <c r="H32" s="63"/>
+      <c r="B32" s="63" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C32" s="64" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D32" s="64"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="44" t="s">
-        <v>1758</v>
+        <v>1765</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C33" s="64" t="s">
-        <v>1760</v>
-      </c>
-      <c r="D33" s="64"/>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
+        <v>1766</v>
+      </c>
+      <c r="C33" s="65" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="65"/>
+      <c r="H33" s="65"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="44" t="s">
-        <v>1761</v>
+        <v>1768</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C34" s="64" t="s">
-        <v>1760</v>
-      </c>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
+        <v>1766</v>
+      </c>
+      <c r="C34" s="65" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="65"/>
+      <c r="H34" s="65"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="44" t="s">
-        <v>1762</v>
+        <v>1769</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C35" s="64" t="s">
-        <v>1760</v>
-      </c>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
+        <v>1766</v>
+      </c>
+      <c r="C35" s="65" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="44" t="s">
-        <v>1763</v>
+        <v>1770</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1745</v>
-      </c>
-      <c r="C36" s="65" t="s">
-        <v>1764</v>
-      </c>
-      <c r="D36" s="65"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
+        <v>1752</v>
+      </c>
+      <c r="C36" s="66" t="s">
+        <v>1771</v>
+      </c>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="66"/>
+      <c r="H36" s="66"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="44" t="s">
-        <v>1765</v>
+        <v>1772</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1747</v>
-      </c>
-      <c r="C37" s="64" t="s">
-        <v>1766</v>
-      </c>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64"/>
-      <c r="F37" s="64"/>
-      <c r="G37" s="64"/>
-      <c r="H37" s="64"/>
+        <v>1754</v>
+      </c>
+      <c r="C37" s="65" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="44" t="s">
-        <v>1767</v>
+        <v>1774</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1745</v>
-      </c>
-      <c r="C38" s="64" t="s">
-        <v>1766</v>
-      </c>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="64"/>
-      <c r="H38" s="64"/>
+        <v>1752</v>
+      </c>
+      <c r="C38" s="65" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="44" t="s">
-        <v>1768</v>
+        <v>1775</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1745</v>
-      </c>
-      <c r="C39" s="65" t="s">
-        <v>1764</v>
-      </c>
-      <c r="D39" s="65"/>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="65"/>
+        <v>1752</v>
+      </c>
+      <c r="C39" s="66" t="s">
+        <v>1771</v>
+      </c>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="66"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="44" t="s">
         <v>518</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1745</v>
-      </c>
-      <c r="C40" s="65" t="s">
-        <v>1764</v>
-      </c>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="65"/>
+        <v>1752</v>
+      </c>
+      <c r="C40" s="66" t="s">
+        <v>1771</v>
+      </c>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
+      <c r="H40" s="66"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="44" t="s">
-        <v>1769</v>
+        <v>1776</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1748</v>
-      </c>
-      <c r="C41" s="65" t="s">
-        <v>1770</v>
-      </c>
-      <c r="D41" s="65"/>
-      <c r="E41" s="65"/>
-      <c r="F41" s="65"/>
-      <c r="G41" s="65"/>
-      <c r="H41" s="65"/>
+        <v>1755</v>
+      </c>
+      <c r="C41" s="66" t="s">
+        <v>1777</v>
+      </c>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="66"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="44" t="s">
-        <v>1771</v>
+        <v>1778</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1749</v>
-      </c>
-      <c r="C42" s="65" t="s">
-        <v>1772</v>
-      </c>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="65"/>
+        <v>1756</v>
+      </c>
+      <c r="C42" s="66" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D42" s="66"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="66"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="44" t="s">
-        <v>1773</v>
+        <v>1780</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1750</v>
-      </c>
-      <c r="C43" s="65" t="s">
-        <v>1774</v>
-      </c>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
+        <v>1757</v>
+      </c>
+      <c r="C43" s="66" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="44" t="s">
-        <v>1775</v>
+        <v>1782</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1751</v>
-      </c>
-      <c r="C44" s="65" t="s">
-        <v>1776</v>
-      </c>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="65"/>
-      <c r="H44" s="65"/>
+        <v>1758</v>
+      </c>
+      <c r="C44" s="66" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D44" s="66"/>
+      <c r="E44" s="66"/>
+      <c r="F44" s="66"/>
+      <c r="G44" s="66"/>
+      <c r="H44" s="66"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="66" t="s">
-        <v>1765</v>
-      </c>
-      <c r="B48" s="66"/>
-      <c r="C48" s="66"/>
-      <c r="D48" s="66"/>
-      <c r="E48" s="66"/>
-      <c r="F48" s="66"/>
-      <c r="G48" s="66"/>
-      <c r="H48" s="66"/>
+      <c r="A48" s="67" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B48" s="67"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="67"/>
+      <c r="F48" s="67"/>
+      <c r="G48" s="67"/>
+      <c r="H48" s="67"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>1777</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>1778</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="66" t="s">
-        <v>1767</v>
-      </c>
-      <c r="B52" s="66"/>
-      <c r="C52" s="66"/>
-      <c r="D52" s="66"/>
-      <c r="E52" s="66"/>
-      <c r="F52" s="66"/>
-      <c r="G52" s="66"/>
-      <c r="H52" s="66"/>
+      <c r="A52" s="67" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B52" s="67"/>
+      <c r="C52" s="67"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="67"/>
+      <c r="G52" s="67"/>
+      <c r="H52" s="67"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>1779</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="66" t="s">
-        <v>1780</v>
-      </c>
-      <c r="B57" s="66"/>
-      <c r="C57" s="66"/>
-      <c r="D57" s="66"/>
-      <c r="E57" s="66"/>
-      <c r="F57" s="66"/>
-      <c r="G57" s="66"/>
-      <c r="H57" s="66"/>
+      <c r="A57" s="67" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B57" s="67"/>
+      <c r="C57" s="67"/>
+      <c r="D57" s="67"/>
+      <c r="E57" s="67"/>
+      <c r="F57" s="67"/>
+      <c r="G57" s="67"/>
+      <c r="H57" s="67"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>1781</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>1782</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>1783</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>1784</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>1785</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1786</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>1787</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>1788</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="67" t="s">
-        <v>1789</v>
+      <c r="A67" s="68" t="s">
+        <v>1796</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="67" t="s">
-        <v>1790</v>
+      <c r="A68" s="68" t="s">
+        <v>1797</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="67" t="s">
-        <v>1791</v>
+      <c r="A69" s="68" t="s">
+        <v>1798</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>1792</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>1793</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H73" s="66" t="s">
-        <v>1794</v>
-      </c>
-      <c r="I73" s="66"/>
-      <c r="J73" s="66"/>
-      <c r="K73" s="66"/>
+      <c r="H73" s="67" t="s">
+        <v>1801</v>
+      </c>
+      <c r="I73" s="67"/>
+      <c r="J73" s="67"/>
+      <c r="K73" s="67"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="67" t="s">
-        <v>1795</v>
+      <c r="A74" s="68" t="s">
+        <v>1802</v>
       </c>
       <c r="H74" s="6" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="68" t="s">
         <v>1796</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="67" t="s">
-        <v>1789</v>
-      </c>
       <c r="H75" s="6" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="68" t="s">
         <v>1797</v>
       </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="67" t="s">
-        <v>1790</v>
-      </c>
       <c r="H76" s="6" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="68" t="s">
         <v>1798</v>
       </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="67" t="s">
-        <v>1791</v>
-      </c>
       <c r="C77" s="6" t="s">
-        <v>1799</v>
+        <v>1806</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>1800</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="67" t="s">
-        <v>1801</v>
+      <c r="A78" s="68" t="s">
+        <v>1808</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>1802</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="67" t="s">
-        <v>1803</v>
+      <c r="A79" s="68" t="s">
+        <v>1810</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>1804</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="67" t="s">
-        <v>1805</v>
+      <c r="A80" s="68" t="s">
+        <v>1812</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>1806</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="67" t="s">
-        <v>1807</v>
+      <c r="A81" s="68" t="s">
+        <v>1814</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>1808</v>
+        <v>1815</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>1809</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="67" t="s">
-        <v>1803</v>
+      <c r="A82" s="68" t="s">
+        <v>1810</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>1804</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="67" t="s">
-        <v>1810</v>
+      <c r="A83" s="68" t="s">
+        <v>1817</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>1806</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="67" t="s">
-        <v>1811</v>
+      <c r="A84" s="68" t="s">
+        <v>1818</v>
       </c>
       <c r="H84" s="6" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="68" t="s">
+        <v>1820</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="68" t="s">
+        <v>1822</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="68" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>1825</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="68" t="s">
+        <v>1827</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="68" t="s">
+        <v>1829</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="68" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>1832</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="68" t="s">
+        <v>1834</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="68" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>1837</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="68" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>1840</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="68" t="s">
+        <v>1842</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="68" t="s">
+        <v>1844</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="68" t="s">
+        <v>1846</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="68" t="s">
+        <v>1848</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="68" t="s">
+        <v>1850</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="68" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>1853</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="68" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>1856</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="68" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>1859</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="68" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>1862</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="68" t="s">
+        <v>1863</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="68" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>1866</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="68" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="68" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>1872</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="68" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>1875</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="68" t="s">
+        <v>1877</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="68" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="68" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="68" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="68" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="68" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="68" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="68" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="68" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="68" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="68" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="68" t="s">
         <v>1812</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="67" t="s">
-        <v>1813</v>
-      </c>
-      <c r="H85" s="6" t="s">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="68" t="s">
         <v>1814</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="67" t="s">
-        <v>1815</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>1816</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="67" t="s">
+      <c r="C122" s="6" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="68" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="68" t="s">
         <v>1817</v>
       </c>
-      <c r="C87" s="6" t="s">
-        <v>1818</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>1819</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="67" t="s">
-        <v>1820</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="67" t="s">
-        <v>1822</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>1823</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="67" t="s">
-        <v>1824</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>1825</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>1826</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="67" t="s">
-        <v>1827</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>1828</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="67" t="s">
-        <v>1829</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>1830</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="67" t="s">
-        <v>1832</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>1833</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>1834</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="67" t="s">
-        <v>1835</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>1836</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="67" t="s">
-        <v>1837</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>1838</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="67" t="s">
-        <v>1839</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>1840</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="67" t="s">
-        <v>1841</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>1842</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="67" t="s">
-        <v>1843</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>1844</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="67" t="s">
-        <v>1845</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>1846</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>1847</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="67" t="s">
-        <v>1848</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>1849</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>1850</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="67" t="s">
-        <v>1851</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>1852</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>1853</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="67" t="s">
-        <v>1854</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>1855</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>1806</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="67" t="s">
-        <v>1856</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>1857</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="67" t="s">
-        <v>1858</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>1859</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>1860</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="67" t="s">
-        <v>1861</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>1862</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="67" t="s">
-        <v>1864</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>1865</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>1866</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="67" t="s">
-        <v>1867</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>1868</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>1869</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="67" t="s">
-        <v>1870</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>1857</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="67" t="s">
-        <v>1871</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>1872</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="67" t="s">
-        <v>1873</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="67" t="s">
-        <v>1874</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="67" t="s">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="67" t="s">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="67" t="s">
-        <v>1877</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="67" t="s">
-        <v>1878</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="67" t="s">
-        <v>1880</v>
-      </c>
-      <c r="C118" s="6" t="s">
+      <c r="C124" s="6" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="68" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="68" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="68" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="68" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="68" t="s">
+        <v>1900</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="68" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="68" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="68" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="68" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="68" t="s">
         <v>1881</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="67" t="s">
-        <v>1882</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>1883</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="67" t="s">
-        <v>1884</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="67" t="s">
-        <v>1805</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="67" t="s">
-        <v>1807</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="67" t="s">
-        <v>1884</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="67" t="s">
-        <v>1810</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>1886</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="67" t="s">
-        <v>1887</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="67" t="s">
-        <v>1878</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="67" t="s">
-        <v>1889</v>
-      </c>
-      <c r="C127" s="6" t="s">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="67" t="s">
-        <v>1891</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>1892</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="67" t="s">
-        <v>1893</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>1894</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="67" t="s">
-        <v>1895</v>
-      </c>
-      <c r="C130" s="6" t="s">
-        <v>1896</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="67" t="s">
-        <v>1897</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="67" t="s">
-        <v>1898</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>1899</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="67" t="s">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="67" t="s">
-        <v>1874</v>
-      </c>
-    </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="67"/>
+      <c r="A135" s="68"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="67"/>
+      <c r="A136" s="68"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="6" t="s">
-        <v>1901</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="67" t="s">
-        <v>1902</v>
+      <c r="A138" s="68" t="s">
+        <v>1909</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>1903</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="67" t="s">
-        <v>1904</v>
+      <c r="A139" s="68" t="s">
+        <v>1911</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>1905</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="67" t="s">
-        <v>1906</v>
+      <c r="A140" s="68" t="s">
+        <v>1913</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="67" t="s">
-        <v>1907</v>
+      <c r="A141" s="68" t="s">
+        <v>1914</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="67" t="s">
-        <v>1908</v>
+      <c r="A142" s="68" t="s">
+        <v>1915</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="67" t="s">
-        <v>1909</v>
+      <c r="A143" s="68" t="s">
+        <v>1916</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="67" t="s">
-        <v>1910</v>
+      <c r="A144" s="68" t="s">
+        <v>1917</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="67" t="s">
-        <v>1911</v>
+      <c r="A145" s="68" t="s">
+        <v>1918</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="67" t="s">
-        <v>1912</v>
+      <c r="A146" s="68" t="s">
+        <v>1919</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="67" t="s">
-        <v>1913</v>
+      <c r="A147" s="68" t="s">
+        <v>1920</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="67" t="s">
-        <v>1914</v>
+      <c r="A148" s="68" t="s">
+        <v>1921</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="67" t="s">
-        <v>1915</v>
+      <c r="A149" s="68" t="s">
+        <v>1922</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="67" t="s">
-        <v>1874</v>
+      <c r="A150" s="68" t="s">
+        <v>1881</v>
       </c>
     </row>
   </sheetData>
@@ -17031,126 +16959,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="33.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="14.69"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="66" t="s">
-        <v>1916</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="68" t="s">
-        <v>808</v>
-      </c>
-      <c r="B2" s="68" t="s">
-        <v>462</v>
-      </c>
-      <c r="C2" s="68" t="s">
-        <v>461</v>
-      </c>
-      <c r="D2" s="68" t="s">
-        <v>1917</v>
-      </c>
-      <c r="E2" s="68" t="s">
-        <v>1918</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="44" t="n">
-        <v>464</v>
-      </c>
-      <c r="B3" s="68" t="s">
-        <v>958</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>1919</v>
-      </c>
-      <c r="D3" s="44" t="n">
-        <v>7</v>
-      </c>
-      <c r="E3" s="44" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="44" t="n">
-        <v>465</v>
-      </c>
-      <c r="B4" s="68" t="s">
-        <v>963</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>1920</v>
-      </c>
-      <c r="D4" s="69" t="s">
-        <v>1921</v>
-      </c>
-      <c r="E4" s="44" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="70" t="n">
-        <v>466</v>
-      </c>
-      <c r="B5" s="71" t="s">
-        <v>963</v>
-      </c>
-      <c r="C5" s="70" t="s">
-        <v>1922</v>
-      </c>
-      <c r="D5" s="69" t="s">
-        <v>1921</v>
-      </c>
-      <c r="E5" s="70" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="70" t="n">
-        <v>467</v>
-      </c>
-      <c r="B6" s="71" t="s">
-        <v>958</v>
-      </c>
-      <c r="C6" s="70" t="s">
-        <v>1923</v>
-      </c>
-      <c r="D6" s="72" t="s">
-        <v>1924</v>
-      </c>
-      <c r="E6" s="70" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -17216,57 +17024,177 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="33.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="14.69"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="67" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="69" t="s">
+        <v>808</v>
+      </c>
+      <c r="B2" s="69" t="s">
+        <v>462</v>
+      </c>
+      <c r="C2" s="69" t="s">
+        <v>461</v>
+      </c>
+      <c r="D2" s="69" t="s">
+        <v>1924</v>
+      </c>
+      <c r="E2" s="69" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="44" t="n">
+        <v>464</v>
+      </c>
+      <c r="B3" s="69" t="s">
+        <v>958</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>1925</v>
+      </c>
+      <c r="D3" s="44" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="44" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="44" t="n">
+        <v>465</v>
+      </c>
+      <c r="B4" s="69" t="s">
+        <v>963</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>1926</v>
+      </c>
+      <c r="D4" s="70" t="s">
+        <v>1927</v>
+      </c>
+      <c r="E4" s="44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="71" t="n">
+        <v>466</v>
+      </c>
+      <c r="B5" s="72" t="s">
+        <v>963</v>
+      </c>
+      <c r="C5" s="71" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D5" s="70" t="s">
+        <v>1927</v>
+      </c>
+      <c r="E5" s="71" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="71" t="n">
+        <v>467</v>
+      </c>
+      <c r="B6" s="72" t="s">
+        <v>958</v>
+      </c>
+      <c r="C6" s="71" t="s">
+        <v>1929</v>
+      </c>
+      <c r="D6" s="73" t="s">
+        <v>1930</v>
+      </c>
+      <c r="E6" s="71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:A10"/>
   <sheetFormatPr defaultColWidth="12.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1925</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1926</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1928</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1929</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1930</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1931</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1932</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1933</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1934</v>
+        <v>1940</v>
       </c>
     </row>
   </sheetData>
@@ -17280,7 +17208,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -17289,45 +17217,45 @@
   <sheetFormatPr defaultColWidth="12.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="73" t="s">
-        <v>1935</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73" t="s">
-        <v>1936</v>
-      </c>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73" t="s">
-        <v>1937</v>
-      </c>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
+      <c r="A1" s="74" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74" t="s">
+        <v>1943</v>
+      </c>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="n">
         <v>24</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1938</v>
+        <v>1944</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>21</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1939</v>
+        <v>1945</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1940</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17335,10 +17263,10 @@
         <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1941</v>
+        <v>1947</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1942</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17346,10 +17274,10 @@
         <v>23</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1943</v>
+        <v>1949</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1944</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17357,35 +17285,35 @@
         <v>24</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1945</v>
+        <v>1951</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1946</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I6" s="6" t="s">
-        <v>1947</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I7" s="6" t="s">
-        <v>1948</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I8" s="6" t="s">
-        <v>1949</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I9" s="6" t="s">
-        <v>1950</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I10" s="6" t="s">
-        <v>1951</v>
+        <v>1957</v>
       </c>
     </row>
   </sheetData>
@@ -17404,7 +17332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -17417,28 +17345,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>1953</v>
+        <v>1959</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>1954</v>
+        <v>1960</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>1447</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>1955</v>
+        <v>1961</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>1956</v>
+        <v>1962</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>1957</v>
+        <v>1963</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17692,7 +17620,7 @@
         <v>164</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1959</v>
+        <v>1965</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>95</v>
@@ -17709,7 +17637,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
@@ -17735,7 +17663,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
@@ -17773,10 +17701,10 @@
         <f aca="false">C14+B15</f>
         <v>559</v>
       </c>
-      <c r="G15" s="74" t="s">
-        <v>1960</v>
-      </c>
-      <c r="H15" s="75" t="n">
+      <c r="G15" s="75" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H15" s="76" t="n">
         <v>45</v>
       </c>
     </row>
@@ -17792,7 +17720,7 @@
         <f aca="false">C15+B16</f>
         <v>679</v>
       </c>
-      <c r="H16" s="76"/>
+      <c r="H16" s="77"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="n">
@@ -17846,10 +17774,10 @@
         <v>1329</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="n">
         <v>20</v>
       </c>
@@ -17875,13 +17803,13 @@
         <v>1770</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1962</v>
-      </c>
-      <c r="H22" s="77" t="s">
+        <v>1968</v>
+      </c>
+      <c r="H22" s="78" t="s">
         <v>1462</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="n">
         <v>22</v>
       </c>
@@ -17894,9 +17822,9 @@
         <v>2023</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>1963</v>
-      </c>
-      <c r="H23" s="77" t="n">
+        <v>1969</v>
+      </c>
+      <c r="H23" s="78" t="n">
         <f aca="false">J4</f>
         <v>1864610</v>
       </c>
@@ -17914,7 +17842,7 @@
         <v>2299</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>1964</v>
+        <v>1970</v>
       </c>
       <c r="H24" s="6" t="e">
         <f aca="false">levelfromexp(H23,VLOOKUP(H22,G2:H10,2,0))</f>
@@ -18275,73 +18203,6 @@
     </row>
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffSeite &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>854</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1965</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>838</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>1966</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>1967</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>1968</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>1969</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>1971</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>1973</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -18361,51 +18222,51 @@
   <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="n">
-        <v>103</v>
+      <c r="A1" s="6" t="s">
+        <v>854</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>1975</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="n">
-        <v>104</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="B4" s="6" t="s">
         <v>1976</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
-        <v>106</v>
-      </c>
-      <c r="B4" s="6" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>1977</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
-        <v>107</v>
-      </c>
       <c r="B5" s="6" t="s">
-        <v>1132</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1978</v>
+      <c r="A6" s="6" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>1980</v>
       </c>
     </row>
   </sheetData>
@@ -18425,6 +18286,73 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="12.0390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffSeite &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18432,7 +18360,7 @@
         <v>808</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1979</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18440,7 +18368,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1980</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18456,7 +18384,7 @@
         <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1981</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18464,7 +18392,7 @@
         <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1982</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18472,7 +18400,7 @@
         <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1983</v>
+        <v>1989</v>
       </c>
     </row>
   </sheetData>
@@ -18486,7 +18414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -18499,7 +18427,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1984</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18510,7 +18438,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1985</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18521,29 +18449,29 @@
         <v>20</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1986</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1987</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1988</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>1984</v>
+        <v>1990</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1989</v>
+        <v>1995</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1990</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18570,7 +18498,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1991</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18589,7 +18517,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1992</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18597,21 +18525,21 @@
         <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1993</v>
+        <v>1999</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="n">
         <v>37</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1993</v>
+        <v>1999</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1994</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18619,13 +18547,13 @@
         <v>45</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1993</v>
+        <v>1999</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="n">
         <v>10</v>
       </c>
@@ -18633,7 +18561,7 @@
         <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1995</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18646,7 +18574,7 @@
         <v>470</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1996</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18657,7 +18585,7 @@
         <v>33.34</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>1997</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18681,7 +18609,7 @@
         <v>457</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>1998</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18689,7 +18617,7 @@
         <v>472</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>1999</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18740,7 +18668,7 @@
         <v>0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>2000</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18756,12 +18684,12 @@
         <v>374</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>2001</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18774,7 +18702,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>1100</v>
@@ -18787,7 +18715,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>2004</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18828,7 +18756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -18840,13 +18768,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="78" t="s">
-        <v>2005</v>
-      </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
+      <c r="A1" s="79" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
       <c r="E1" s="14" t="s">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="F1" s="14"/>
       <c r="G1" s="14"/>
@@ -18854,30 +18782,30 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2009</v>
-      </c>
-      <c r="E2" s="79" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E2" s="80" t="s">
         <v>461</v>
       </c>
-      <c r="F2" s="79" t="s">
-        <v>2010</v>
-      </c>
-      <c r="G2" s="79" t="s">
-        <v>2011</v>
-      </c>
-      <c r="H2" s="79" t="s">
-        <v>2012</v>
+      <c r="F2" s="80" t="s">
+        <v>2016</v>
+      </c>
+      <c r="G2" s="80" t="s">
+        <v>2017</v>
+      </c>
+      <c r="H2" s="80" t="s">
+        <v>2018</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>1</v>
@@ -18885,22 +18813,22 @@
       <c r="C3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="70" t="s">
-        <v>2013</v>
-      </c>
-      <c r="F3" s="70" t="n">
+      <c r="E3" s="71" t="s">
+        <v>2019</v>
+      </c>
+      <c r="F3" s="71" t="n">
         <v>5</v>
       </c>
-      <c r="G3" s="70" t="n">
+      <c r="G3" s="71" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="70" t="n">
+      <c r="H3" s="71" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>6</v>
@@ -18908,14 +18836,14 @@
       <c r="C4" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>5</v>
@@ -18923,14 +18851,14 @@
       <c r="C5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>3</v>
@@ -18938,14 +18866,14 @@
       <c r="C6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>2</v>
@@ -18953,14 +18881,14 @@
       <c r="C7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>0</v>
@@ -18968,25 +18896,25 @@
       <c r="C8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="80" t="s">
-        <v>2016</v>
-      </c>
-      <c r="F8" s="80" t="n">
+      <c r="E8" s="81" t="s">
+        <v>2022</v>
+      </c>
+      <c r="F8" s="81" t="n">
         <f aca="false">SUM(F3:F7)</f>
         <v>5</v>
       </c>
-      <c r="G8" s="80" t="n">
+      <c r="G8" s="81" t="n">
         <f aca="false">SUM(G3:G7)</f>
         <v>5</v>
       </c>
-      <c r="H8" s="80" t="n">
+      <c r="H8" s="81" t="n">
         <f aca="false">SUM(H3:H7)</f>
         <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="B9" s="6" t="n">
         <v>5</v>
@@ -18997,7 +18925,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1740</v>
+        <v>1747</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>5</v>
@@ -19006,9 +18934,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>20</v>
@@ -19016,16 +18944,16 @@
       <c r="C11" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E11" s="80" t="s">
-        <v>2019</v>
-      </c>
-      <c r="F11" s="80" t="n">
+      <c r="E11" s="81" t="s">
+        <v>2025</v>
+      </c>
+      <c r="F11" s="81" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="B12" s="6" t="n">
         <v>135</v>
@@ -19033,16 +18961,16 @@
       <c r="C12" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="E12" s="80" t="s">
-        <v>2021</v>
-      </c>
-      <c r="F12" s="80" t="n">
+      <c r="E12" s="81" t="s">
+        <v>2027</v>
+      </c>
+      <c r="F12" s="81" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>2022</v>
+        <v>2028</v>
       </c>
       <c r="B13" s="6" t="n">
         <v>2</v>
@@ -19053,7 +18981,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>2023</v>
+        <v>2029</v>
       </c>
       <c r="B14" s="6" t="n">
         <v>5</v>
@@ -19064,7 +18992,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="B15" s="6" t="n">
         <v>15</v>
@@ -19075,7 +19003,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>2025</v>
+        <v>2031</v>
       </c>
       <c r="B16" s="6" t="n">
         <v>0</v>
@@ -19086,7 +19014,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>2026</v>
+        <v>2032</v>
       </c>
       <c r="B17" s="6" t="n">
         <v>30</v>
@@ -19095,7 +19023,7 @@
         <v>85</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>2027</v>
+        <v>2033</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
@@ -19103,7 +19031,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>2028</v>
+        <v>2034</v>
       </c>
       <c r="B18" s="6" t="n">
         <v>0</v>
@@ -19111,22 +19039,22 @@
       <c r="C18" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E18" s="79" t="s">
-        <v>2007</v>
-      </c>
-      <c r="F18" s="79" t="s">
-        <v>2008</v>
-      </c>
-      <c r="G18" s="79" t="s">
-        <v>2009</v>
-      </c>
-      <c r="H18" s="79" t="s">
-        <v>2029</v>
+      <c r="E18" s="80" t="s">
+        <v>2013</v>
+      </c>
+      <c r="F18" s="80" t="s">
+        <v>2014</v>
+      </c>
+      <c r="G18" s="80" t="s">
+        <v>2015</v>
+      </c>
+      <c r="H18" s="80" t="s">
+        <v>2035</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>2030</v>
+        <v>2036</v>
       </c>
       <c r="B19" s="6" t="n">
         <v>0</v>
@@ -19134,25 +19062,25 @@
       <c r="C19" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="E19" s="70" t="s">
-        <v>1952</v>
-      </c>
-      <c r="F19" s="70" t="n">
+      <c r="E19" s="71" t="s">
+        <v>1958</v>
+      </c>
+      <c r="F19" s="71" t="n">
         <f aca="false">C3+C26+C34+C41+C48+C55+C63+C70+C77</f>
         <v>33</v>
       </c>
-      <c r="G19" s="80" t="n">
+      <c r="G19" s="81" t="n">
         <f aca="false">F19</f>
         <v>33</v>
       </c>
-      <c r="H19" s="70" t="n">
+      <c r="H19" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F19:G19),0)</f>
         <v>33</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>2031</v>
+        <v>2037</v>
       </c>
       <c r="B20" s="6" t="n">
         <v>0</v>
@@ -19160,28 +19088,28 @@
       <c r="C20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="70" t="s">
-        <v>2012</v>
-      </c>
-      <c r="F20" s="70" t="n">
+      <c r="E20" s="71" t="s">
+        <v>2018</v>
+      </c>
+      <c r="F20" s="71" t="n">
         <f aca="false">B4+B29+B66+B71+(F19-B3)*(F11/2)</f>
         <v>209</v>
       </c>
-      <c r="G20" s="80" t="n">
+      <c r="G20" s="81" t="n">
         <f aca="false">C4+C29+C66+C71+(G19-C3)*F11+H8</f>
         <v>391</v>
       </c>
-      <c r="H20" s="70" t="n">
+      <c r="H20" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F20:G20),0)</f>
         <v>300</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>2032</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>2033</v>
+        <v>2039</v>
       </c>
       <c r="B21" s="6" t="n">
         <v>20</v>
@@ -19189,25 +19117,25 @@
       <c r="C21" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E21" s="70" t="s">
-        <v>2014</v>
-      </c>
-      <c r="F21" s="70" t="n">
+      <c r="E21" s="71" t="s">
+        <v>2020</v>
+      </c>
+      <c r="F21" s="71" t="n">
         <f aca="false">B5+B30+B81+(F19-B3)*(F12/2)</f>
         <v>147</v>
       </c>
-      <c r="G21" s="80" t="n">
+      <c r="G21" s="81" t="n">
         <f aca="false">B5+B30+B81+(F19-B3)*F12</f>
         <v>259</v>
       </c>
-      <c r="H21" s="70" t="n">
+      <c r="H21" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F21:G21),0)</f>
         <v>203</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>2034</v>
+        <v>2040</v>
       </c>
       <c r="B22" s="6" t="n">
         <v>0</v>
@@ -19215,25 +19143,25 @@
       <c r="C22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="70" t="s">
-        <v>2015</v>
-      </c>
-      <c r="F22" s="70" t="n">
+      <c r="E22" s="71" t="s">
+        <v>2021</v>
+      </c>
+      <c r="F22" s="71" t="n">
         <f aca="false">B6+B37+B50</f>
         <v>5</v>
       </c>
-      <c r="G22" s="80" t="n">
+      <c r="G22" s="81" t="n">
         <f aca="false">F22</f>
         <v>5</v>
       </c>
-      <c r="H22" s="70" t="n">
+      <c r="H22" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F22:G22),0)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>2035</v>
+        <v>2041</v>
       </c>
       <c r="B23" s="6" t="n">
         <v>0</v>
@@ -19241,74 +19169,74 @@
       <c r="C23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="70" t="s">
-        <v>2010</v>
-      </c>
-      <c r="F23" s="70" t="n">
+      <c r="E23" s="71" t="s">
+        <v>2016</v>
+      </c>
+      <c r="F23" s="71" t="n">
         <f aca="false">B7+B36+B56+B65+ROUNDDOWN(F25/25,0)</f>
         <v>20</v>
       </c>
-      <c r="G23" s="80" t="n">
+      <c r="G23" s="81" t="n">
         <f aca="false">C7+C36+C56+C65+F8+ROUNDDOWN(G25/25,0)</f>
         <v>31</v>
       </c>
-      <c r="H23" s="70" t="n">
+      <c r="H23" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F23:G23),0)</f>
         <v>25</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E24" s="70" t="s">
-        <v>2011</v>
-      </c>
-      <c r="F24" s="70" t="n">
+      <c r="E24" s="71" t="s">
+        <v>2017</v>
+      </c>
+      <c r="F24" s="71" t="n">
         <f aca="false">B8+B42+B57+ROUNDDOWN(F29/25,0)</f>
         <v>17</v>
       </c>
-      <c r="G24" s="80" t="n">
+      <c r="G24" s="81" t="n">
         <f aca="false">C8+C42+C57+G8+ROUNDDOWN(G29/25,0)</f>
         <v>27</v>
       </c>
-      <c r="H24" s="70" t="n">
+      <c r="H24" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F24:G24),0)</f>
         <v>22</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>1967</v>
+        <v>1973</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>2009</v>
-      </c>
-      <c r="E25" s="70" t="s">
-        <v>2017</v>
-      </c>
-      <c r="F25" s="70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E25" s="71" t="s">
+        <v>2023</v>
+      </c>
+      <c r="F25" s="71" t="n">
         <f aca="false">B9+B44+B64</f>
         <v>25</v>
       </c>
-      <c r="G25" s="80" t="n">
+      <c r="G25" s="81" t="n">
         <f aca="false">C9+C44+C64</f>
         <v>30</v>
       </c>
-      <c r="H25" s="70" t="n">
+      <c r="H25" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F25:G25),0)</f>
         <v>27</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="B26" s="6" t="n">
         <v>4</v>
@@ -19316,25 +19244,25 @@
       <c r="C26" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="70" t="s">
-        <v>1740</v>
-      </c>
-      <c r="F26" s="70" t="n">
+      <c r="E26" s="71" t="s">
+        <v>1747</v>
+      </c>
+      <c r="F26" s="71" t="n">
         <f aca="false">B10+B78</f>
         <v>15</v>
       </c>
-      <c r="G26" s="80" t="n">
+      <c r="G26" s="81" t="n">
         <f aca="false">C10+C78</f>
         <v>25</v>
       </c>
-      <c r="H26" s="70" t="n">
+      <c r="H26" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F26:G26),0)</f>
         <v>20</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>2022</v>
+        <v>2028</v>
       </c>
       <c r="B27" s="6" t="n">
         <v>10</v>
@@ -19342,25 +19270,25 @@
       <c r="C27" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E27" s="70" t="s">
-        <v>2018</v>
-      </c>
-      <c r="F27" s="70" t="n">
+      <c r="E27" s="71" t="s">
+        <v>2024</v>
+      </c>
+      <c r="F27" s="71" t="n">
         <f aca="false">B11+B79</f>
         <v>30</v>
       </c>
-      <c r="G27" s="80" t="n">
+      <c r="G27" s="81" t="n">
         <f aca="false">C11+C79</f>
         <v>35</v>
       </c>
-      <c r="H27" s="70" t="n">
+      <c r="H27" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F27:G27),0)</f>
         <v>32</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>2030</v>
+        <v>2036</v>
       </c>
       <c r="B28" s="6" t="n">
         <v>20</v>
@@ -19368,25 +19296,25 @@
       <c r="C28" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="E28" s="70" t="s">
-        <v>2020</v>
-      </c>
-      <c r="F28" s="70" t="n">
+      <c r="E28" s="71" t="s">
+        <v>2026</v>
+      </c>
+      <c r="F28" s="71" t="n">
         <f aca="false">B12+B49</f>
         <v>145</v>
       </c>
-      <c r="G28" s="80" t="n">
+      <c r="G28" s="81" t="n">
         <f aca="false">C12+C49</f>
         <v>160</v>
       </c>
-      <c r="H28" s="70" t="n">
+      <c r="H28" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F28:G28),0)</f>
         <v>152</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="B29" s="6" t="n">
         <v>18</v>
@@ -19394,25 +19322,25 @@
       <c r="C29" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="E29" s="70" t="s">
-        <v>2022</v>
-      </c>
-      <c r="F29" s="70" t="n">
+      <c r="E29" s="71" t="s">
+        <v>2028</v>
+      </c>
+      <c r="F29" s="71" t="n">
         <f aca="false">B13+B27+B58</f>
         <v>22</v>
       </c>
-      <c r="G29" s="80" t="n">
+      <c r="G29" s="81" t="n">
         <f aca="false">C13+C27+C58</f>
         <v>30</v>
       </c>
-      <c r="H29" s="70" t="n">
+      <c r="H29" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F29:G29),0)</f>
         <v>26</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="B30" s="6" t="n">
         <v>5</v>
@@ -19420,52 +19348,52 @@
       <c r="C30" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E30" s="70" t="s">
-        <v>2023</v>
-      </c>
-      <c r="F30" s="70" t="n">
+      <c r="E30" s="71" t="s">
+        <v>2029</v>
+      </c>
+      <c r="F30" s="71" t="n">
         <f aca="false">B14+B59+B80</f>
         <v>25</v>
       </c>
-      <c r="G30" s="80" t="n">
+      <c r="G30" s="81" t="n">
         <f aca="false">C14+C59+C80</f>
         <v>70</v>
       </c>
-      <c r="H30" s="70" t="n">
+      <c r="H30" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F30:G30),0)</f>
         <v>47</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E31" s="70" t="s">
-        <v>2024</v>
-      </c>
-      <c r="F31" s="70" t="n">
+      <c r="E31" s="71" t="s">
+        <v>2030</v>
+      </c>
+      <c r="F31" s="71" t="n">
         <f aca="false">B15</f>
         <v>15</v>
       </c>
-      <c r="G31" s="80" t="n">
+      <c r="G31" s="81" t="n">
         <f aca="false">C15</f>
         <v>95</v>
       </c>
-      <c r="H31" s="70" t="n">
+      <c r="H31" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F31:G31),0)</f>
         <v>55</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E32" s="70" t="s">
-        <v>2025</v>
-      </c>
-      <c r="F32" s="70" t="n">
+      <c r="E32" s="71" t="s">
+        <v>2031</v>
+      </c>
+      <c r="F32" s="71" t="n">
         <f aca="false">B16+B35+B43+B51</f>
         <v>15</v>
       </c>
-      <c r="G32" s="80" t="n">
+      <c r="G32" s="81" t="n">
         <f aca="false">C16+C35+C43+C51</f>
         <v>15</v>
       </c>
-      <c r="H32" s="70" t="n">
+      <c r="H32" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F32:G32),0)</f>
         <v>15</v>
       </c>
@@ -19475,28 +19403,28 @@
         <v>838</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>2009</v>
-      </c>
-      <c r="E33" s="70" t="s">
-        <v>2026</v>
-      </c>
-      <c r="F33" s="70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E33" s="71" t="s">
+        <v>2032</v>
+      </c>
+      <c r="F33" s="71" t="n">
         <v>30</v>
       </c>
-      <c r="G33" s="80" t="n">
+      <c r="G33" s="81" t="n">
         <v>85</v>
       </c>
-      <c r="H33" s="70" t="n">
+      <c r="H33" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F33:G33),0)</f>
         <v>57</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="B34" s="6" t="n">
         <v>4</v>
@@ -19504,23 +19432,23 @@
       <c r="C34" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E34" s="70" t="s">
-        <v>2028</v>
-      </c>
-      <c r="F34" s="70" t="n">
+      <c r="E34" s="71" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F34" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="80" t="n">
+      <c r="G34" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="H34" s="70" t="n">
+      <c r="H34" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F34:G34),0)</f>
         <v>12</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>2025</v>
+        <v>2031</v>
       </c>
       <c r="B35" s="6" t="n">
         <v>5</v>
@@ -19528,24 +19456,24 @@
       <c r="C35" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E35" s="70" t="s">
-        <v>2030</v>
-      </c>
-      <c r="F35" s="70" t="n">
+      <c r="E35" s="71" t="s">
+        <v>2036</v>
+      </c>
+      <c r="F35" s="71" t="n">
         <f aca="false">B19+B28</f>
         <v>20</v>
       </c>
-      <c r="G35" s="80" t="n">
+      <c r="G35" s="81" t="n">
         <v>99</v>
       </c>
-      <c r="H35" s="70" t="n">
+      <c r="H35" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F35:G35),0)</f>
         <v>59</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="B36" s="6" t="n">
         <v>4</v>
@@ -19553,24 +19481,24 @@
       <c r="C36" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E36" s="70" t="s">
-        <v>2031</v>
-      </c>
-      <c r="F36" s="70" t="n">
+      <c r="E36" s="71" t="s">
+        <v>2037</v>
+      </c>
+      <c r="F36" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="80" t="n">
+      <c r="G36" s="81" t="n">
         <f aca="false">C20+C82</f>
         <v>5</v>
       </c>
-      <c r="H36" s="70" t="n">
+      <c r="H36" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F36:G36),0)</f>
         <v>2</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="B37" s="6" t="n">
         <v>1</v>
@@ -19578,50 +19506,50 @@
       <c r="C37" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E37" s="70" t="s">
-        <v>2033</v>
-      </c>
-      <c r="F37" s="70" t="n">
+      <c r="E37" s="71" t="s">
+        <v>2039</v>
+      </c>
+      <c r="F37" s="71" t="n">
         <v>20</v>
       </c>
-      <c r="G37" s="80" t="n">
+      <c r="G37" s="81" t="n">
         <v>60</v>
       </c>
-      <c r="H37" s="70" t="n">
+      <c r="H37" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F37:G37),0)</f>
         <v>40</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E38" s="70" t="s">
-        <v>2034</v>
-      </c>
-      <c r="F38" s="70" t="n">
+      <c r="E38" s="71" t="s">
+        <v>2040</v>
+      </c>
+      <c r="F38" s="71" t="n">
         <f aca="false">B22+B45+B60+B84</f>
         <v>3</v>
       </c>
-      <c r="G38" s="80" t="n">
+      <c r="G38" s="81" t="n">
         <f aca="false">F38</f>
         <v>3</v>
       </c>
-      <c r="H38" s="70" t="n">
+      <c r="H38" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F38:G38),0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E39" s="70" t="s">
-        <v>2035</v>
-      </c>
-      <c r="F39" s="70" t="n">
+      <c r="E39" s="71" t="s">
+        <v>2041</v>
+      </c>
+      <c r="F39" s="71" t="n">
         <f aca="false">B23+B67+B72+B83</f>
         <v>3</v>
       </c>
-      <c r="G39" s="80" t="n">
+      <c r="G39" s="81" t="n">
         <f aca="false">F39</f>
         <v>3</v>
       </c>
-      <c r="H39" s="70" t="n">
+      <c r="H39" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F39:G39),0)</f>
         <v>3</v>
       </c>
@@ -19631,15 +19559,15 @@
         <v>854</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>2009</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="B41" s="6" t="n">
         <v>4</v>
@@ -19650,7 +19578,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="B42" s="6" t="n">
         <v>13</v>
@@ -19661,7 +19589,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>2025</v>
+        <v>2031</v>
       </c>
       <c r="B43" s="6" t="n">
         <v>5</v>
@@ -19672,7 +19600,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="B44" s="6" t="n">
         <v>10</v>
@@ -19683,7 +19611,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>2034</v>
+        <v>2040</v>
       </c>
       <c r="B45" s="6" t="n">
         <v>1</v>
@@ -19694,18 +19622,18 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>1969</v>
+        <v>1975</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>2009</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="B48" s="6" t="n">
         <v>4</v>
@@ -19716,7 +19644,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="B49" s="6" t="n">
         <v>10</v>
@@ -19727,7 +19655,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="B50" s="6" t="n">
         <v>1</v>
@@ -19738,7 +19666,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>2025</v>
+        <v>2031</v>
       </c>
       <c r="B51" s="6" t="n">
         <v>5</v>
@@ -19749,18 +19677,18 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>1971</v>
+        <v>1977</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2009</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="B55" s="6" t="n">
         <v>4</v>
@@ -19771,7 +19699,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="B56" s="6" t="n">
         <v>4</v>
@@ -19782,7 +19710,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="B57" s="6" t="n">
         <v>4</v>
@@ -19793,7 +19721,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>2022</v>
+        <v>2028</v>
       </c>
       <c r="B58" s="6" t="n">
         <v>10</v>
@@ -19804,7 +19732,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>2023</v>
+        <v>2029</v>
       </c>
       <c r="B59" s="6" t="n">
         <v>10</v>
@@ -19815,7 +19743,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>2034</v>
+        <v>2040</v>
       </c>
       <c r="B60" s="6" t="n">
         <v>1</v>
@@ -19826,18 +19754,18 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>1973</v>
+        <v>1979</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>2009</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="B63" s="6" t="n">
         <v>4</v>
@@ -19848,7 +19776,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="B64" s="6" t="n">
         <v>10</v>
@@ -19859,7 +19787,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="B65" s="6" t="n">
         <v>9</v>
@@ -19870,7 +19798,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="B66" s="6" t="n">
         <v>10</v>
@@ -19881,7 +19809,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>2035</v>
+        <v>2041</v>
       </c>
       <c r="B67" s="6" t="n">
         <v>1</v>
@@ -19892,18 +19820,18 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>2036</v>
+        <v>2042</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>2009</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="B70" s="6" t="n">
         <v>3</v>
@@ -19914,7 +19842,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="B71" s="6" t="n">
         <v>15</v>
@@ -19925,7 +19853,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>2035</v>
+        <v>2041</v>
       </c>
       <c r="B72" s="6" t="n">
         <v>1</v>
@@ -19936,18 +19864,18 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>2037</v>
+        <v>2043</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>2009</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="B77" s="6" t="n">
         <v>5</v>
@@ -19958,7 +19886,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>1740</v>
+        <v>1747</v>
       </c>
       <c r="B78" s="6" t="n">
         <v>10</v>
@@ -19969,7 +19897,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="B79" s="6" t="n">
         <v>10</v>
@@ -19980,7 +19908,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>2023</v>
+        <v>2029</v>
       </c>
       <c r="B80" s="6" t="n">
         <v>10</v>
@@ -19991,7 +19919,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="B81" s="6" t="n">
         <v>25</v>
@@ -20002,7 +19930,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>2038</v>
+        <v>2044</v>
       </c>
       <c r="B82" s="6" t="n">
         <v>5</v>
@@ -20013,7 +19941,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>2035</v>
+        <v>2041</v>
       </c>
       <c r="B83" s="6" t="n">
         <v>1</v>
@@ -20024,7 +19952,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>2034</v>
+        <v>2040</v>
       </c>
       <c r="B84" s="6" t="n">
         <v>1</v>
@@ -20049,7 +19977,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -20059,170 +19987,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2039</v>
+        <v>2045</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2040</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>2041</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>2042</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2043</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2044</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2045</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>2046</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>2047</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>2048</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>2049</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.67"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>2050</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2052</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>963</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>2053</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2054</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>963</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1" t="s">
         <v>2055</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>2056</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>963</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>2057</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -20706,194 +20520,308 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2056</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>963</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>2063</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:A43"/>
   <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2058</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2060</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2061</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2062</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>2063</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>2064</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>2065</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>2066</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>2067</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>2068</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>2069</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>2070</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>2071</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>2072</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>2073</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>2074</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>2075</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>2076</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>2077</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>2078</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>2079</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>2080</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>2081</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>2082</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>2083</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>2084</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>2085</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>2086</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>2087</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>2088</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>2089</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>2090</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>2091</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>2092</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>2093</v>
+        <v>2099</v>
       </c>
     </row>
   </sheetData>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="20"/>
   </bookViews>
   <sheets>
     <sheet name="Neue Daten Ep3" sheetId="1" state="visible" r:id="rId3"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="2105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2920" uniqueCount="2108">
   <si>
     <t xml:space="preserve">Map texts</t>
   </si>
@@ -4878,6 +4878,12 @@
     <t xml:space="preserve">Small robot</t>
   </si>
   <si>
+    <t xml:space="preserve">Pulsating light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">346 clean without the metal part and red</t>
+  </si>
+  <si>
     <t xml:space="preserve">Manyeyes’ castle door</t>
   </si>
   <si>
@@ -4945,6 +4951,9 @@
   </si>
   <si>
     <t xml:space="preserve">Ancient city pillars (4 next to each other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancient city door dark</t>
   </si>
   <si>
     <t xml:space="preserve">Pillar left</t>
@@ -13249,13 +13258,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultColWidth="11.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="30.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="44.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13901,6 +13910,23 @@
       </c>
       <c r="D39" s="6" t="s">
         <v>1507</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="n">
+        <v>408</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>1563</v>
       </c>
     </row>
   </sheetData>
@@ -13919,7 +13945,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="12.31640625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="67.86"/>
@@ -13945,13 +13971,13 @@
         <v>173</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13959,13 +13985,13 @@
         <v>174</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>1049</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13973,13 +13999,13 @@
         <v>175</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>1049</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13987,13 +14013,13 @@
         <v>176</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>1051</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14001,13 +14027,13 @@
         <v>177</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>1051</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14015,13 +14041,13 @@
         <v>178</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14029,13 +14055,13 @@
         <v>179</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1060</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14043,13 +14069,13 @@
         <v>180</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>1060</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14057,13 +14083,13 @@
         <v>181</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>1060</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14071,13 +14097,13 @@
         <v>182</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>1060</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14085,13 +14111,13 @@
         <v>183</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>1060</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14099,13 +14125,13 @@
         <v>184</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>1062</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14113,13 +14139,13 @@
         <v>185</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>1062</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14127,13 +14153,13 @@
         <v>186</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>1062</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14141,13 +14167,13 @@
         <v>187</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>1065</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14155,13 +14181,13 @@
         <v>188</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>1065</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14169,13 +14195,13 @@
         <v>189</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>1065</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14183,13 +14209,13 @@
         <v>190</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>1559</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14197,13 +14223,27 @@
         <v>191</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>1559</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1564</v>
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <v>192</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>1566</v>
       </c>
     </row>
   </sheetData>
@@ -14249,13 +14289,13 @@
         <v>92</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>1043</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14263,13 +14303,13 @@
         <v>93</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1587</v>
+        <v>1590</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>1043</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14277,13 +14317,13 @@
         <v>94</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1588</v>
+        <v>1591</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>1043</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14291,13 +14331,13 @@
         <v>95</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1589</v>
+        <v>1592</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1590</v>
+        <v>1593</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14305,13 +14345,13 @@
         <v>96</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1592</v>
+        <v>1595</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1593</v>
+        <v>1596</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14319,13 +14359,13 @@
         <v>97</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>1594</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>1593</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>1591</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14333,13 +14373,13 @@
         <v>98</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1595</v>
+        <v>1598</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1049</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14347,13 +14387,13 @@
         <v>99</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1597</v>
+        <v>1600</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14361,13 +14401,13 @@
         <v>100</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1598</v>
+        <v>1601</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1597</v>
+        <v>1600</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14375,13 +14415,13 @@
         <v>101</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1597</v>
+        <v>1600</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14389,13 +14429,13 @@
         <v>102</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14403,13 +14443,13 @@
         <v>103</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>1057</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14417,13 +14457,13 @@
         <v>104</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>1057</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14431,13 +14471,13 @@
         <v>105</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>1057</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14445,13 +14485,13 @@
         <v>106</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1604</v>
+        <v>1607</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>1057</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14459,13 +14499,13 @@
         <v>107</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>1057</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14473,13 +14513,13 @@
         <v>108</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1606</v>
+        <v>1609</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>1057</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14487,13 +14527,13 @@
         <v>109</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>1060</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14501,13 +14541,13 @@
         <v>110</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>1060</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14515,13 +14555,13 @@
         <v>111</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>1062</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14529,13 +14569,13 @@
         <v>112</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>1062</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14543,13 +14583,13 @@
         <v>113</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>1062</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14557,13 +14597,13 @@
         <v>114</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>1062</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14571,13 +14611,13 @@
         <v>115</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>1062</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14585,13 +14625,13 @@
         <v>116</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>1062</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14599,13 +14639,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>1062</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14613,13 +14653,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>1062</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14627,13 +14667,13 @@
         <v>119</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>1617</v>
+        <v>1620</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>1062</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14641,13 +14681,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>1065</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14655,13 +14695,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>1065</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14669,13 +14709,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>1065</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14683,13 +14723,13 @@
         <v>123</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>1065</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14697,13 +14737,13 @@
         <v>124</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>1622</v>
+        <v>1625</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>1559</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14711,13 +14751,13 @@
         <v>125</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>1559</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14725,13 +14765,13 @@
         <v>126</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>1624</v>
+        <v>1627</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>1559</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14739,13 +14779,13 @@
         <v>127</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>1625</v>
+        <v>1628</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>1559</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14753,13 +14793,13 @@
         <v>128</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>1559</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14767,13 +14807,13 @@
         <v>129</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>1559</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
   </sheetData>
@@ -14797,7 +14837,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14805,7 +14845,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14813,7 +14853,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14821,7 +14861,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
     </row>
   </sheetData>
@@ -14849,7 +14889,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="B1" s="0"/>
       <c r="D1" s="0"/>
@@ -14866,13 +14906,13 @@
         <v>458</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1634</v>
+        <v>1637</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14880,7 +14920,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1636</v>
+        <v>1639</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>382</v>
@@ -14897,7 +14937,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1637</v>
+        <v>1640</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>382</v>
@@ -14914,13 +14954,13 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1638</v>
+        <v>1641</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>481</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>56</v>
@@ -14951,19 +14991,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>1640</v>
+        <v>1643</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
       <c r="G1" s="13" t="s">
-        <v>1641</v>
+        <v>1644</v>
       </c>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>462</v>
@@ -14972,7 +15012,7 @@
         <v>458</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>462</v>
@@ -14989,7 +15029,7 @@
         <v>1193</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>4</v>
@@ -14998,7 +15038,7 @@
         <v>1167</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15009,7 +15049,7 @@
         <v>1194</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>4</v>
@@ -15018,7 +15058,7 @@
         <v>1168</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15029,7 +15069,7 @@
         <v>1195</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>4</v>
@@ -15038,7 +15078,7 @@
         <v>1169</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15049,7 +15089,7 @@
         <v>1196</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>4</v>
@@ -15058,7 +15098,7 @@
         <v>1170</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15069,7 +15109,7 @@
         <v>1197</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>4</v>
@@ -15078,7 +15118,7 @@
         <v>1171</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15089,7 +15129,7 @@
         <v>1198</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>4</v>
@@ -15098,7 +15138,7 @@
         <v>1172</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15109,7 +15149,7 @@
         <v>1199</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>4</v>
@@ -15118,7 +15158,7 @@
         <v>1173</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15129,7 +15169,7 @@
         <v>1200</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>4</v>
@@ -15138,7 +15178,7 @@
         <v>1174</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
     </row>
   </sheetData>
@@ -15173,15 +15213,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="D1" s="13"/>
       <c r="E1" s="13"/>
       <c r="G1" s="13" t="s">
-        <v>1646</v>
+        <v>1649</v>
       </c>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
@@ -15189,10 +15229,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1647</v>
+        <v>1650</v>
       </c>
       <c r="C2" s="52" t="s">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="D2" s="53"/>
       <c r="E2" s="54"/>
@@ -15200,291 +15240,291 @@
         <v>463</v>
       </c>
       <c r="H2" s="52" t="s">
-        <v>1649</v>
+        <v>1652</v>
       </c>
       <c r="I2" s="52" t="s">
         <v>458</v>
       </c>
       <c r="J2" s="52" t="s">
-        <v>1650</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1651</v>
+        <v>1654</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="E3" s="55"/>
       <c r="G3" s="1" t="s">
-        <v>1653</v>
+        <v>1656</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1654</v>
+        <v>1657</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1655</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1656</v>
+        <v>1659</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1658</v>
+        <v>1661</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1664</v>
+        <v>1667</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1669</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1670</v>
+        <v>1673</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1672</v>
+        <v>1675</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>1674</v>
+        <v>1677</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1675</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1676</v>
+        <v>1679</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1677</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1678</v>
+        <v>1681</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1679</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>1680</v>
+        <v>1683</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1681</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1683</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>1684</v>
+        <v>1687</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>1686</v>
+        <v>1689</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1687</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1689</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>1690</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>1692</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>1693</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>1695</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1696</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1698</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1699</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>1701</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>1704</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>1706</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>1707</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>1708</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>1709</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>1710</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>1711</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>1712</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>1714</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15492,147 +15532,147 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>1715</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>1716</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>1717</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>1718</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>1719</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>1720</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>1721</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>1723</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>1724</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>1726</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>1727</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>1729</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>1730</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1732</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>1733</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15666,32 +15706,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
     </row>
   </sheetData>
@@ -15719,20 +15759,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1751</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="56" t="s">
-        <v>1752</v>
+        <v>1755</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15800,41 +15840,41 @@
     </row>
     <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1754</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>1755</v>
+        <v>1758</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>1756</v>
+        <v>1759</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>1758</v>
+        <v>1761</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>1759</v>
+        <v>1762</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>1760</v>
+        <v>1763</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>1761</v>
+        <v>1764</v>
       </c>
       <c r="H15" s="43" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="I15" s="29" t="s">
-        <v>1763</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="60" t="s">
-        <v>1756</v>
+        <v>1759</v>
       </c>
       <c r="B16" s="44" t="n">
         <v>0</v>
@@ -15863,7 +15903,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="60" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
       <c r="B17" s="44" t="n">
         <v>125</v>
@@ -15892,7 +15932,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="60" t="s">
-        <v>1758</v>
+        <v>1761</v>
       </c>
       <c r="B18" s="44" t="n">
         <v>100</v>
@@ -15921,7 +15961,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="60" t="s">
-        <v>1759</v>
+        <v>1762</v>
       </c>
       <c r="B19" s="44" t="n">
         <v>100</v>
@@ -15950,7 +15990,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="60" t="s">
-        <v>1760</v>
+        <v>1763</v>
       </c>
       <c r="B20" s="44" t="n">
         <v>75</v>
@@ -15979,7 +16019,7 @@
     </row>
     <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="60" t="s">
-        <v>1761</v>
+        <v>1764</v>
       </c>
       <c r="B21" s="44" t="n">
         <v>75</v>
@@ -16008,7 +16048,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="60" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="B22" s="44" t="n">
         <v>75</v>
@@ -16037,7 +16077,7 @@
     </row>
     <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="61" t="s">
-        <v>1763</v>
+        <v>1766</v>
       </c>
       <c r="B23" s="46" t="n">
         <v>75</v>
@@ -16066,22 +16106,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1764</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1765</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1766</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1767</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16089,10 +16129,10 @@
         <v>463</v>
       </c>
       <c r="B32" s="62" t="s">
-        <v>1768</v>
+        <v>1771</v>
       </c>
       <c r="C32" s="63" t="s">
-        <v>1769</v>
+        <v>1772</v>
       </c>
       <c r="D32" s="63"/>
       <c r="E32" s="63"/>
@@ -16102,13 +16142,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="44" t="s">
-        <v>1770</v>
+        <v>1773</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1771</v>
+        <v>1774</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>1772</v>
+        <v>1775</v>
       </c>
       <c r="D33" s="64"/>
       <c r="E33" s="64"/>
@@ -16118,13 +16158,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="44" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1771</v>
+        <v>1774</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>1772</v>
+        <v>1775</v>
       </c>
       <c r="D34" s="64"/>
       <c r="E34" s="64"/>
@@ -16134,13 +16174,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="44" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B35" s="36" t="s">
         <v>1774</v>
       </c>
-      <c r="B35" s="36" t="s">
-        <v>1771</v>
-      </c>
       <c r="C35" s="64" t="s">
-        <v>1772</v>
+        <v>1775</v>
       </c>
       <c r="D35" s="64"/>
       <c r="E35" s="64"/>
@@ -16150,13 +16190,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="44" t="s">
-        <v>1775</v>
+        <v>1778</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
       <c r="C36" s="65" t="s">
-        <v>1776</v>
+        <v>1779</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
@@ -16166,13 +16206,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="44" t="s">
-        <v>1777</v>
+        <v>1780</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1759</v>
+        <v>1762</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>1778</v>
+        <v>1781</v>
       </c>
       <c r="D37" s="64"/>
       <c r="E37" s="64"/>
@@ -16182,13 +16222,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="44" t="s">
-        <v>1779</v>
+        <v>1782</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>1778</v>
+        <v>1781</v>
       </c>
       <c r="D38" s="64"/>
       <c r="E38" s="64"/>
@@ -16198,13 +16238,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="44" t="s">
-        <v>1780</v>
+        <v>1783</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
       <c r="C39" s="65" t="s">
-        <v>1776</v>
+        <v>1779</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65"/>
@@ -16217,10 +16257,10 @@
         <v>520</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
       <c r="C40" s="65" t="s">
-        <v>1776</v>
+        <v>1779</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -16230,13 +16270,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="44" t="s">
-        <v>1781</v>
+        <v>1784</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1760</v>
+        <v>1763</v>
       </c>
       <c r="C41" s="65" t="s">
-        <v>1782</v>
+        <v>1785</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65"/>
@@ -16246,13 +16286,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="44" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1761</v>
+        <v>1764</v>
       </c>
       <c r="C42" s="65" t="s">
-        <v>1784</v>
+        <v>1787</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -16262,13 +16302,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="44" t="s">
-        <v>1785</v>
+        <v>1788</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="C43" s="65" t="s">
-        <v>1786</v>
+        <v>1789</v>
       </c>
       <c r="D43" s="65"/>
       <c r="E43" s="65"/>
@@ -16278,13 +16318,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="44" t="s">
-        <v>1787</v>
+        <v>1790</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1763</v>
+        <v>1766</v>
       </c>
       <c r="C44" s="65" t="s">
-        <v>1788</v>
+        <v>1791</v>
       </c>
       <c r="D44" s="65"/>
       <c r="E44" s="65"/>
@@ -16294,7 +16334,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="66" t="s">
-        <v>1777</v>
+        <v>1780</v>
       </c>
       <c r="B48" s="66"/>
       <c r="C48" s="66"/>
@@ -16306,17 +16346,17 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>1789</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>1790</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="66" t="s">
-        <v>1779</v>
+        <v>1782</v>
       </c>
       <c r="B52" s="66"/>
       <c r="C52" s="66"/>
@@ -16328,12 +16368,12 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>1791</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="66" t="s">
-        <v>1792</v>
+        <v>1795</v>
       </c>
       <c r="B57" s="66"/>
       <c r="C57" s="66"/>
@@ -16345,72 +16385,72 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>1793</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>1794</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>1795</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>1796</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>1797</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1798</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>1799</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>1800</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="67" t="s">
-        <v>1801</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="67" t="s">
-        <v>1802</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="67" t="s">
-        <v>1803</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>1804</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>1805</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H73" s="66" t="s">
-        <v>1806</v>
+        <v>1809</v>
       </c>
       <c r="I73" s="66"/>
       <c r="J73" s="66"/>
@@ -16418,483 +16458,483 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="67" t="s">
-        <v>1807</v>
+        <v>1810</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>1808</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="67" t="s">
-        <v>1801</v>
+        <v>1804</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>1809</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="67" t="s">
-        <v>1802</v>
+        <v>1805</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>1810</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="67" t="s">
-        <v>1803</v>
+        <v>1806</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>1811</v>
+        <v>1814</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>1812</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="67" t="s">
-        <v>1813</v>
+        <v>1816</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>1814</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="67" t="s">
-        <v>1815</v>
+        <v>1818</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="67" t="s">
-        <v>1817</v>
+        <v>1820</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>1818</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="67" t="s">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>1821</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="67" t="s">
-        <v>1815</v>
+        <v>1818</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="67" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>1818</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="67" t="s">
-        <v>1823</v>
+        <v>1826</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>1824</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="67" t="s">
-        <v>1825</v>
+        <v>1828</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>1826</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="67" t="s">
-        <v>1827</v>
+        <v>1830</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>1828</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="67" t="s">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>1830</v>
+        <v>1833</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="67" t="s">
-        <v>1832</v>
+        <v>1835</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>1833</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="67" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>1835</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="67" t="s">
-        <v>1836</v>
+        <v>1839</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>1838</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="67" t="s">
-        <v>1839</v>
+        <v>1842</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>1840</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="67" t="s">
-        <v>1841</v>
+        <v>1844</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>1843</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="67" t="s">
-        <v>1844</v>
+        <v>1847</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>1845</v>
+        <v>1848</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>1846</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="67" t="s">
-        <v>1847</v>
+        <v>1850</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>1848</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="67" t="s">
-        <v>1849</v>
+        <v>1852</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>1850</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="67" t="s">
-        <v>1851</v>
+        <v>1854</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>1852</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="67" t="s">
-        <v>1853</v>
+        <v>1856</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>1854</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="67" t="s">
-        <v>1855</v>
+        <v>1858</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>1856</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="67" t="s">
-        <v>1857</v>
+        <v>1860</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>1858</v>
+        <v>1861</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>1859</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="67" t="s">
-        <v>1860</v>
+        <v>1863</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>1861</v>
+        <v>1864</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>1862</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="67" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>1864</v>
+        <v>1867</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>1865</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="67" t="s">
-        <v>1866</v>
+        <v>1869</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>1867</v>
+        <v>1870</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>1818</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="67" t="s">
-        <v>1868</v>
+        <v>1871</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="67" t="s">
-        <v>1870</v>
+        <v>1873</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>1872</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="67" t="s">
-        <v>1873</v>
+        <v>1876</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>1875</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="67" t="s">
-        <v>1876</v>
+        <v>1879</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>1877</v>
+        <v>1880</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>1878</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="67" t="s">
-        <v>1879</v>
+        <v>1882</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>1880</v>
+        <v>1883</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>1881</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="67" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="67" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="67" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="67" t="s">
-        <v>1886</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="67" t="s">
-        <v>1887</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="67" t="s">
-        <v>1888</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="67" t="s">
-        <v>1889</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="67" t="s">
-        <v>1890</v>
+        <v>1893</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="67" t="s">
-        <v>1892</v>
+        <v>1895</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>1893</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="67" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>1895</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="67" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="67" t="s">
-        <v>1817</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="67" t="s">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="67" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="67" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>1898</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="67" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>1900</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="67" t="s">
-        <v>1890</v>
+        <v>1893</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="67" t="s">
-        <v>1901</v>
+        <v>1904</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="67" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>1904</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="67" t="s">
-        <v>1905</v>
+        <v>1908</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>1906</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="67" t="s">
-        <v>1907</v>
+        <v>1910</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="67" t="s">
-        <v>1909</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="67" t="s">
-        <v>1910</v>
+        <v>1913</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>1911</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="67" t="s">
-        <v>1912</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="67" t="s">
-        <v>1886</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16905,78 +16945,78 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="6" t="s">
-        <v>1913</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="67" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>1915</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="67" t="s">
-        <v>1916</v>
+        <v>1919</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="67" t="s">
-        <v>1918</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="67" t="s">
-        <v>1919</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="67" t="s">
-        <v>1920</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="67" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="67" t="s">
-        <v>1922</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="67" t="s">
-        <v>1923</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="67" t="s">
-        <v>1924</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="67" t="s">
-        <v>1925</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="67" t="s">
-        <v>1926</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="67" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="67" t="s">
-        <v>1886</v>
+        <v>1889</v>
       </c>
     </row>
   </sheetData>
@@ -17083,7 +17123,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="66" t="s">
-        <v>1928</v>
+        <v>1931</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="66"/>
@@ -17101,10 +17141,10 @@
         <v>463</v>
       </c>
       <c r="D2" s="68" t="s">
-        <v>1929</v>
+        <v>1932</v>
       </c>
       <c r="E2" s="68" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17115,7 +17155,7 @@
         <v>960</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="D3" s="44" t="n">
         <v>7</v>
@@ -17132,10 +17172,10 @@
         <v>965</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="D4" s="69" t="s">
-        <v>1932</v>
+        <v>1935</v>
       </c>
       <c r="E4" s="44" t="n">
         <v>6</v>
@@ -17149,10 +17189,10 @@
         <v>965</v>
       </c>
       <c r="C5" s="70" t="s">
-        <v>1933</v>
+        <v>1936</v>
       </c>
       <c r="D5" s="69" t="s">
-        <v>1932</v>
+        <v>1935</v>
       </c>
       <c r="E5" s="70" t="n">
         <v>6</v>
@@ -17166,10 +17206,10 @@
         <v>960</v>
       </c>
       <c r="C6" s="70" t="s">
-        <v>1934</v>
+        <v>1937</v>
       </c>
       <c r="D6" s="72" t="s">
-        <v>1935</v>
+        <v>1938</v>
       </c>
       <c r="E6" s="70" t="n">
         <v>1</v>
@@ -17199,52 +17239,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1937</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1939</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1940</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1941</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1942</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1943</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1944</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
     </row>
   </sheetData>
@@ -17268,19 +17308,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="73" t="s">
-        <v>1946</v>
+        <v>1949</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
       <c r="D1" s="73"/>
       <c r="E1" s="73" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="F1" s="73"/>
       <c r="G1" s="73"/>
       <c r="H1" s="73"/>
       <c r="I1" s="73" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
       <c r="J1" s="73"/>
       <c r="K1" s="73"/>
@@ -17296,16 +17336,16 @@
         <v>24</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1949</v>
+        <v>1952</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>21</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1950</v>
+        <v>1953</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1951</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17313,10 +17353,10 @@
         <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1952</v>
+        <v>1955</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1953</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17324,10 +17364,10 @@
         <v>23</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1954</v>
+        <v>1957</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1955</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17335,35 +17375,35 @@
         <v>24</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1956</v>
+        <v>1959</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I6" s="6" t="s">
-        <v>1958</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I7" s="6" t="s">
-        <v>1959</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I8" s="6" t="s">
-        <v>1960</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I9" s="6" t="s">
-        <v>1961</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I10" s="6" t="s">
-        <v>1962</v>
+        <v>1965</v>
       </c>
     </row>
   </sheetData>
@@ -17395,28 +17435,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>1964</v>
+        <v>1967</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>1965</v>
+        <v>1968</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>1449</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>1967</v>
+        <v>1970</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>1968</v>
+        <v>1971</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>1969</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17670,7 +17710,7 @@
         <v>164</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>95</v>
@@ -17752,7 +17792,7 @@
         <v>559</v>
       </c>
       <c r="G15" s="74" t="s">
-        <v>1971</v>
+        <v>1974</v>
       </c>
       <c r="H15" s="75" t="n">
         <v>45</v>
@@ -17824,7 +17864,7 @@
         <v>1329</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>1972</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17853,7 +17893,7 @@
         <v>1770</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>1973</v>
+        <v>1976</v>
       </c>
       <c r="H22" s="77" t="s">
         <v>1464</v>
@@ -17872,7 +17912,7 @@
         <v>2023</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>1974</v>
+        <v>1977</v>
       </c>
       <c r="H23" s="77" t="n">
         <f aca="false">J4</f>
@@ -17892,7 +17932,7 @@
         <v>2299</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>1975</v>
+        <v>1978</v>
       </c>
       <c r="H24" s="6" t="e">
         <f aca="false">levelfromexp(H23,VLOOKUP(H22,G2:H10,2,0))</f>
@@ -18276,7 +18316,7 @@
         <v>856</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1976</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18284,39 +18324,39 @@
         <v>840</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1979</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1981</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1982</v>
+        <v>1985</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1984</v>
+        <v>1987</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1985</v>
+        <v>1988</v>
       </c>
     </row>
   </sheetData>
@@ -18343,7 +18383,7 @@
         <v>103</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18351,7 +18391,7 @@
         <v>104</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1987</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18367,7 +18407,7 @@
         <v>106</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1988</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18383,7 +18423,7 @@
         <v>108</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1989</v>
+        <v>1992</v>
       </c>
     </row>
   </sheetData>
@@ -18410,7 +18450,7 @@
         <v>810</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1990</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18418,7 +18458,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1991</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18434,7 +18474,7 @@
         <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1992</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18442,7 +18482,7 @@
         <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1993</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18450,7 +18490,7 @@
         <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1994</v>
+        <v>1997</v>
       </c>
     </row>
   </sheetData>
@@ -18477,7 +18517,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1995</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18488,7 +18528,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1996</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18499,29 +18539,29 @@
         <v>20</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1997</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1998</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1999</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>1995</v>
+        <v>1998</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>2001</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18548,7 +18588,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>2002</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18567,7 +18607,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>2003</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18575,10 +18615,10 @@
         <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>2005</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18586,10 +18626,10 @@
         <v>37</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>2005</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18597,10 +18637,10 @@
         <v>45</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>2005</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18611,7 +18651,7 @@
         <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>2006</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18624,7 +18664,7 @@
         <v>470</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>2007</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18635,7 +18675,7 @@
         <v>33.34</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>2008</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18659,7 +18699,7 @@
         <v>457</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>2009</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18667,7 +18707,7 @@
         <v>472</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>2010</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18718,7 +18758,7 @@
         <v>0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18734,12 +18774,12 @@
         <v>374</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>2012</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18752,7 +18792,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>1102</v>
@@ -18765,7 +18805,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>2015</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18819,12 +18859,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="78" t="s">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="B1" s="78"/>
       <c r="C1" s="78"/>
       <c r="E1" s="14" t="s">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="F1" s="14"/>
       <c r="G1" s="14"/>
@@ -18832,30 +18872,30 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="E2" s="79" t="s">
         <v>463</v>
       </c>
       <c r="F2" s="79" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="G2" s="79" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="H2" s="79" t="s">
-        <v>2023</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>1</v>
@@ -18864,7 +18904,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="70" t="s">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="F3" s="70" t="n">
         <v>5</v>
@@ -18878,7 +18918,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>6</v>
@@ -18893,7 +18933,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>5</v>
@@ -18908,7 +18948,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>3</v>
@@ -18923,7 +18963,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>2</v>
@@ -18938,7 +18978,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>0</v>
@@ -18947,7 +18987,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="F8" s="80" t="n">
         <f aca="false">SUM(F3:F7)</f>
@@ -18964,7 +19004,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="B9" s="6" t="n">
         <v>5</v>
@@ -18975,7 +19015,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1752</v>
+        <v>1755</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>5</v>
@@ -18986,7 +19026,7 @@
     </row>
     <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>20</v>
@@ -18995,7 +19035,7 @@
         <v>25</v>
       </c>
       <c r="E11" s="80" t="s">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="F11" s="80" t="n">
         <v>10</v>
@@ -19003,7 +19043,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="B12" s="6" t="n">
         <v>135</v>
@@ -19012,7 +19052,7 @@
         <v>150</v>
       </c>
       <c r="E12" s="80" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="F12" s="80" t="n">
         <v>7</v>
@@ -19020,7 +19060,7 @@
     </row>
     <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="B13" s="6" t="n">
         <v>2</v>
@@ -19031,7 +19071,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="B14" s="6" t="n">
         <v>5</v>
@@ -19042,7 +19082,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="B15" s="6" t="n">
         <v>15</v>
@@ -19053,7 +19093,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="B16" s="6" t="n">
         <v>0</v>
@@ -19064,7 +19104,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="B17" s="6" t="n">
         <v>30</v>
@@ -19073,7 +19113,7 @@
         <v>85</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
@@ -19081,7 +19121,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="B18" s="6" t="n">
         <v>0</v>
@@ -19090,21 +19130,21 @@
         <v>25</v>
       </c>
       <c r="E18" s="79" t="s">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="F18" s="79" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="G18" s="79" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="H18" s="79" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="B19" s="6" t="n">
         <v>0</v>
@@ -19113,7 +19153,7 @@
         <v>99</v>
       </c>
       <c r="E19" s="70" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="F19" s="70" t="n">
         <f aca="false">C3+C26+C34+C41+C48+C55+C63+C70+C77</f>
@@ -19130,7 +19170,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="B20" s="6" t="n">
         <v>0</v>
@@ -19139,7 +19179,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="70" t="s">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="F20" s="70" t="n">
         <f aca="false">B4+B29+B66+B71+(F19-B3)*(F11/2)</f>
@@ -19154,12 +19194,12 @@
         <v>300</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="B21" s="6" t="n">
         <v>20</v>
@@ -19168,7 +19208,7 @@
         <v>60</v>
       </c>
       <c r="E21" s="70" t="s">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="F21" s="70" t="n">
         <f aca="false">B5+B30+B81+(F19-B3)*(F12/2)</f>
@@ -19185,7 +19225,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="B22" s="6" t="n">
         <v>0</v>
@@ -19194,7 +19234,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="70" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="F22" s="70" t="n">
         <f aca="false">B6+B37+B50</f>
@@ -19211,7 +19251,7 @@
     </row>
     <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="B23" s="6" t="n">
         <v>0</v>
@@ -19220,7 +19260,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="70" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="F23" s="70" t="n">
         <f aca="false">B7+B36+B56+B65+ROUNDDOWN(F25/25,0)</f>
@@ -19235,12 +19275,12 @@
         <v>25</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E24" s="70" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="F24" s="70" t="n">
         <f aca="false">B8+B42+B57+ROUNDDOWN(F29/25,0)</f>
@@ -19255,21 +19295,21 @@
         <v>22</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="E25" s="70" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="F25" s="70" t="n">
         <f aca="false">B9+B44+B64</f>
@@ -19286,7 +19326,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="B26" s="6" t="n">
         <v>4</v>
@@ -19295,7 +19335,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="70" t="s">
-        <v>1752</v>
+        <v>1755</v>
       </c>
       <c r="F26" s="70" t="n">
         <f aca="false">B10+B78</f>
@@ -19312,7 +19352,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="B27" s="6" t="n">
         <v>10</v>
@@ -19321,7 +19361,7 @@
         <v>10</v>
       </c>
       <c r="E27" s="70" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="F27" s="70" t="n">
         <f aca="false">B11+B79</f>
@@ -19338,7 +19378,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="B28" s="6" t="n">
         <v>20</v>
@@ -19347,7 +19387,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="70" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="F28" s="70" t="n">
         <f aca="false">B12+B49</f>
@@ -19364,7 +19404,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B29" s="6" t="n">
         <v>18</v>
@@ -19373,7 +19413,7 @@
         <v>22</v>
       </c>
       <c r="E29" s="70" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="F29" s="70" t="n">
         <f aca="false">B13+B27+B58</f>
@@ -19390,7 +19430,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="B30" s="6" t="n">
         <v>5</v>
@@ -19399,7 +19439,7 @@
         <v>5</v>
       </c>
       <c r="E30" s="70" t="s">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="F30" s="70" t="n">
         <f aca="false">B14+B59+B80</f>
@@ -19416,7 +19456,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E31" s="70" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="F31" s="70" t="n">
         <f aca="false">B15</f>
@@ -19433,7 +19473,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E32" s="70" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="F32" s="70" t="n">
         <f aca="false">B16+B35+B43+B51</f>
@@ -19453,13 +19493,13 @@
         <v>840</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="E33" s="70" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="F33" s="70" t="n">
         <v>30</v>
@@ -19474,7 +19514,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="B34" s="6" t="n">
         <v>4</v>
@@ -19483,7 +19523,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="70" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="F34" s="70" t="n">
         <v>0</v>
@@ -19498,7 +19538,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="B35" s="6" t="n">
         <v>5</v>
@@ -19507,7 +19547,7 @@
         <v>5</v>
       </c>
       <c r="E35" s="70" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="F35" s="70" t="n">
         <f aca="false">B19+B28</f>
@@ -19523,7 +19563,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B36" s="6" t="n">
         <v>4</v>
@@ -19532,7 +19572,7 @@
         <v>6</v>
       </c>
       <c r="E36" s="70" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="F36" s="70" t="n">
         <v>0</v>
@@ -19548,7 +19588,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="B37" s="6" t="n">
         <v>1</v>
@@ -19557,7 +19597,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="70" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="F37" s="70" t="n">
         <v>20</v>
@@ -19572,7 +19612,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E38" s="70" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="F38" s="70" t="n">
         <f aca="false">B22+B45+B60+B84</f>
@@ -19589,7 +19629,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E39" s="70" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="F39" s="70" t="n">
         <f aca="false">B23+B67+B72+B83</f>
@@ -19609,15 +19649,15 @@
         <v>856</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="B41" s="6" t="n">
         <v>4</v>
@@ -19628,7 +19668,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B42" s="6" t="n">
         <v>13</v>
@@ -19639,7 +19679,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="B43" s="6" t="n">
         <v>5</v>
@@ -19650,7 +19690,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="B44" s="6" t="n">
         <v>10</v>
@@ -19661,7 +19701,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="B45" s="6" t="n">
         <v>1</v>
@@ -19672,18 +19712,18 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="B48" s="6" t="n">
         <v>4</v>
@@ -19694,7 +19734,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="B49" s="6" t="n">
         <v>10</v>
@@ -19705,7 +19745,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="B50" s="6" t="n">
         <v>1</v>
@@ -19716,7 +19756,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="B51" s="6" t="n">
         <v>5</v>
@@ -19727,18 +19767,18 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>1982</v>
+        <v>1985</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="B55" s="6" t="n">
         <v>4</v>
@@ -19749,7 +19789,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B56" s="6" t="n">
         <v>4</v>
@@ -19760,7 +19800,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B57" s="6" t="n">
         <v>4</v>
@@ -19771,7 +19811,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="B58" s="6" t="n">
         <v>10</v>
@@ -19782,7 +19822,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="B59" s="6" t="n">
         <v>10</v>
@@ -19793,7 +19833,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="B60" s="6" t="n">
         <v>1</v>
@@ -19804,18 +19844,18 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>1984</v>
+        <v>1987</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="B63" s="6" t="n">
         <v>4</v>
@@ -19826,7 +19866,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="B64" s="6" t="n">
         <v>10</v>
@@ -19837,7 +19877,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B65" s="6" t="n">
         <v>9</v>
@@ -19848,7 +19888,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B66" s="6" t="n">
         <v>10</v>
@@ -19859,7 +19899,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="B67" s="6" t="n">
         <v>1</v>
@@ -19870,18 +19910,18 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>2047</v>
+        <v>2050</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="B70" s="6" t="n">
         <v>3</v>
@@ -19892,7 +19932,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B71" s="6" t="n">
         <v>15</v>
@@ -19903,7 +19943,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="B72" s="6" t="n">
         <v>1</v>
@@ -19914,18 +19954,18 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>2048</v>
+        <v>2051</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="B77" s="6" t="n">
         <v>5</v>
@@ -19936,7 +19976,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>1752</v>
+        <v>1755</v>
       </c>
       <c r="B78" s="6" t="n">
         <v>10</v>
@@ -19947,7 +19987,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="B79" s="6" t="n">
         <v>10</v>
@@ -19958,7 +19998,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="B80" s="6" t="n">
         <v>10</v>
@@ -19969,7 +20009,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="B81" s="6" t="n">
         <v>25</v>
@@ -19980,7 +20020,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="B82" s="6" t="n">
         <v>5</v>
@@ -19991,7 +20031,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="B83" s="6" t="n">
         <v>1</v>
@@ -20002,7 +20042,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="B84" s="6" t="n">
         <v>1</v>
@@ -20037,55 +20077,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>2053</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>2059</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>2060</v>
+        <v>2063</v>
       </c>
     </row>
   </sheetData>
@@ -20599,10 +20639,10 @@
         <v>462</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2061</v>
+        <v>2064</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2062</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20610,7 +20650,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2063</v>
+        <v>2066</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>965</v>
@@ -20622,7 +20662,7 @@
         <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>2064</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20630,7 +20670,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2065</v>
+        <v>2068</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>965</v>
@@ -20642,7 +20682,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20650,7 +20690,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2067</v>
+        <v>2070</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>965</v>
@@ -20659,7 +20699,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>2068</v>
+        <v>2071</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>1065</v>
@@ -20697,189 +20737,189 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>2079</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>2082</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>2083</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>2084</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>2085</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>2089</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>2091</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>2094</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>2095</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>2096</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>2097</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>2099</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>2100</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>2101</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>2102</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
     </row>
   </sheetData>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="24"/>
   </bookViews>
   <sheets>
     <sheet name="Neue Daten Ep3" sheetId="1" state="visible" r:id="rId3"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="2160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="2166">
   <si>
     <t xml:space="preserve">Map texts</t>
   </si>
@@ -5228,6 +5228,24 @@
   </si>
   <si>
     <t xml:space="preserve">Rebel’s Hideout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancient city. Approaching the re-emerged ruins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">513+x?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airship and rebells with parachutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morag Hangar</t>
   </si>
   <si>
     <t xml:space="preserve">Tileset Graphics (Icon Gfx)</t>
@@ -7036,7 +7054,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7238,6 +7256,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -15142,7 +15164,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.98"/>
@@ -15221,6 +15243,40 @@
       </c>
       <c r="E6" s="1" t="n">
         <v>56</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -15248,19 +15304,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>1679</v>
+        <v>1685</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
       <c r="G1" s="13" t="s">
-        <v>1680</v>
+        <v>1686</v>
       </c>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1681</v>
+        <v>1687</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>484</v>
@@ -15269,7 +15325,7 @@
         <v>480</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1681</v>
+        <v>1687</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>484</v>
@@ -15286,7 +15342,7 @@
         <v>1193</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>4</v>
@@ -15295,7 +15351,7 @@
         <v>1167</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15306,7 +15362,7 @@
         <v>1194</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>4</v>
@@ -15315,7 +15371,7 @@
         <v>1168</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15326,7 +15382,7 @@
         <v>1195</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>4</v>
@@ -15335,7 +15391,7 @@
         <v>1169</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15346,7 +15402,7 @@
         <v>1196</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>4</v>
@@ -15355,7 +15411,7 @@
         <v>1170</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15366,7 +15422,7 @@
         <v>1197</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>4</v>
@@ -15375,7 +15431,7 @@
         <v>1171</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15386,7 +15442,7 @@
         <v>1198</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>4</v>
@@ -15395,7 +15451,7 @@
         <v>1172</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15406,7 +15462,7 @@
         <v>1199</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>4</v>
@@ -15415,7 +15471,7 @@
         <v>1173</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15426,7 +15482,7 @@
         <v>1200</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>4</v>
@@ -15435,7 +15491,7 @@
         <v>1174</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
     </row>
   </sheetData>
@@ -15469,16 +15525,16 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="51" t="s">
-        <v>1683</v>
+      <c r="A1" s="52" t="s">
+        <v>1689</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1684</v>
+        <v>1690</v>
       </c>
       <c r="D1" s="13"/>
       <c r="E1" s="13"/>
       <c r="G1" s="13" t="s">
-        <v>1685</v>
+        <v>1691</v>
       </c>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
@@ -15486,302 +15542,302 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1686</v>
-      </c>
-      <c r="C2" s="52" t="s">
-        <v>1687</v>
-      </c>
-      <c r="D2" s="53"/>
-      <c r="E2" s="54"/>
-      <c r="G2" s="52" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D2" s="54"/>
+      <c r="E2" s="55"/>
+      <c r="G2" s="53" t="s">
         <v>485</v>
       </c>
-      <c r="H2" s="52" t="s">
-        <v>1688</v>
-      </c>
-      <c r="I2" s="52" t="s">
+      <c r="H2" s="53" t="s">
+        <v>1694</v>
+      </c>
+      <c r="I2" s="53" t="s">
         <v>480</v>
       </c>
-      <c r="J2" s="52" t="s">
-        <v>1689</v>
+      <c r="J2" s="53" t="s">
+        <v>1695</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1690</v>
+        <v>1696</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1691</v>
-      </c>
-      <c r="E3" s="55"/>
+        <v>1697</v>
+      </c>
+      <c r="E3" s="56"/>
       <c r="G3" s="1" t="s">
-        <v>1692</v>
+        <v>1698</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1693</v>
+        <v>1699</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1694</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1695</v>
+        <v>1701</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1696</v>
+        <v>1702</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1697</v>
+        <v>1703</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>1698</v>
+        <v>1704</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1699</v>
+        <v>1705</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>1700</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1701</v>
+        <v>1707</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1702</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1703</v>
+        <v>1709</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1704</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1705</v>
+        <v>1711</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1706</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1707</v>
+        <v>1713</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1708</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1709</v>
+        <v>1715</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1710</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1711</v>
+        <v>1717</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1712</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>1713</v>
+        <v>1719</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1714</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1715</v>
+        <v>1721</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1716</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1717</v>
+        <v>1723</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1718</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>1719</v>
+        <v>1725</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1720</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>1721</v>
+        <v>1727</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1722</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>1723</v>
+        <v>1729</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1724</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>1725</v>
+        <v>1731</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1726</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>1727</v>
+        <v>1733</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1728</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>1729</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>1730</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>1731</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>1732</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>1733</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>1734</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1735</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>1736</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1737</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1738</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1739</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>1740</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>1741</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>1742</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>1743</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>1744</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>1745</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>1746</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>1747</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>1748</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>1749</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>1750</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>1751</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>1752</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>1753</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15789,147 +15845,147 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>1754</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>1755</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>1756</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>1757</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>1758</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>1759</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>1760</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>1761</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>1762</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>1763</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>1764</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>1765</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>1766</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>1767</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>1768</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>1769</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>1770</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1771</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>1772</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>1773</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>1774</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>1775</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>1776</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>1777</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>1779</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>1780</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>1781</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>1782</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15963,32 +16019,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1783</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1784</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1785</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1786</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1787</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1788</v>
+        <v>1794</v>
       </c>
     </row>
   </sheetData>
@@ -16016,27 +16072,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1789</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1790</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="56" t="s">
-        <v>1791</v>
-      </c>
-      <c r="B4" s="57" t="s">
-        <v>1792</v>
+      <c r="A4" s="57" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B4" s="58" t="s">
+        <v>1798</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="B5" s="58" t="n">
+      <c r="B5" s="59" t="n">
         <f aca="false">ROUNDDOWN((A5-50)/5,0)</f>
         <v>-10</v>
       </c>
@@ -16045,7 +16101,7 @@
       <c r="A6" s="35" t="n">
         <v>25</v>
       </c>
-      <c r="B6" s="58" t="n">
+      <c r="B6" s="59" t="n">
         <f aca="false">ROUNDDOWN((A6-50)/5,0)</f>
         <v>-5</v>
       </c>
@@ -16054,7 +16110,7 @@
       <c r="A7" s="35" t="n">
         <v>50</v>
       </c>
-      <c r="B7" s="58" t="n">
+      <c r="B7" s="59" t="n">
         <f aca="false">ROUNDDOWN((A7-50)/5,0)</f>
         <v>0</v>
       </c>
@@ -16063,7 +16119,7 @@
       <c r="A8" s="35" t="n">
         <v>75</v>
       </c>
-      <c r="B8" s="58" t="n">
+      <c r="B8" s="59" t="n">
         <f aca="false">ROUNDDOWN((A8-50)/5,0)</f>
         <v>5</v>
       </c>
@@ -16072,7 +16128,7 @@
       <c r="A9" s="35" t="n">
         <v>100</v>
       </c>
-      <c r="B9" s="58" t="n">
+      <c r="B9" s="59" t="n">
         <f aca="false">ROUNDDOWN((A9-50)/5,0)</f>
         <v>10</v>
       </c>
@@ -16081,7 +16137,7 @@
       <c r="A10" s="35" t="n">
         <v>125</v>
       </c>
-      <c r="B10" s="58" t="n">
+      <c r="B10" s="59" t="n">
         <f aca="false">ROUNDDOWN((A10-50)/5,0)</f>
         <v>15</v>
       </c>
@@ -16090,48 +16146,48 @@
       <c r="A11" s="41" t="n">
         <v>150</v>
       </c>
-      <c r="B11" s="59" t="n">
+      <c r="B11" s="60" t="n">
         <f aca="false">ROUNDDOWN((A11-50)/5,0)</f>
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1793</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>1794</v>
+        <v>1800</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>1795</v>
+        <v>1801</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>1796</v>
+        <v>1802</v>
       </c>
       <c r="D15" s="43" t="s">
-        <v>1797</v>
+        <v>1803</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>1798</v>
+        <v>1804</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>1799</v>
+        <v>1805</v>
       </c>
       <c r="G15" s="43" t="s">
-        <v>1800</v>
+        <v>1806</v>
       </c>
       <c r="H15" s="43" t="s">
+        <v>1807</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="61" t="s">
         <v>1801</v>
-      </c>
-      <c r="I15" s="29" t="s">
-        <v>1802</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="60" t="s">
-        <v>1795</v>
       </c>
       <c r="B16" s="44" t="n">
         <v>0</v>
@@ -16159,8 +16215,8 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="60" t="s">
-        <v>1796</v>
+      <c r="A17" s="61" t="s">
+        <v>1802</v>
       </c>
       <c r="B17" s="44" t="n">
         <v>125</v>
@@ -16188,8 +16244,8 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="60" t="s">
-        <v>1797</v>
+      <c r="A18" s="61" t="s">
+        <v>1803</v>
       </c>
       <c r="B18" s="44" t="n">
         <v>100</v>
@@ -16217,8 +16273,8 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="60" t="s">
-        <v>1798</v>
+      <c r="A19" s="61" t="s">
+        <v>1804</v>
       </c>
       <c r="B19" s="44" t="n">
         <v>100</v>
@@ -16246,8 +16302,8 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="60" t="s">
-        <v>1799</v>
+      <c r="A20" s="61" t="s">
+        <v>1805</v>
       </c>
       <c r="B20" s="44" t="n">
         <v>75</v>
@@ -16275,8 +16331,8 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="60" t="s">
-        <v>1800</v>
+      <c r="A21" s="61" t="s">
+        <v>1806</v>
       </c>
       <c r="B21" s="44" t="n">
         <v>75</v>
@@ -16304,8 +16360,8 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="60" t="s">
-        <v>1801</v>
+      <c r="A22" s="61" t="s">
+        <v>1807</v>
       </c>
       <c r="B22" s="44" t="n">
         <v>75</v>
@@ -16333,8 +16389,8 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="61" t="s">
-        <v>1802</v>
+      <c r="A23" s="62" t="s">
+        <v>1808</v>
       </c>
       <c r="B23" s="46" t="n">
         <v>75</v>
@@ -16363,917 +16419,917 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1803</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1804</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1805</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1806</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="62" t="s">
+      <c r="A32" s="63" t="s">
         <v>485</v>
       </c>
-      <c r="B32" s="62" t="s">
-        <v>1807</v>
-      </c>
-      <c r="C32" s="63" t="s">
-        <v>1808</v>
-      </c>
-      <c r="D32" s="63"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="63"/>
-      <c r="H32" s="63"/>
+      <c r="B32" s="63" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C32" s="64" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D32" s="64"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="44" t="s">
-        <v>1809</v>
+        <v>1815</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1810</v>
-      </c>
-      <c r="C33" s="64" t="s">
-        <v>1811</v>
-      </c>
-      <c r="D33" s="64"/>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
+        <v>1816</v>
+      </c>
+      <c r="C33" s="65" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D33" s="65"/>
+      <c r="E33" s="65"/>
+      <c r="F33" s="65"/>
+      <c r="G33" s="65"/>
+      <c r="H33" s="65"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="44" t="s">
-        <v>1812</v>
+        <v>1818</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>1810</v>
-      </c>
-      <c r="C34" s="64" t="s">
-        <v>1811</v>
-      </c>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
+        <v>1816</v>
+      </c>
+      <c r="C34" s="65" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
+      <c r="F34" s="65"/>
+      <c r="G34" s="65"/>
+      <c r="H34" s="65"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="44" t="s">
-        <v>1813</v>
+        <v>1819</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>1810</v>
-      </c>
-      <c r="C35" s="64" t="s">
-        <v>1811</v>
-      </c>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
+        <v>1816</v>
+      </c>
+      <c r="C35" s="65" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="44" t="s">
-        <v>1814</v>
+        <v>1820</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>1796</v>
-      </c>
-      <c r="C36" s="65" t="s">
-        <v>1815</v>
-      </c>
-      <c r="D36" s="65"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
+        <v>1802</v>
+      </c>
+      <c r="C36" s="66" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="66"/>
+      <c r="H36" s="66"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="44" t="s">
-        <v>1816</v>
+        <v>1822</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>1798</v>
-      </c>
-      <c r="C37" s="64" t="s">
-        <v>1817</v>
-      </c>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64"/>
-      <c r="F37" s="64"/>
-      <c r="G37" s="64"/>
-      <c r="H37" s="64"/>
+        <v>1804</v>
+      </c>
+      <c r="C37" s="65" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="44" t="s">
-        <v>1818</v>
+        <v>1824</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>1796</v>
-      </c>
-      <c r="C38" s="64" t="s">
-        <v>1817</v>
-      </c>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="64"/>
-      <c r="H38" s="64"/>
+        <v>1802</v>
+      </c>
+      <c r="C38" s="65" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="44" t="s">
-        <v>1819</v>
+        <v>1825</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>1796</v>
-      </c>
-      <c r="C39" s="65" t="s">
-        <v>1815</v>
-      </c>
-      <c r="D39" s="65"/>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="65"/>
+        <v>1802</v>
+      </c>
+      <c r="C39" s="66" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="66"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="44" t="s">
         <v>542</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>1796</v>
-      </c>
-      <c r="C40" s="65" t="s">
-        <v>1815</v>
-      </c>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="65"/>
+        <v>1802</v>
+      </c>
+      <c r="C40" s="66" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
+      <c r="H40" s="66"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="44" t="s">
-        <v>1820</v>
+        <v>1826</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>1799</v>
-      </c>
-      <c r="C41" s="65" t="s">
-        <v>1821</v>
-      </c>
-      <c r="D41" s="65"/>
-      <c r="E41" s="65"/>
-      <c r="F41" s="65"/>
-      <c r="G41" s="65"/>
-      <c r="H41" s="65"/>
+        <v>1805</v>
+      </c>
+      <c r="C41" s="66" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="66"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="44" t="s">
-        <v>1822</v>
+        <v>1828</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>1800</v>
-      </c>
-      <c r="C42" s="65" t="s">
-        <v>1823</v>
-      </c>
-      <c r="D42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="65"/>
+        <v>1806</v>
+      </c>
+      <c r="C42" s="66" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D42" s="66"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="66"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="44" t="s">
-        <v>1824</v>
+        <v>1830</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>1801</v>
-      </c>
-      <c r="C43" s="65" t="s">
-        <v>1825</v>
-      </c>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
-      <c r="H43" s="65"/>
+        <v>1807</v>
+      </c>
+      <c r="C43" s="66" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="44" t="s">
-        <v>1826</v>
+        <v>1832</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>1802</v>
-      </c>
-      <c r="C44" s="65" t="s">
-        <v>1827</v>
-      </c>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="65"/>
-      <c r="H44" s="65"/>
+        <v>1808</v>
+      </c>
+      <c r="C44" s="66" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D44" s="66"/>
+      <c r="E44" s="66"/>
+      <c r="F44" s="66"/>
+      <c r="G44" s="66"/>
+      <c r="H44" s="66"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="66" t="s">
-        <v>1816</v>
-      </c>
-      <c r="B48" s="66"/>
-      <c r="C48" s="66"/>
-      <c r="D48" s="66"/>
-      <c r="E48" s="66"/>
-      <c r="F48" s="66"/>
-      <c r="G48" s="66"/>
-      <c r="H48" s="66"/>
+      <c r="A48" s="67" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B48" s="67"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="67"/>
+      <c r="F48" s="67"/>
+      <c r="G48" s="67"/>
+      <c r="H48" s="67"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>1828</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>1829</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="66" t="s">
-        <v>1818</v>
-      </c>
-      <c r="B52" s="66"/>
-      <c r="C52" s="66"/>
-      <c r="D52" s="66"/>
-      <c r="E52" s="66"/>
-      <c r="F52" s="66"/>
-      <c r="G52" s="66"/>
-      <c r="H52" s="66"/>
+      <c r="A52" s="67" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B52" s="67"/>
+      <c r="C52" s="67"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="67"/>
+      <c r="G52" s="67"/>
+      <c r="H52" s="67"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>1830</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="66" t="s">
-        <v>1831</v>
-      </c>
-      <c r="B57" s="66"/>
-      <c r="C57" s="66"/>
-      <c r="D57" s="66"/>
-      <c r="E57" s="66"/>
-      <c r="F57" s="66"/>
-      <c r="G57" s="66"/>
-      <c r="H57" s="66"/>
+      <c r="A57" s="67" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B57" s="67"/>
+      <c r="C57" s="67"/>
+      <c r="D57" s="67"/>
+      <c r="E57" s="67"/>
+      <c r="F57" s="67"/>
+      <c r="G57" s="67"/>
+      <c r="H57" s="67"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>1832</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>1833</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>1834</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>1835</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>1836</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1837</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>1838</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>1839</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="67" t="s">
-        <v>1840</v>
+      <c r="A67" s="68" t="s">
+        <v>1846</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="67" t="s">
-        <v>1841</v>
+      <c r="A68" s="68" t="s">
+        <v>1847</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="67" t="s">
-        <v>1842</v>
+      <c r="A69" s="68" t="s">
+        <v>1848</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>1843</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>1844</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H73" s="66" t="s">
-        <v>1845</v>
-      </c>
-      <c r="I73" s="66"/>
-      <c r="J73" s="66"/>
-      <c r="K73" s="66"/>
+      <c r="H73" s="67" t="s">
+        <v>1851</v>
+      </c>
+      <c r="I73" s="67"/>
+      <c r="J73" s="67"/>
+      <c r="K73" s="67"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="67" t="s">
+      <c r="A74" s="68" t="s">
+        <v>1852</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="68" t="s">
         <v>1846</v>
       </c>
-      <c r="H74" s="6" t="s">
+      <c r="H75" s="6" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="68" t="s">
         <v>1847</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="67" t="s">
-        <v>1840</v>
-      </c>
-      <c r="H75" s="6" t="s">
+      <c r="H76" s="6" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="68" t="s">
         <v>1848</v>
       </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="67" t="s">
-        <v>1841</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>1849</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="67" t="s">
-        <v>1842</v>
-      </c>
       <c r="C77" s="6" t="s">
-        <v>1850</v>
+        <v>1856</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>1851</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="67" t="s">
-        <v>1852</v>
+      <c r="A78" s="68" t="s">
+        <v>1858</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>1853</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="67" t="s">
-        <v>1854</v>
+      <c r="A79" s="68" t="s">
+        <v>1860</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>1855</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="67" t="s">
-        <v>1856</v>
+      <c r="A80" s="68" t="s">
+        <v>1862</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>1857</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="67" t="s">
-        <v>1858</v>
+      <c r="A81" s="68" t="s">
+        <v>1864</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="H81" s="6" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="68" t="s">
         <v>1860</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="67" t="s">
-        <v>1854</v>
-      </c>
       <c r="H82" s="6" t="s">
-        <v>1855</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="67" t="s">
-        <v>1861</v>
+      <c r="A83" s="68" t="s">
+        <v>1867</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>1857</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="67" t="s">
+      <c r="A84" s="68" t="s">
+        <v>1868</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="68" t="s">
+        <v>1870</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="68" t="s">
+        <v>1872</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="68" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>1875</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="68" t="s">
+        <v>1877</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="68" t="s">
+        <v>1879</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="68" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>1882</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="68" t="s">
+        <v>1884</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="68" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>1887</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="68" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>1890</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="68" t="s">
+        <v>1892</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="68" t="s">
+        <v>1894</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="68" t="s">
+        <v>1896</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="68" t="s">
+        <v>1898</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="68" t="s">
+        <v>1900</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="68" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>1903</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="68" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>1906</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="68" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>1909</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="68" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="68" t="s">
+        <v>1913</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="68" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>1916</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="68" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>1919</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="68" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>1922</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="68" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>1925</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="68" t="s">
+        <v>1927</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="68" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="68" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="68" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="68" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="68" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="68" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="68" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="68" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="68" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="68" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="68" t="s">
         <v>1862</v>
       </c>
-      <c r="H84" s="6" t="s">
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="67" t="s">
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="68" t="s">
         <v>1864</v>
       </c>
-      <c r="H85" s="6" t="s">
-        <v>1865</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="67" t="s">
-        <v>1866</v>
-      </c>
-      <c r="H86" s="6" t="s">
+      <c r="C122" s="6" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="68" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="68" t="s">
         <v>1867</v>
       </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="67" t="s">
-        <v>1868</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>1869</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="67" t="s">
-        <v>1871</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>1872</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="67" t="s">
-        <v>1873</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>1874</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="67" t="s">
-        <v>1875</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>1876</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>1877</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="67" t="s">
-        <v>1878</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="67" t="s">
-        <v>1880</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>1881</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>1882</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="67" t="s">
-        <v>1883</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>1884</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="67" t="s">
-        <v>1886</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="67" t="s">
-        <v>1888</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>1889</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="67" t="s">
-        <v>1890</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>1891</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="67" t="s">
-        <v>1892</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>1893</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="67" t="s">
-        <v>1894</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="67" t="s">
-        <v>1896</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>1897</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>1898</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="67" t="s">
-        <v>1899</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>1900</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>1901</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="67" t="s">
-        <v>1902</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>1903</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>1904</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="67" t="s">
-        <v>1905</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>1906</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>1857</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="67" t="s">
-        <v>1907</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>1908</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="67" t="s">
-        <v>1909</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>1910</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>1911</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="67" t="s">
-        <v>1912</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>1913</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>1914</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="67" t="s">
-        <v>1915</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>1916</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="67" t="s">
-        <v>1918</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>1919</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="67" t="s">
-        <v>1921</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>1908</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="67" t="s">
-        <v>1922</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>1923</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="67" t="s">
-        <v>1924</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="67" t="s">
-        <v>1925</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="67" t="s">
-        <v>1926</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="67" t="s">
-        <v>1927</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="67" t="s">
-        <v>1928</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="67" t="s">
-        <v>1929</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>1930</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="67" t="s">
+      <c r="C124" s="6" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="68" t="s">
+        <v>1944</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="68" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="68" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="68" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="68" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="68" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="68" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="68" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="68" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="68" t="s">
         <v>1931</v>
       </c>
-      <c r="C118" s="6" t="s">
-        <v>1932</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="67" t="s">
-        <v>1933</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>1934</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="67" t="s">
-        <v>1935</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="67" t="s">
-        <v>1856</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="67" t="s">
-        <v>1858</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="67" t="s">
-        <v>1935</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="67" t="s">
-        <v>1861</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>1937</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="67" t="s">
-        <v>1938</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>1939</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="67" t="s">
-        <v>1929</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>1930</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="67" t="s">
-        <v>1940</v>
-      </c>
-      <c r="C127" s="6" t="s">
-        <v>1941</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="67" t="s">
-        <v>1942</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>1943</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="67" t="s">
-        <v>1944</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="67" t="s">
-        <v>1946</v>
-      </c>
-      <c r="C130" s="6" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="67" t="s">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="67" t="s">
-        <v>1949</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="67" t="s">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="67" t="s">
-        <v>1925</v>
-      </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="67"/>
+      <c r="A135" s="68"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="67"/>
+      <c r="A136" s="68"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="6" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="67" t="s">
-        <v>1953</v>
+      <c r="A138" s="68" t="s">
+        <v>1959</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>1954</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="67" t="s">
-        <v>1955</v>
+      <c r="A139" s="68" t="s">
+        <v>1961</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>1956</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="67" t="s">
-        <v>1957</v>
+      <c r="A140" s="68" t="s">
+        <v>1963</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="67" t="s">
-        <v>1958</v>
+      <c r="A141" s="68" t="s">
+        <v>1964</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="67" t="s">
-        <v>1959</v>
+      <c r="A142" s="68" t="s">
+        <v>1965</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="67" t="s">
-        <v>1960</v>
+      <c r="A143" s="68" t="s">
+        <v>1966</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="67" t="s">
-        <v>1961</v>
+      <c r="A144" s="68" t="s">
+        <v>1967</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="67" t="s">
-        <v>1962</v>
+      <c r="A145" s="68" t="s">
+        <v>1968</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="67" t="s">
-        <v>1963</v>
+      <c r="A146" s="68" t="s">
+        <v>1969</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="67" t="s">
-        <v>1964</v>
+      <c r="A147" s="68" t="s">
+        <v>1970</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="67" t="s">
-        <v>1965</v>
+      <c r="A148" s="68" t="s">
+        <v>1971</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="67" t="s">
-        <v>1966</v>
+      <c r="A149" s="68" t="s">
+        <v>1972</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="67" t="s">
-        <v>1925</v>
+      <c r="A150" s="68" t="s">
+        <v>1931</v>
       </c>
     </row>
   </sheetData>
@@ -17379,28 +17435,28 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="66" t="s">
-        <v>1967</v>
-      </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
+      <c r="A1" s="67" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="69" t="s">
         <v>834</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="69" t="s">
         <v>486</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="69" t="s">
         <v>485</v>
       </c>
-      <c r="D2" s="68" t="s">
-        <v>1968</v>
-      </c>
-      <c r="E2" s="68" t="s">
+      <c r="D2" s="69" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E2" s="69" t="s">
         <v>1674</v>
       </c>
     </row>
@@ -17408,11 +17464,11 @@
       <c r="A3" s="44" t="n">
         <v>464</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="69" t="s">
         <v>987</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>1969</v>
+        <v>1975</v>
       </c>
       <c r="D3" s="44" t="n">
         <v>7</v>
@@ -17425,50 +17481,50 @@
       <c r="A4" s="44" t="n">
         <v>465</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="69" t="s">
         <v>992</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>1970</v>
-      </c>
-      <c r="D4" s="69" t="s">
-        <v>1971</v>
+        <v>1976</v>
+      </c>
+      <c r="D4" s="70" t="s">
+        <v>1977</v>
       </c>
       <c r="E4" s="44" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="70" t="n">
+      <c r="A5" s="71" t="n">
         <v>466</v>
       </c>
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="72" t="s">
         <v>992</v>
       </c>
-      <c r="C5" s="70" t="s">
-        <v>1972</v>
-      </c>
-      <c r="D5" s="69" t="s">
-        <v>1971</v>
-      </c>
-      <c r="E5" s="70" t="n">
+      <c r="C5" s="71" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D5" s="70" t="s">
+        <v>1977</v>
+      </c>
+      <c r="E5" s="71" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="70" t="n">
+      <c r="A6" s="71" t="n">
         <v>467</v>
       </c>
-      <c r="B6" s="71" t="s">
+      <c r="B6" s="72" t="s">
         <v>987</v>
       </c>
-      <c r="C6" s="70" t="s">
-        <v>1973</v>
-      </c>
-      <c r="D6" s="72" t="s">
-        <v>1974</v>
-      </c>
-      <c r="E6" s="70" t="n">
+      <c r="C6" s="71" t="s">
+        <v>1979</v>
+      </c>
+      <c r="D6" s="73" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E6" s="71" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17496,52 +17552,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1975</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1976</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1977</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1978</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1979</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1980</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1981</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1982</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1983</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1984</v>
+        <v>1990</v>
       </c>
     </row>
   </sheetData>
@@ -17564,45 +17620,45 @@
   <sheetFormatPr defaultColWidth="12.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="73" t="s">
-        <v>1985</v>
-      </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73" t="s">
-        <v>1986</v>
-      </c>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73" t="s">
-        <v>1987</v>
-      </c>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="73"/>
+      <c r="A1" s="74" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74" t="s">
+        <v>1992</v>
+      </c>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74" t="s">
+        <v>1993</v>
+      </c>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="n">
         <v>24</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1988</v>
+        <v>1994</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>21</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1989</v>
+        <v>1995</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>1990</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17610,10 +17666,10 @@
         <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1991</v>
+        <v>1997</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1992</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17621,10 +17677,10 @@
         <v>23</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1993</v>
+        <v>1999</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1994</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17632,35 +17688,35 @@
         <v>24</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1995</v>
+        <v>2001</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1996</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I6" s="6" t="s">
-        <v>1997</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I7" s="6" t="s">
-        <v>1998</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I8" s="6" t="s">
-        <v>1999</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I9" s="6" t="s">
-        <v>2000</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I10" s="6" t="s">
-        <v>2001</v>
+        <v>2007</v>
       </c>
     </row>
   </sheetData>
@@ -17692,28 +17748,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>1480</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>2005</v>
+        <v>2011</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>2008</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17967,7 +18023,7 @@
         <v>164</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>95</v>
@@ -18048,10 +18104,10 @@
         <f aca="false">C14+B15</f>
         <v>559</v>
       </c>
-      <c r="G15" s="74" t="s">
-        <v>2010</v>
-      </c>
-      <c r="H15" s="75" t="n">
+      <c r="G15" s="75" t="s">
+        <v>2016</v>
+      </c>
+      <c r="H15" s="76" t="n">
         <v>45</v>
       </c>
     </row>
@@ -18067,7 +18123,7 @@
         <f aca="false">C15+B16</f>
         <v>679</v>
       </c>
-      <c r="H16" s="76"/>
+      <c r="H16" s="77"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="n">
@@ -18121,7 +18177,7 @@
         <v>1329</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>2011</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18150,9 +18206,9 @@
         <v>1770</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>2012</v>
-      </c>
-      <c r="H22" s="77" t="s">
+        <v>2018</v>
+      </c>
+      <c r="H22" s="78" t="s">
         <v>1495</v>
       </c>
     </row>
@@ -18169,9 +18225,9 @@
         <v>2023</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>2013</v>
-      </c>
-      <c r="H23" s="77" t="n">
+        <v>2019</v>
+      </c>
+      <c r="H23" s="78" t="n">
         <f aca="false">J4</f>
         <v>1864610</v>
       </c>
@@ -18189,7 +18245,7 @@
         <v>2299</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="H24" s="6" t="e">
         <f aca="false">levelfromexp(H23,VLOOKUP(H22,G2:H10,2,0))</f>
@@ -18573,7 +18629,7 @@
         <v>880</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2015</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18581,39 +18637,39 @@
         <v>864</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2016</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2018</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2020</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2021</v>
+        <v>2027</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2022</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2023</v>
+        <v>2029</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
     </row>
   </sheetData>
@@ -18640,7 +18696,7 @@
         <v>103</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2025</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18648,7 +18704,7 @@
         <v>104</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2026</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18664,7 +18720,7 @@
         <v>106</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2027</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18680,7 +18736,7 @@
         <v>108</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2028</v>
+        <v>2034</v>
       </c>
     </row>
   </sheetData>
@@ -18710,7 +18766,7 @@
         <v>834</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2029</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18718,7 +18774,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2030</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18734,7 +18790,7 @@
         <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2031</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18742,7 +18798,7 @@
         <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18750,7 +18806,7 @@
         <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2033</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18758,7 +18814,7 @@
         <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2034</v>
+        <v>2040</v>
       </c>
     </row>
   </sheetData>
@@ -18785,7 +18841,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2035</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18796,7 +18852,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2036</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18807,29 +18863,29 @@
         <v>20</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>2037</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>2038</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>2039</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>2035</v>
+        <v>2041</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>2040</v>
+        <v>2046</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>2041</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18856,7 +18912,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>2042</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18875,7 +18931,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>2043</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18883,10 +18939,10 @@
         <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>2044</v>
+        <v>2050</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>2045</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18894,10 +18950,10 @@
         <v>37</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>2044</v>
+        <v>2050</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>2045</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18905,10 +18961,10 @@
         <v>45</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>2044</v>
+        <v>2050</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>2045</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18919,7 +18975,7 @@
         <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>2046</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18932,7 +18988,7 @@
         <v>470</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>2047</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18943,7 +18999,7 @@
         <v>33.34</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>2048</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18967,7 +19023,7 @@
         <v>457</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>2049</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18975,7 +19031,7 @@
         <v>472</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>2050</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19026,7 +19082,7 @@
         <v>0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>2051</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19042,12 +19098,12 @@
         <v>374</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>2052</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>2053</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19060,7 +19116,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>2054</v>
+        <v>2060</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>1129</v>
@@ -19073,7 +19129,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>2055</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19126,13 +19182,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="78" t="s">
-        <v>2056</v>
-      </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
+      <c r="A1" s="79" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
       <c r="E1" s="14" t="s">
-        <v>2057</v>
+        <v>2063</v>
       </c>
       <c r="F1" s="14"/>
       <c r="G1" s="14"/>
@@ -19140,30 +19196,30 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>2058</v>
+        <v>2064</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E2" s="79" t="s">
+        <v>2066</v>
+      </c>
+      <c r="E2" s="80" t="s">
         <v>485</v>
       </c>
-      <c r="F2" s="79" t="s">
-        <v>2061</v>
-      </c>
-      <c r="G2" s="79" t="s">
-        <v>2062</v>
-      </c>
-      <c r="H2" s="79" t="s">
-        <v>2063</v>
+      <c r="F2" s="80" t="s">
+        <v>2067</v>
+      </c>
+      <c r="G2" s="80" t="s">
+        <v>2068</v>
+      </c>
+      <c r="H2" s="80" t="s">
+        <v>2069</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>1</v>
@@ -19171,22 +19227,22 @@
       <c r="C3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="70" t="s">
-        <v>2064</v>
-      </c>
-      <c r="F3" s="70" t="n">
+      <c r="E3" s="71" t="s">
+        <v>2070</v>
+      </c>
+      <c r="F3" s="71" t="n">
         <v>5</v>
       </c>
-      <c r="G3" s="70" t="n">
+      <c r="G3" s="71" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="70" t="n">
+      <c r="H3" s="71" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2063</v>
+        <v>2069</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>6</v>
@@ -19194,14 +19250,14 @@
       <c r="C4" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2065</v>
+        <v>2071</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>5</v>
@@ -19209,14 +19265,14 @@
       <c r="C5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2066</v>
+        <v>2072</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>3</v>
@@ -19224,14 +19280,14 @@
       <c r="C6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>2061</v>
+        <v>2067</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>2</v>
@@ -19239,14 +19295,14 @@
       <c r="C7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>2062</v>
+        <v>2068</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>0</v>
@@ -19254,25 +19310,25 @@
       <c r="C8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="80" t="s">
-        <v>2067</v>
-      </c>
-      <c r="F8" s="80" t="n">
+      <c r="E8" s="81" t="s">
+        <v>2073</v>
+      </c>
+      <c r="F8" s="81" t="n">
         <f aca="false">SUM(F3:F7)</f>
         <v>5</v>
       </c>
-      <c r="G8" s="80" t="n">
+      <c r="G8" s="81" t="n">
         <f aca="false">SUM(G3:G7)</f>
         <v>5</v>
       </c>
-      <c r="H8" s="80" t="n">
+      <c r="H8" s="81" t="n">
         <f aca="false">SUM(H3:H7)</f>
         <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>2068</v>
+        <v>2074</v>
       </c>
       <c r="B9" s="6" t="n">
         <v>5</v>
@@ -19283,7 +19339,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1791</v>
+        <v>1797</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>5</v>
@@ -19294,7 +19350,7 @@
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>2069</v>
+        <v>2075</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>20</v>
@@ -19302,16 +19358,16 @@
       <c r="C11" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E11" s="80" t="s">
-        <v>2070</v>
-      </c>
-      <c r="F11" s="80" t="n">
+      <c r="E11" s="81" t="s">
+        <v>2076</v>
+      </c>
+      <c r="F11" s="81" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>2071</v>
+        <v>2077</v>
       </c>
       <c r="B12" s="6" t="n">
         <v>135</v>
@@ -19319,16 +19375,16 @@
       <c r="C12" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="E12" s="80" t="s">
-        <v>2072</v>
-      </c>
-      <c r="F12" s="80" t="n">
+      <c r="E12" s="81" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F12" s="81" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>2073</v>
+        <v>2079</v>
       </c>
       <c r="B13" s="6" t="n">
         <v>2</v>
@@ -19339,7 +19395,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>2074</v>
+        <v>2080</v>
       </c>
       <c r="B14" s="6" t="n">
         <v>5</v>
@@ -19350,7 +19406,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>2075</v>
+        <v>2081</v>
       </c>
       <c r="B15" s="6" t="n">
         <v>15</v>
@@ -19361,7 +19417,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>2076</v>
+        <v>2082</v>
       </c>
       <c r="B16" s="6" t="n">
         <v>0</v>
@@ -19372,7 +19428,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>2077</v>
+        <v>2083</v>
       </c>
       <c r="B17" s="6" t="n">
         <v>30</v>
@@ -19381,7 +19437,7 @@
         <v>85</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>2078</v>
+        <v>2084</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
@@ -19389,7 +19445,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>2079</v>
+        <v>2085</v>
       </c>
       <c r="B18" s="6" t="n">
         <v>0</v>
@@ -19397,22 +19453,22 @@
       <c r="C18" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E18" s="79" t="s">
-        <v>2058</v>
-      </c>
-      <c r="F18" s="79" t="s">
-        <v>2059</v>
-      </c>
-      <c r="G18" s="79" t="s">
-        <v>2060</v>
-      </c>
-      <c r="H18" s="79" t="s">
-        <v>2080</v>
+      <c r="E18" s="80" t="s">
+        <v>2064</v>
+      </c>
+      <c r="F18" s="80" t="s">
+        <v>2065</v>
+      </c>
+      <c r="G18" s="80" t="s">
+        <v>2066</v>
+      </c>
+      <c r="H18" s="80" t="s">
+        <v>2086</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>2081</v>
+        <v>2087</v>
       </c>
       <c r="B19" s="6" t="n">
         <v>0</v>
@@ -19420,25 +19476,25 @@
       <c r="C19" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="E19" s="70" t="s">
-        <v>2002</v>
-      </c>
-      <c r="F19" s="70" t="n">
+      <c r="E19" s="71" t="s">
+        <v>2008</v>
+      </c>
+      <c r="F19" s="71" t="n">
         <f aca="false">C3+C26+C34+C41+C48+C55+C63+C70+C77</f>
         <v>33</v>
       </c>
-      <c r="G19" s="80" t="n">
+      <c r="G19" s="81" t="n">
         <f aca="false">F19</f>
         <v>33</v>
       </c>
-      <c r="H19" s="70" t="n">
+      <c r="H19" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F19:G19),0)</f>
         <v>33</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>2082</v>
+        <v>2088</v>
       </c>
       <c r="B20" s="6" t="n">
         <v>0</v>
@@ -19446,28 +19502,28 @@
       <c r="C20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="70" t="s">
-        <v>2063</v>
-      </c>
-      <c r="F20" s="70" t="n">
+      <c r="E20" s="71" t="s">
+        <v>2069</v>
+      </c>
+      <c r="F20" s="71" t="n">
         <f aca="false">B4+B29+B66+B71+(F19-B3)*(F11/2)</f>
         <v>209</v>
       </c>
-      <c r="G20" s="80" t="n">
+      <c r="G20" s="81" t="n">
         <f aca="false">C4+C29+C66+C71+(G19-C3)*F11+H8</f>
         <v>391</v>
       </c>
-      <c r="H20" s="70" t="n">
+      <c r="H20" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F20:G20),0)</f>
         <v>300</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>2083</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>2084</v>
+        <v>2090</v>
       </c>
       <c r="B21" s="6" t="n">
         <v>20</v>
@@ -19475,25 +19531,25 @@
       <c r="C21" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E21" s="70" t="s">
-        <v>2065</v>
-      </c>
-      <c r="F21" s="70" t="n">
+      <c r="E21" s="71" t="s">
+        <v>2071</v>
+      </c>
+      <c r="F21" s="71" t="n">
         <f aca="false">B5+B30+B81+(F19-B3)*(F12/2)</f>
         <v>147</v>
       </c>
-      <c r="G21" s="80" t="n">
+      <c r="G21" s="81" t="n">
         <f aca="false">B5+B30+B81+(F19-B3)*F12</f>
         <v>259</v>
       </c>
-      <c r="H21" s="70" t="n">
+      <c r="H21" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F21:G21),0)</f>
         <v>203</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>2085</v>
+        <v>2091</v>
       </c>
       <c r="B22" s="6" t="n">
         <v>0</v>
@@ -19501,25 +19557,25 @@
       <c r="C22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="70" t="s">
-        <v>2066</v>
-      </c>
-      <c r="F22" s="70" t="n">
+      <c r="E22" s="71" t="s">
+        <v>2072</v>
+      </c>
+      <c r="F22" s="71" t="n">
         <f aca="false">B6+B37+B50</f>
         <v>5</v>
       </c>
-      <c r="G22" s="80" t="n">
+      <c r="G22" s="81" t="n">
         <f aca="false">F22</f>
         <v>5</v>
       </c>
-      <c r="H22" s="70" t="n">
+      <c r="H22" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F22:G22),0)</f>
         <v>5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>2086</v>
+        <v>2092</v>
       </c>
       <c r="B23" s="6" t="n">
         <v>0</v>
@@ -19527,74 +19583,74 @@
       <c r="C23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E23" s="70" t="s">
-        <v>2061</v>
-      </c>
-      <c r="F23" s="70" t="n">
+      <c r="E23" s="71" t="s">
+        <v>2067</v>
+      </c>
+      <c r="F23" s="71" t="n">
         <f aca="false">B7+B36+B56+B65+ROUNDDOWN(F25/25,0)</f>
         <v>20</v>
       </c>
-      <c r="G23" s="80" t="n">
+      <c r="G23" s="81" t="n">
         <f aca="false">C7+C36+C56+C65+F8+ROUNDDOWN(G25/25,0)</f>
         <v>31</v>
       </c>
-      <c r="H23" s="70" t="n">
+      <c r="H23" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F23:G23),0)</f>
         <v>25</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>2083</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E24" s="70" t="s">
-        <v>2062</v>
-      </c>
-      <c r="F24" s="70" t="n">
+      <c r="E24" s="71" t="s">
+        <v>2068</v>
+      </c>
+      <c r="F24" s="71" t="n">
         <f aca="false">B8+B42+B57+ROUNDDOWN(F29/25,0)</f>
         <v>17</v>
       </c>
-      <c r="G24" s="80" t="n">
+      <c r="G24" s="81" t="n">
         <f aca="false">C8+C42+C57+G8+ROUNDDOWN(G29/25,0)</f>
         <v>27</v>
       </c>
-      <c r="H24" s="70" t="n">
+      <c r="H24" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F24:G24),0)</f>
         <v>22</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>2083</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E25" s="70" t="s">
-        <v>2068</v>
-      </c>
-      <c r="F25" s="70" t="n">
+        <v>2066</v>
+      </c>
+      <c r="E25" s="71" t="s">
+        <v>2074</v>
+      </c>
+      <c r="F25" s="71" t="n">
         <f aca="false">B9+B44+B64</f>
         <v>25</v>
       </c>
-      <c r="G25" s="80" t="n">
+      <c r="G25" s="81" t="n">
         <f aca="false">C9+C44+C64</f>
         <v>30</v>
       </c>
-      <c r="H25" s="70" t="n">
+      <c r="H25" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F25:G25),0)</f>
         <v>27</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="B26" s="6" t="n">
         <v>4</v>
@@ -19602,25 +19658,25 @@
       <c r="C26" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="70" t="s">
-        <v>1791</v>
-      </c>
-      <c r="F26" s="70" t="n">
+      <c r="E26" s="71" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F26" s="71" t="n">
         <f aca="false">B10+B78</f>
         <v>15</v>
       </c>
-      <c r="G26" s="80" t="n">
+      <c r="G26" s="81" t="n">
         <f aca="false">C10+C78</f>
         <v>25</v>
       </c>
-      <c r="H26" s="70" t="n">
+      <c r="H26" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F26:G26),0)</f>
         <v>20</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>2073</v>
+        <v>2079</v>
       </c>
       <c r="B27" s="6" t="n">
         <v>10</v>
@@ -19628,25 +19684,25 @@
       <c r="C27" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="E27" s="70" t="s">
-        <v>2069</v>
-      </c>
-      <c r="F27" s="70" t="n">
+      <c r="E27" s="71" t="s">
+        <v>2075</v>
+      </c>
+      <c r="F27" s="71" t="n">
         <f aca="false">B11+B79</f>
         <v>30</v>
       </c>
-      <c r="G27" s="80" t="n">
+      <c r="G27" s="81" t="n">
         <f aca="false">C11+C79</f>
         <v>35</v>
       </c>
-      <c r="H27" s="70" t="n">
+      <c r="H27" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F27:G27),0)</f>
         <v>32</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>2081</v>
+        <v>2087</v>
       </c>
       <c r="B28" s="6" t="n">
         <v>20</v>
@@ -19654,25 +19710,25 @@
       <c r="C28" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="E28" s="70" t="s">
-        <v>2071</v>
-      </c>
-      <c r="F28" s="70" t="n">
+      <c r="E28" s="71" t="s">
+        <v>2077</v>
+      </c>
+      <c r="F28" s="71" t="n">
         <f aca="false">B12+B49</f>
         <v>145</v>
       </c>
-      <c r="G28" s="80" t="n">
+      <c r="G28" s="81" t="n">
         <f aca="false">C12+C49</f>
         <v>160</v>
       </c>
-      <c r="H28" s="70" t="n">
+      <c r="H28" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F28:G28),0)</f>
         <v>152</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>2063</v>
+        <v>2069</v>
       </c>
       <c r="B29" s="6" t="n">
         <v>18</v>
@@ -19680,25 +19736,25 @@
       <c r="C29" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="E29" s="70" t="s">
-        <v>2073</v>
-      </c>
-      <c r="F29" s="70" t="n">
+      <c r="E29" s="71" t="s">
+        <v>2079</v>
+      </c>
+      <c r="F29" s="71" t="n">
         <f aca="false">B13+B27+B58</f>
         <v>22</v>
       </c>
-      <c r="G29" s="80" t="n">
+      <c r="G29" s="81" t="n">
         <f aca="false">C13+C27+C58</f>
         <v>30</v>
       </c>
-      <c r="H29" s="70" t="n">
+      <c r="H29" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F29:G29),0)</f>
         <v>26</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>2065</v>
+        <v>2071</v>
       </c>
       <c r="B30" s="6" t="n">
         <v>5</v>
@@ -19706,52 +19762,52 @@
       <c r="C30" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E30" s="70" t="s">
-        <v>2074</v>
-      </c>
-      <c r="F30" s="70" t="n">
+      <c r="E30" s="71" t="s">
+        <v>2080</v>
+      </c>
+      <c r="F30" s="71" t="n">
         <f aca="false">B14+B59+B80</f>
         <v>25</v>
       </c>
-      <c r="G30" s="80" t="n">
+      <c r="G30" s="81" t="n">
         <f aca="false">C14+C59+C80</f>
         <v>70</v>
       </c>
-      <c r="H30" s="70" t="n">
+      <c r="H30" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F30:G30),0)</f>
         <v>47</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E31" s="70" t="s">
-        <v>2075</v>
-      </c>
-      <c r="F31" s="70" t="n">
+      <c r="E31" s="71" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F31" s="71" t="n">
         <f aca="false">B15</f>
         <v>15</v>
       </c>
-      <c r="G31" s="80" t="n">
+      <c r="G31" s="81" t="n">
         <f aca="false">C15</f>
         <v>95</v>
       </c>
-      <c r="H31" s="70" t="n">
+      <c r="H31" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F31:G31),0)</f>
         <v>55</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E32" s="70" t="s">
-        <v>2076</v>
-      </c>
-      <c r="F32" s="70" t="n">
+      <c r="E32" s="71" t="s">
+        <v>2082</v>
+      </c>
+      <c r="F32" s="71" t="n">
         <f aca="false">B16+B35+B43+B51</f>
         <v>15</v>
       </c>
-      <c r="G32" s="80" t="n">
+      <c r="G32" s="81" t="n">
         <f aca="false">C16+C35+C43+C51</f>
         <v>15</v>
       </c>
-      <c r="H32" s="70" t="n">
+      <c r="H32" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F32:G32),0)</f>
         <v>15</v>
       </c>
@@ -19761,28 +19817,28 @@
         <v>864</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E33" s="70" t="s">
-        <v>2077</v>
-      </c>
-      <c r="F33" s="70" t="n">
+        <v>2066</v>
+      </c>
+      <c r="E33" s="71" t="s">
+        <v>2083</v>
+      </c>
+      <c r="F33" s="71" t="n">
         <v>30</v>
       </c>
-      <c r="G33" s="80" t="n">
+      <c r="G33" s="81" t="n">
         <v>85</v>
       </c>
-      <c r="H33" s="70" t="n">
+      <c r="H33" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F33:G33),0)</f>
         <v>57</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="B34" s="6" t="n">
         <v>4</v>
@@ -19790,23 +19846,23 @@
       <c r="C34" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E34" s="70" t="s">
-        <v>2079</v>
-      </c>
-      <c r="F34" s="70" t="n">
+      <c r="E34" s="71" t="s">
+        <v>2085</v>
+      </c>
+      <c r="F34" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="80" t="n">
+      <c r="G34" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="H34" s="70" t="n">
+      <c r="H34" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F34:G34),0)</f>
         <v>12</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>2076</v>
+        <v>2082</v>
       </c>
       <c r="B35" s="6" t="n">
         <v>5</v>
@@ -19814,24 +19870,24 @@
       <c r="C35" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E35" s="70" t="s">
-        <v>2081</v>
-      </c>
-      <c r="F35" s="70" t="n">
+      <c r="E35" s="71" t="s">
+        <v>2087</v>
+      </c>
+      <c r="F35" s="71" t="n">
         <f aca="false">B19+B28</f>
         <v>20</v>
       </c>
-      <c r="G35" s="80" t="n">
+      <c r="G35" s="81" t="n">
         <v>99</v>
       </c>
-      <c r="H35" s="70" t="n">
+      <c r="H35" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F35:G35),0)</f>
         <v>59</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>2061</v>
+        <v>2067</v>
       </c>
       <c r="B36" s="6" t="n">
         <v>4</v>
@@ -19839,24 +19895,24 @@
       <c r="C36" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E36" s="70" t="s">
-        <v>2082</v>
-      </c>
-      <c r="F36" s="70" t="n">
+      <c r="E36" s="71" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F36" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="80" t="n">
+      <c r="G36" s="81" t="n">
         <f aca="false">C20+C82</f>
         <v>5</v>
       </c>
-      <c r="H36" s="70" t="n">
+      <c r="H36" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F36:G36),0)</f>
         <v>2</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>2066</v>
+        <v>2072</v>
       </c>
       <c r="B37" s="6" t="n">
         <v>1</v>
@@ -19864,50 +19920,50 @@
       <c r="C37" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E37" s="70" t="s">
-        <v>2084</v>
-      </c>
-      <c r="F37" s="70" t="n">
+      <c r="E37" s="71" t="s">
+        <v>2090</v>
+      </c>
+      <c r="F37" s="71" t="n">
         <v>20</v>
       </c>
-      <c r="G37" s="80" t="n">
+      <c r="G37" s="81" t="n">
         <v>60</v>
       </c>
-      <c r="H37" s="70" t="n">
+      <c r="H37" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F37:G37),0)</f>
         <v>40</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E38" s="70" t="s">
-        <v>2085</v>
-      </c>
-      <c r="F38" s="70" t="n">
+      <c r="E38" s="71" t="s">
+        <v>2091</v>
+      </c>
+      <c r="F38" s="71" t="n">
         <f aca="false">B22+B45+B60+B84</f>
         <v>3</v>
       </c>
-      <c r="G38" s="80" t="n">
+      <c r="G38" s="81" t="n">
         <f aca="false">F38</f>
         <v>3</v>
       </c>
-      <c r="H38" s="70" t="n">
+      <c r="H38" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F38:G38),0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E39" s="70" t="s">
-        <v>2086</v>
-      </c>
-      <c r="F39" s="70" t="n">
+      <c r="E39" s="71" t="s">
+        <v>2092</v>
+      </c>
+      <c r="F39" s="71" t="n">
         <f aca="false">B23+B67+B72+B83</f>
         <v>3</v>
       </c>
-      <c r="G39" s="80" t="n">
+      <c r="G39" s="81" t="n">
         <f aca="false">F39</f>
         <v>3</v>
       </c>
-      <c r="H39" s="70" t="n">
+      <c r="H39" s="71" t="n">
         <f aca="false">ROUNDDOWN(AVERAGE(F39:G39),0)</f>
         <v>3</v>
       </c>
@@ -19917,15 +19973,15 @@
         <v>880</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>2060</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="B41" s="6" t="n">
         <v>4</v>
@@ -19936,7 +19992,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>2062</v>
+        <v>2068</v>
       </c>
       <c r="B42" s="6" t="n">
         <v>13</v>
@@ -19947,7 +20003,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>2076</v>
+        <v>2082</v>
       </c>
       <c r="B43" s="6" t="n">
         <v>5</v>
@@ -19958,7 +20014,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>2068</v>
+        <v>2074</v>
       </c>
       <c r="B44" s="6" t="n">
         <v>10</v>
@@ -19969,7 +20025,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>2085</v>
+        <v>2091</v>
       </c>
       <c r="B45" s="6" t="n">
         <v>1</v>
@@ -19980,18 +20036,18 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>2060</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="B48" s="6" t="n">
         <v>4</v>
@@ -20002,7 +20058,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>2071</v>
+        <v>2077</v>
       </c>
       <c r="B49" s="6" t="n">
         <v>10</v>
@@ -20013,7 +20069,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>2066</v>
+        <v>2072</v>
       </c>
       <c r="B50" s="6" t="n">
         <v>1</v>
@@ -20024,7 +20080,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>2076</v>
+        <v>2082</v>
       </c>
       <c r="B51" s="6" t="n">
         <v>5</v>
@@ -20035,18 +20091,18 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>2021</v>
+        <v>2027</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2060</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="B55" s="6" t="n">
         <v>4</v>
@@ -20057,7 +20113,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>2061</v>
+        <v>2067</v>
       </c>
       <c r="B56" s="6" t="n">
         <v>4</v>
@@ -20068,7 +20124,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>2062</v>
+        <v>2068</v>
       </c>
       <c r="B57" s="6" t="n">
         <v>4</v>
@@ -20079,7 +20135,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>2073</v>
+        <v>2079</v>
       </c>
       <c r="B58" s="6" t="n">
         <v>10</v>
@@ -20090,7 +20146,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>2074</v>
+        <v>2080</v>
       </c>
       <c r="B59" s="6" t="n">
         <v>10</v>
@@ -20101,7 +20157,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>2085</v>
+        <v>2091</v>
       </c>
       <c r="B60" s="6" t="n">
         <v>1</v>
@@ -20112,18 +20168,18 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>2023</v>
+        <v>2029</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>2060</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="B63" s="6" t="n">
         <v>4</v>
@@ -20134,7 +20190,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>2068</v>
+        <v>2074</v>
       </c>
       <c r="B64" s="6" t="n">
         <v>10</v>
@@ -20145,7 +20201,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>2061</v>
+        <v>2067</v>
       </c>
       <c r="B65" s="6" t="n">
         <v>9</v>
@@ -20156,7 +20212,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>2063</v>
+        <v>2069</v>
       </c>
       <c r="B66" s="6" t="n">
         <v>10</v>
@@ -20167,7 +20223,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>2086</v>
+        <v>2092</v>
       </c>
       <c r="B67" s="6" t="n">
         <v>1</v>
@@ -20178,18 +20234,18 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>2087</v>
+        <v>2093</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>2060</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="B70" s="6" t="n">
         <v>3</v>
@@ -20200,7 +20256,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>2063</v>
+        <v>2069</v>
       </c>
       <c r="B71" s="6" t="n">
         <v>15</v>
@@ -20211,7 +20267,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>2086</v>
+        <v>2092</v>
       </c>
       <c r="B72" s="6" t="n">
         <v>1</v>
@@ -20222,18 +20278,18 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>2088</v>
+        <v>2094</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>2060</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="B77" s="6" t="n">
         <v>5</v>
@@ -20244,7 +20300,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>1791</v>
+        <v>1797</v>
       </c>
       <c r="B78" s="6" t="n">
         <v>10</v>
@@ -20255,7 +20311,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>2069</v>
+        <v>2075</v>
       </c>
       <c r="B79" s="6" t="n">
         <v>10</v>
@@ -20266,7 +20322,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>2074</v>
+        <v>2080</v>
       </c>
       <c r="B80" s="6" t="n">
         <v>10</v>
@@ -20277,7 +20333,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>2065</v>
+        <v>2071</v>
       </c>
       <c r="B81" s="6" t="n">
         <v>25</v>
@@ -20288,7 +20344,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>2089</v>
+        <v>2095</v>
       </c>
       <c r="B82" s="6" t="n">
         <v>5</v>
@@ -20299,7 +20355,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>2086</v>
+        <v>2092</v>
       </c>
       <c r="B83" s="6" t="n">
         <v>1</v>
@@ -20310,7 +20366,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>2085</v>
+        <v>2091</v>
       </c>
       <c r="B84" s="6" t="n">
         <v>1</v>
@@ -20345,55 +20401,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2090</v>
+        <v>2096</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2091</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>2092</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>2093</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2094</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2095</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2096</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>2097</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>2098</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>2099</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>2100</v>
+        <v>2106</v>
       </c>
     </row>
   </sheetData>
@@ -20939,10 +20995,10 @@
         <v>484</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2101</v>
+        <v>2107</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2102</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20950,7 +21006,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2103</v>
+        <v>2109</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>992</v>
@@ -20962,7 +21018,7 @@
         <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>2104</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20970,7 +21026,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2105</v>
+        <v>2111</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>992</v>
@@ -20982,7 +21038,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>2106</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20990,7 +21046,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2107</v>
+        <v>2113</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>992</v>
@@ -20999,7 +21055,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>2108</v>
+        <v>2114</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>1092</v>
@@ -21037,189 +21093,189 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2109</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>2110</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2111</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2112</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>2116</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>2119</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>2120</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>2122</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>2123</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>2124</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>2126</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>2127</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>2128</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>2129</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>2130</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>2131</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>2132</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>2133</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>2134</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>2135</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>2136</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>2137</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>2138</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>2139</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>2140</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>2141</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>2142</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>2143</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>2144</v>
+        <v>2150</v>
       </c>
     </row>
   </sheetData>
@@ -21246,197 +21302,197 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="78" t="s">
-        <v>2145</v>
-      </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="E1" s="78" t="s">
-        <v>2146</v>
-      </c>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="J1" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
+      <c r="A1" s="79" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="E1" s="79" t="s">
+        <v>2152</v>
+      </c>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="J1" s="79" t="s">
+        <v>2153</v>
+      </c>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="82" t="s">
         <v>834</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="82" t="s">
         <v>485</v>
       </c>
-      <c r="C2" s="81" t="s">
-        <v>2148</v>
-      </c>
-      <c r="E2" s="81" t="s">
+      <c r="C2" s="82" t="s">
+        <v>2154</v>
+      </c>
+      <c r="E2" s="82" t="s">
         <v>834</v>
       </c>
-      <c r="F2" s="81" t="s">
+      <c r="F2" s="82" t="s">
         <v>485</v>
       </c>
-      <c r="G2" s="81" t="s">
-        <v>2148</v>
-      </c>
-      <c r="H2" s="81" t="s">
+      <c r="G2" s="82" t="s">
+        <v>2154</v>
+      </c>
+      <c r="H2" s="82" t="s">
         <v>1447</v>
       </c>
-      <c r="J2" s="81" t="s">
+      <c r="J2" s="82" t="s">
         <v>834</v>
       </c>
-      <c r="K2" s="81" t="s">
-        <v>2149</v>
-      </c>
-      <c r="L2" s="81" t="s">
-        <v>2148</v>
+      <c r="K2" s="82" t="s">
+        <v>2155</v>
+      </c>
+      <c r="L2" s="82" t="s">
+        <v>2154</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="81" t="n">
+      <c r="A3" s="82" t="n">
         <v>73</v>
       </c>
-      <c r="B3" s="81" t="s">
-        <v>2150</v>
-      </c>
-      <c r="C3" s="81" t="n">
+      <c r="B3" s="82" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C3" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="81" t="s">
-        <v>2151</v>
-      </c>
-      <c r="F3" s="81" t="s">
-        <v>2152</v>
-      </c>
-      <c r="G3" s="81" t="n">
+      <c r="E3" s="82" t="s">
+        <v>2157</v>
+      </c>
+      <c r="F3" s="82" t="s">
+        <v>2158</v>
+      </c>
+      <c r="G3" s="82" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="81" t="s">
-        <v>2153</v>
-      </c>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
+      <c r="H3" s="82" t="s">
+        <v>2159</v>
+      </c>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="81" t="n">
+      <c r="A4" s="82" t="n">
         <v>98</v>
       </c>
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="82" t="s">
         <v>937</v>
       </c>
-      <c r="C4" s="81" t="n">
+      <c r="C4" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="81"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+      <c r="L4" s="82"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="81" t="n">
+      <c r="A5" s="82" t="n">
         <v>106</v>
       </c>
-      <c r="B5" s="81" t="s">
-        <v>2154</v>
-      </c>
-      <c r="C5" s="81" t="n">
+      <c r="B5" s="82" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C5" s="82" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+      <c r="L5" s="82"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="81" t="n">
+      <c r="A6" s="82" t="n">
         <v>107</v>
       </c>
-      <c r="B6" s="81" t="s">
-        <v>2155</v>
-      </c>
-      <c r="C6" s="81" t="n">
+      <c r="B6" s="82" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C6" s="82" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="81" t="n">
+      <c r="A7" s="82" t="n">
         <v>108</v>
       </c>
-      <c r="B7" s="81" t="s">
-        <v>2156</v>
-      </c>
-      <c r="C7" s="81" t="n">
+      <c r="B7" s="82" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C7" s="82" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="81" t="n">
+      <c r="A8" s="82" t="n">
         <v>109</v>
       </c>
-      <c r="B8" s="81" t="s">
-        <v>2157</v>
-      </c>
-      <c r="C8" s="81" t="n">
+      <c r="B8" s="82" t="s">
+        <v>2163</v>
+      </c>
+      <c r="C8" s="82" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="J8" s="81"/>
-      <c r="K8" s="81"/>
-      <c r="L8" s="81"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="82"/>
+      <c r="L8" s="82"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="81" t="n">
+      <c r="A9" s="82" t="n">
         <v>110</v>
       </c>
-      <c r="B9" s="81" t="s">
-        <v>2158</v>
-      </c>
-      <c r="C9" s="81" t="n">
+      <c r="B9" s="82" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C9" s="82" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="81"/>
-      <c r="J9" s="81"/>
-      <c r="K9" s="81"/>
-      <c r="L9" s="81"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="82"/>
+      <c r="L9" s="82"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="81" t="n">
+      <c r="A10" s="82" t="n">
         <v>111</v>
       </c>
-      <c r="B10" s="81" t="s">
-        <v>2159</v>
-      </c>
-      <c r="C10" s="81" t="n">
+      <c r="B10" s="82" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C10" s="82" t="n">
         <v>7</v>
       </c>
     </row>

--- a/AmbermoonAdvanced.xlsx
+++ b/AmbermoonAdvanced.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="Neue Daten Ep3" sheetId="1" state="visible" r:id="rId3"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3008" uniqueCount="2174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3014" uniqueCount="2178">
   <si>
     <t xml:space="preserve">Map texts</t>
   </si>
@@ -3489,6 +3489,12 @@
     <t xml:space="preserve">Ancient city</t>
   </si>
   <si>
+    <t xml:space="preserve">Ancient temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sabotage Airship</t>
+  </si>
+  <si>
     <t xml:space="preserve">World map</t>
   </si>
   <si>
@@ -5216,6 +5222,12 @@
   </si>
   <si>
     <t xml:space="preserve">Screen lower left building on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ship’s wheel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy of object gfx 145</t>
   </si>
   <si>
     <t xml:space="preserve">Floors</t>
@@ -9613,7 +9625,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="12.60546875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="12.29"/>
@@ -9782,6 +9794,22 @@
       </c>
       <c r="B10" s="6" t="s">
         <v>1100</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -9826,10 +9854,10 @@
         <v>45</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="F2" s="22"/>
       <c r="G2" s="21"/>
@@ -9840,10 +9868,10 @@
         <v>57</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="F3" s="20"/>
     </row>
@@ -9852,10 +9880,10 @@
         <v>71</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="F4" s="20"/>
     </row>
@@ -9864,10 +9892,10 @@
         <v>77</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="F5" s="20"/>
       <c r="G5" s="21"/>
@@ -9878,10 +9906,10 @@
         <v>112</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="F6" s="22"/>
       <c r="G6" s="21"/>
@@ -9892,10 +9920,10 @@
         <v>117</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="F7" s="20"/>
       <c r="G7" s="21"/>
@@ -9906,10 +9934,10 @@
         <v>118</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="F8" s="20"/>
       <c r="G8" s="21"/>
@@ -9920,10 +9948,10 @@
         <v>135</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="F9" s="20"/>
       <c r="G9" s="21"/>
@@ -9934,10 +9962,10 @@
         <v>139</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="F10" s="20"/>
       <c r="G10" s="21"/>
@@ -9948,10 +9976,10 @@
         <v>157</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="F11" s="20"/>
       <c r="G11" s="21"/>
@@ -9962,10 +9990,10 @@
         <v>163</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="G12" s="21"/>
       <c r="H12" s="1"/>
@@ -9975,10 +10003,10 @@
         <v>198</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="F13" s="20"/>
       <c r="G13" s="21"/>
@@ -9989,10 +10017,10 @@
         <v>203</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="F14" s="22"/>
       <c r="G14" s="21"/>
@@ -10003,10 +10031,10 @@
         <v>244</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="F15" s="20"/>
       <c r="G15" s="21"/>
@@ -10017,10 +10045,10 @@
         <v>249</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="F16" s="20"/>
     </row>
@@ -10029,10 +10057,10 @@
         <v>257</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="F17" s="20"/>
     </row>
@@ -10041,10 +10069,10 @@
         <v>258</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="F18" s="20"/>
       <c r="G18" s="21"/>
@@ -10055,10 +10083,10 @@
         <v>259</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="F19" s="20"/>
       <c r="G19" s="21"/>
@@ -10069,10 +10097,10 @@
         <v>262</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="F20" s="20"/>
       <c r="H20" s="1"/>
@@ -10085,7 +10113,7 @@
         <v>1087</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="F21" s="20"/>
       <c r="H21" s="1"/>
@@ -10095,10 +10123,10 @@
         <v>273</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="F22" s="22"/>
       <c r="H22" s="1"/>
@@ -10108,10 +10136,10 @@
         <v>421</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
     </row>
   </sheetData>
@@ -10145,7 +10173,7 @@
         <v>489</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>484</v>
@@ -10156,13 +10184,13 @@
         <v>36</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10170,13 +10198,13 @@
         <v>37</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10184,10 +10212,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10195,10 +10223,10 @@
         <v>39</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10206,13 +10234,13 @@
         <v>40</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10220,13 +10248,13 @@
         <v>41</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10234,13 +10262,13 @@
         <v>42</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10248,13 +10276,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10262,13 +10290,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>1149</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>1147</v>
-      </c>
       <c r="D10" s="6" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10276,13 +10304,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10290,13 +10318,13 @@
         <v>46</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10304,13 +10332,13 @@
         <v>47</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10318,13 +10346,13 @@
         <v>71</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10332,13 +10360,13 @@
         <v>72</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10346,13 +10374,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10360,13 +10388,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10374,13 +10402,13 @@
         <v>75</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>1172</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>1170</v>
-      </c>
       <c r="D18" s="6" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10388,10 +10416,10 @@
         <v>76</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10399,13 +10427,13 @@
         <v>77</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="M20" s="23"/>
       <c r="N20" s="23"/>
@@ -10416,19 +10444,19 @@
         <v>78</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>11</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10436,19 +10464,19 @@
         <v>79</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>19</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
     </row>
   </sheetData>
@@ -10485,13 +10513,13 @@
         <v>488</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="F1" s="13"/>
     </row>
@@ -10500,16 +10528,16 @@
         <v>132</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>488</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>495</v>
@@ -10520,19 +10548,19 @@
         <v>133</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="E3" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10540,19 +10568,19 @@
         <v>134</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10560,19 +10588,19 @@
         <v>135</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>124</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10580,19 +10608,19 @@
         <v>136</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>84</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10600,19 +10628,19 @@
         <v>137</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>27</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10620,19 +10648,19 @@
         <v>138</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>104</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10640,19 +10668,19 @@
         <v>139</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>45</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10660,10 +10688,10 @@
         <v>140</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10671,10 +10699,10 @@
         <v>141</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10682,10 +10710,10 @@
         <v>142</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10693,10 +10721,10 @@
         <v>143</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10704,10 +10732,10 @@
         <v>144</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10715,10 +10743,10 @@
         <v>145</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10726,13 +10754,13 @@
         <v>146</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="F16" s="13"/>
     </row>
@@ -10741,22 +10769,22 @@
         <v>147</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>488</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10764,22 +10792,22 @@
         <v>148</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>252</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>384</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10787,10 +10815,10 @@
         <v>149</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10798,10 +10826,10 @@
         <v>150</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10809,13 +10837,13 @@
         <v>151</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F21" s="13"/>
     </row>
@@ -10824,13 +10852,13 @@
         <v>152</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10838,13 +10866,13 @@
         <v>153</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10852,13 +10880,13 @@
         <v>154</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10866,13 +10894,13 @@
         <v>155</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10880,10 +10908,10 @@
         <v>156</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10891,10 +10919,10 @@
         <v>157</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10902,10 +10930,10 @@
         <v>158</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10913,10 +10941,10 @@
         <v>159</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10924,10 +10952,10 @@
         <v>160</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10935,10 +10963,10 @@
         <v>161</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10946,10 +10974,10 @@
         <v>162</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10957,10 +10985,10 @@
         <v>163</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10968,10 +10996,10 @@
         <v>164</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10979,10 +11007,10 @@
         <v>165</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10990,10 +11018,10 @@
         <v>166</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11001,10 +11029,10 @@
         <v>167</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11012,10 +11040,10 @@
         <v>168</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11023,10 +11051,10 @@
         <v>169</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11034,10 +11062,10 @@
         <v>170</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11045,10 +11073,10 @@
         <v>171</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11056,10 +11084,10 @@
         <v>172</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11067,10 +11095,10 @@
         <v>173</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11078,10 +11106,10 @@
         <v>174</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11089,10 +11117,10 @@
         <v>175</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11100,10 +11128,10 @@
         <v>176</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11111,10 +11139,10 @@
         <v>177</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11122,10 +11150,10 @@
         <v>178</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11133,10 +11161,10 @@
         <v>179</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11144,10 +11172,10 @@
         <v>180</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11155,10 +11183,10 @@
         <v>181</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11166,10 +11194,10 @@
         <v>182</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11177,10 +11205,10 @@
         <v>183</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11188,10 +11216,10 @@
         <v>184</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11199,10 +11227,10 @@
         <v>185</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11210,10 +11238,10 @@
         <v>186</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11221,10 +11249,10 @@
         <v>187</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11232,10 +11260,10 @@
         <v>188</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11243,10 +11271,10 @@
         <v>189</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11254,10 +11282,10 @@
         <v>190</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11265,10 +11293,10 @@
         <v>191</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11276,10 +11304,10 @@
         <v>192</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11287,10 +11315,10 @@
         <v>193</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11298,10 +11326,10 @@
         <v>194</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11309,10 +11337,10 @@
         <v>195</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11320,10 +11348,10 @@
         <v>196</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11331,10 +11359,10 @@
         <v>197</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11342,10 +11370,10 @@
         <v>198</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11353,10 +11381,10 @@
         <v>199</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11364,10 +11392,10 @@
         <v>200</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11375,10 +11403,10 @@
         <v>201</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11386,527 +11414,527 @@
         <v>202</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="24" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="24" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="24" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="24" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="24" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="24" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="24" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>1311</v>
       </c>
-      <c r="B79" s="6" t="s">
-        <v>1309</v>
-      </c>
       <c r="C79" s="6" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="24" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="24" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="24" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="24" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="24" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="24" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B85" s="6" t="s">
         <v>1324</v>
       </c>
-      <c r="B85" s="6" t="s">
-        <v>1322</v>
-      </c>
       <c r="C85" s="6" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="24" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="24" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="24" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="24" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="24" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="24" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B91" s="6" t="s">
         <v>1340</v>
       </c>
-      <c r="B91" s="6" t="s">
-        <v>1338</v>
-      </c>
       <c r="C91" s="6" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="24" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="24" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="24" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="24" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="24" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="24" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="24" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B98" s="6" t="s">
         <v>1355</v>
       </c>
-      <c r="B98" s="6" t="s">
-        <v>1353</v>
-      </c>
       <c r="C98" s="6" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="24" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="24" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="24" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="24" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="24" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="24" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="24" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="24" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B106" s="6" t="s">
         <v>1375</v>
       </c>
-      <c r="B106" s="6" t="s">
-        <v>1373</v>
-      </c>
       <c r="C106" s="6" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="24" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="24" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="24" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="24" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="24" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="24" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B112" s="6" t="s">
         <v>1386</v>
       </c>
-      <c r="B112" s="6" t="s">
-        <v>1384</v>
-      </c>
       <c r="C112" s="6" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="24" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="24" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="24" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="24" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="24" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="24" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="24" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
     </row>
   </sheetData>
@@ -11938,7 +11966,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>484</v>
@@ -11949,7 +11977,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11957,7 +11985,7 @@
         <v>40</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11965,7 +11993,7 @@
         <v>41</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11973,7 +12001,7 @@
         <v>42</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11981,7 +12009,7 @@
         <v>43</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11989,7 +12017,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11997,7 +12025,7 @@
         <v>45</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12005,7 +12033,7 @@
         <v>46</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12013,7 +12041,7 @@
         <v>47</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12021,7 +12049,7 @@
         <v>48</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12029,7 +12057,7 @@
         <v>49</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12037,7 +12065,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12045,7 +12073,7 @@
         <v>51</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12053,7 +12081,7 @@
         <v>52</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12061,7 +12089,7 @@
         <v>53</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12069,7 +12097,7 @@
         <v>54</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12077,7 +12105,7 @@
         <v>55</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12085,7 +12113,7 @@
         <v>56</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12093,7 +12121,7 @@
         <v>57</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12101,7 +12129,7 @@
         <v>58</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12109,7 +12137,7 @@
         <v>59</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12117,7 +12145,7 @@
         <v>60</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12125,7 +12153,7 @@
         <v>61</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12133,7 +12161,7 @@
         <v>62</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12141,7 +12169,7 @@
         <v>63</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12149,7 +12177,7 @@
         <v>64</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12157,7 +12185,7 @@
         <v>65</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12165,7 +12193,7 @@
         <v>66</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12173,7 +12201,7 @@
         <v>67</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12181,7 +12209,7 @@
         <v>68</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12189,7 +12217,7 @@
         <v>69</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12197,7 +12225,7 @@
         <v>70</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
     </row>
   </sheetData>
@@ -12226,13 +12254,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>490</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12240,10 +12268,10 @@
         <v>66</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12251,10 +12279,10 @@
         <v>67</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12262,10 +12290,10 @@
         <v>68</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12273,10 +12301,10 @@
         <v>69</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12284,10 +12312,10 @@
         <v>70</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12295,10 +12323,10 @@
         <v>71</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12306,10 +12334,10 @@
         <v>72</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12317,10 +12345,10 @@
         <v>73</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12342,7 +12370,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12350,10 +12378,10 @@
         <v>76</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12361,21 +12389,21 @@
         <v>77</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12383,10 +12411,10 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12394,10 +12422,10 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12405,10 +12433,10 @@
         <v>21</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12424,10 +12452,10 @@
         <v>23</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12435,10 +12463,10 @@
         <v>24</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12451,7 +12479,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12459,10 +12487,10 @@
         <v>11</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12470,10 +12498,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12481,10 +12509,10 @@
         <v>32</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
     </row>
   </sheetData>
@@ -12511,26 +12539,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
     </row>
   </sheetData>
@@ -12566,80 +12594,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="F1" s="27"/>
       <c r="G1" s="27"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="G4" s="30" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="I4" s="31" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="J4" s="30" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="K4" s="31" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="L4" s="30" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="M4" s="31" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="N4" s="32" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>1486</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>1484</v>
-      </c>
       <c r="E5" s="33" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="F5" s="34" t="n">
         <v>75</v>
@@ -12674,13 +12702,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="F6" s="34" t="n">
         <v>150</v>
@@ -12715,13 +12743,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="F7" s="34" t="n">
         <v>180</v>
@@ -12756,13 +12784,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="F8" s="34" t="n">
         <v>100</v>
@@ -12797,13 +12825,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="F9" s="34" t="n">
         <v>125</v>
@@ -12838,13 +12866,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F10" s="34" t="n">
         <v>90</v>
@@ -12879,10 +12907,10 @@
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="E11" s="33" t="s">
         <v>17</v>
@@ -12920,13 +12948,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="F12" s="34" t="n">
         <v>90</v>
@@ -12961,13 +12989,13 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="F13" s="34" t="n">
         <v>95</v>
@@ -13002,13 +13030,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="F14" s="40" t="n">
         <v>32767</v>
@@ -13043,58 +13071,58 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="I17" s="44" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="J17" s="44" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="K17" s="30" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="F18" s="45" t="n">
         <v>75</v>
@@ -13121,13 +13149,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="E19" s="36" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="F19" s="45" t="n">
         <v>59850</v>
@@ -13154,13 +13182,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="F20" s="45" t="n">
         <v>150</v>
@@ -13187,7 +13215,7 @@
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E21" s="36" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="F21" s="45" t="n">
         <v>600</v>
@@ -13214,7 +13242,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E22" s="36" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="F22" s="45" t="n">
         <v>950</v>
@@ -13241,7 +13269,7 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E23" s="36" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="F23" s="45" t="n">
         <v>1890</v>
@@ -13268,7 +13296,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E24" s="36" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="F24" s="45" t="n">
         <v>4500</v>
@@ -13295,7 +13323,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E25" s="36" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="F25" s="45" t="n">
         <v>12240</v>
@@ -13322,7 +13350,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E26" s="36" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="F26" s="45" t="n">
         <v>29250</v>
@@ -13349,7 +13377,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E27" s="42" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="F27" s="47" t="n">
         <v>113400</v>
@@ -13499,7 +13527,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
     </row>
   </sheetData>
@@ -13529,7 +13557,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="49" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="B1" s="50" t="s">
         <v>484</v>
@@ -13538,10 +13566,10 @@
         <v>1075</v>
       </c>
       <c r="D1" s="50" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="E1" s="51" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13549,16 +13577,16 @@
         <v>39</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13566,16 +13594,16 @@
         <v>153</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13583,16 +13611,16 @@
         <v>86</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13600,16 +13628,16 @@
         <v>154</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13617,16 +13645,16 @@
         <v>374</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13634,16 +13662,16 @@
         <v>375</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>997</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13651,16 +13679,16 @@
         <v>376</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1090</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13668,16 +13696,16 @@
         <v>377</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>1084</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13685,16 +13713,16 @@
         <v>378</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>1084</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13702,16 +13730,16 @@
         <v>379</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>1084</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13719,16 +13747,16 @@
         <v>380</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13736,16 +13764,16 @@
         <v>381</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13753,16 +13781,16 @@
         <v>382</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13770,16 +13798,16 @@
         <v>383</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>1559</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>1557</v>
-      </c>
       <c r="D15" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13787,16 +13815,16 @@
         <v>384</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13804,16 +13832,16 @@
         <v>385</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13821,16 +13849,16 @@
         <v>386</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13838,16 +13866,16 @@
         <v>387</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>1092</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13855,16 +13883,16 @@
         <v>388</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>1092</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13872,16 +13900,16 @@
         <v>389</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>1092</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13889,16 +13917,16 @@
         <v>390</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>1092</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13906,16 +13934,16 @@
         <v>391</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13923,16 +13951,16 @@
         <v>392</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13940,16 +13968,16 @@
         <v>393</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13957,16 +13985,16 @@
         <v>394</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13974,16 +14002,16 @@
         <v>395</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13994,13 +14022,13 @@
         <v>924</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14008,16 +14036,16 @@
         <v>397</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14025,16 +14053,16 @@
         <v>398</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14042,16 +14070,16 @@
         <v>399</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14059,16 +14087,16 @@
         <v>400</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14076,13 +14104,13 @@
         <v>401</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14090,16 +14118,16 @@
         <v>402</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14107,13 +14135,13 @@
         <v>403</v>
       </c>
       <c r="B35" s="6" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>1595</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>1593</v>
-      </c>
       <c r="D35" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14121,13 +14149,13 @@
         <v>404</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14135,13 +14163,13 @@
         <v>405</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14149,13 +14177,13 @@
         <v>406</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14163,13 +14191,13 @@
         <v>407</v>
       </c>
       <c r="B39" s="6" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>1600</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>1598</v>
-      </c>
       <c r="D39" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14177,16 +14205,16 @@
         <v>408</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14194,13 +14222,13 @@
         <v>409</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14208,16 +14236,16 @@
         <v>410</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
     </row>
   </sheetData>
@@ -14245,7 +14273,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>484</v>
@@ -14254,7 +14282,7 @@
         <v>1075</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14262,13 +14290,13 @@
         <v>173</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14276,13 +14304,13 @@
         <v>174</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>1084</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14290,13 +14318,13 @@
         <v>175</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>1084</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14304,13 +14332,13 @@
         <v>176</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>1086</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14318,13 +14346,13 @@
         <v>177</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>1086</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14332,13 +14360,13 @@
         <v>178</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14346,13 +14374,13 @@
         <v>179</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1095</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14360,13 +14388,13 @@
         <v>180</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>1095</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14374,13 +14402,13 @@
         <v>181</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>1095</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14388,13 +14416,13 @@
         <v>182</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>1095</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14402,13 +14430,13 @@
         <v>183</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>1095</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14416,13 +14444,13 @@
         <v>184</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>1097</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14430,13 +14458,13 @@
         <v>185</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>1097</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14444,13 +14472,13 @@
         <v>186</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>1097</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14458,13 +14486,13 @@
         <v>187</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>1100</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14472,13 +14500,13 @@
         <v>188</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>1100</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14486,13 +14514,13 @@
         <v>189</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>1100</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14500,13 +14528,13 @@
         <v>190</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14514,13 +14542,13 @@
         <v>191</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14528,13 +14556,13 @@
         <v>192</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
     </row>
   </sheetData>
@@ -14553,7 +14581,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultColWidth="12.60546875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="43.71"/>
@@ -14563,7 +14591,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>484</v>
@@ -14572,7 +14600,7 @@
         <v>1075</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14580,13 +14608,13 @@
         <v>92</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>1078</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14594,13 +14622,13 @@
         <v>93</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>1078</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14608,13 +14636,13 @@
         <v>94</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>1078</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14622,13 +14650,13 @@
         <v>95</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14636,13 +14664,13 @@
         <v>96</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>1638</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>1636</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14650,13 +14678,13 @@
         <v>97</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>1638</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>1636</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14664,13 +14692,13 @@
         <v>98</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1084</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14678,13 +14706,13 @@
         <v>99</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14692,13 +14720,13 @@
         <v>100</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14706,13 +14734,13 @@
         <v>101</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>1644</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>1642</v>
-      </c>
       <c r="D11" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14720,13 +14748,13 @@
         <v>102</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14734,13 +14762,13 @@
         <v>103</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>1092</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14748,13 +14776,13 @@
         <v>104</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>1092</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14762,13 +14790,13 @@
         <v>105</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>1092</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14776,13 +14804,13 @@
         <v>106</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>1092</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14790,13 +14818,13 @@
         <v>107</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>1092</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14804,13 +14832,13 @@
         <v>108</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>1092</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14818,13 +14846,13 @@
         <v>109</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>1095</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14832,13 +14860,13 @@
         <v>110</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>1095</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14846,13 +14874,13 @@
         <v>111</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>1097</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14860,13 +14888,13 @@
         <v>112</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>1097</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14874,13 +14902,13 @@
         <v>113</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>1097</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14888,13 +14916,13 @@
         <v>114</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>1097</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14902,13 +14930,13 @@
         <v>115</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>1097</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14916,13 +14944,13 @@
         <v>116</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>1097</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14930,13 +14958,13 @@
         <v>117</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>1097</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14944,13 +14972,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>1097</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14958,13 +14986,13 @@
         <v>119</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>1097</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14972,13 +15000,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>1100</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14986,13 +15014,13 @@
         <v>121</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>1100</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15000,13 +15028,13 @@
         <v>122</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>1100</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15014,13 +15042,13 @@
         <v>123</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>1100</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15028,13 +15056,13 @@
         <v>124</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15042,13 +15070,13 @@
         <v>125</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15056,13 +15084,13 @@
         <v>126</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15070,13 +15098,13 @@
         <v>127</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15084,13 +15112,13 @@
         <v>128</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15098,13 +15126,13 @@
         <v>129</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15112,13 +15140,13 @@
         <v>130</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15126,17 +15154,31 @@
         <v>131</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>1636</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1"/>
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>1638</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>1678</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -15159,7 +15201,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1675</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15167,7 +15209,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1676</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15175,7 +15217,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1677</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15183,7 +15225,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1678</v>
+        <v>1682</v>
       </c>
     </row>
   </sheetData>
@@ -15211,7 +15253,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1679</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -15223,13 +15265,13 @@
         <v>484</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1681</v>
+        <v>1685</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1682</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15237,13 +15279,13 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1683</v>
+        <v>1687</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>382</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>51</v>
@@ -15254,13 +15296,13 @@
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1684</v>
+        <v>1688</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>382</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>52</v>
@@ -15271,13 +15313,13 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1685</v>
+        <v>1689</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>481</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1686</v>
+        <v>1690</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>56</v>
@@ -15288,13 +15330,13 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1687</v>
+        <v>1691</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>1688</v>
+        <v>1692</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1689</v>
+        <v>1693</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>57</v>
@@ -15305,13 +15347,13 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1690</v>
+        <v>1694</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>1691</v>
+        <v>1695</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1692</v>
+        <v>1696</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>58</v>
@@ -15342,19 +15384,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>1693</v>
+        <v>1697</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
       <c r="G1" s="13" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>488</v>
@@ -15363,7 +15405,7 @@
         <v>484</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>488</v>
@@ -15380,7 +15422,7 @@
         <v>1193</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>4</v>
@@ -15389,7 +15431,7 @@
         <v>1167</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15400,7 +15442,7 @@
         <v>1194</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>4</v>
@@ -15409,7 +15451,7 @@
         <v>1168</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15420,7 +15462,7 @@
         <v>1195</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>4</v>
@@ -15429,7 +15471,7 @@
         <v>1169</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15440,7 +15482,7 @@
         <v>1196</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>4</v>
@@ -15449,7 +15491,7 @@
         <v>1170</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15460,7 +15502,7 @@
         <v>1197</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>4</v>
@@ -15469,7 +15511,7 @@
         <v>1171</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15480,7 +15522,7 @@
         <v>1198</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>4</v>
@@ -15489,7 +15531,7 @@
         <v>1172</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15500,7 +15542,7 @@
         <v>1199</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>4</v>
@@ -15509,7 +15551,7 @@
         <v>1173</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15520,7 +15562,7 @@
         <v>1200</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>4</v>
@@ -15529,7 +15571,7 @@
         <v>1174</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>1696</v>
+        <v>1700</v>
       </c>
     </row>
   </sheetData>
@@ -15564,15 +15606,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="52" t="s">
-        <v>1697</v>
+        <v>1701</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1698</v>
+        <v>1702</v>
       </c>
       <c r="D1" s="13"/>
       <c r="E1" s="13"/>
       <c r="G1" s="13" t="s">
-        <v>1699</v>
+        <v>1703</v>
       </c>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
@@ -15580,10 +15622,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="C2" s="53" t="s">
-        <v>1701</v>
+        <v>1705</v>
       </c>
       <c r="D2" s="54"/>
       <c r="E2" s="55"/>
@@ -15591,291 +15633,291 @@
         <v>489</v>
       </c>
       <c r="H2" s="53" t="s">
-        <v>1702</v>
+        <v>1706</v>
       </c>
       <c r="I2" s="53" t="s">
         <v>484</v>
       </c>
       <c r="J2" s="53" t="s">
-        <v>1703</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1704</v>
+        <v>1708</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1705</v>
+        <v>1709</v>
       </c>
       <c r="E3" s="56"/>
       <c r="G3" s="1" t="s">
-        <v>1706</v>
+        <v>1710</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1707</v>
+        <v>1711</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1708</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1709</v>
+        <v>1713</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1710</v>
+        <v>1714</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1715</v>
+        <v>1719</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1716</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1717</v>
+        <v>1721</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1718</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1719</v>
+        <v>1723</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1720</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1721</v>
+        <v>1725</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1722</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1723</v>
+        <v>1727</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1724</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>1727</v>
+        <v>1731</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1728</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>1729</v>
+        <v>1733</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1730</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1731</v>
+        <v>1735</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>1732</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>1733</v>
+        <v>1737</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1734</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>1735</v>
+        <v>1739</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1736</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>1737</v>
+        <v>1741</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1738</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>1739</v>
+        <v>1743</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1740</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>1741</v>
+        <v>1745</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1742</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>1743</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>1744</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>1745</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>1746</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>1748</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1749</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>1750</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1751</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1752</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1753</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>1754</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>1755</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>1756</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>1757</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>1758</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>1759</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>1760</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>1762</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>1763</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>1764</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>1765</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>1766</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>1767</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15883,147 +15925,147 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>1768</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>1769</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>1770</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>1771</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>1772</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>1773</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>1774</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>1775</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>1776</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>1777</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>1778</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>1779</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>1780</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>1783</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>1784</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1785</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>1786</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>1787</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>1788</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>1789</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>1790</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>1791</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>1792</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>1793</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>1794</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>1796</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16057,32 +16099,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1797</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1798</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1799</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1800</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1801</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1802</v>
+        <v>1806</v>
       </c>
     </row>
   </sheetData>
@@ -16110,20 +16152,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1803</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1804</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="57" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>1806</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16191,41 +16233,41 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>1807</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>1808</v>
+        <v>1812</v>
       </c>
       <c r="B15" s="44" t="s">
-        <v>1809</v>
+        <v>1813</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>1810</v>
+        <v>1814</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>1811</v>
+        <v>1815</v>
       </c>
       <c r="E15" s="44" t="s">
-        <v>1812</v>
+        <v>1816</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>1813</v>
+        <v>1817</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>1814</v>
+        <v>1818</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>1815</v>
+        <v>1819</v>
       </c>
       <c r="I15" s="30" t="s">
-        <v>1816</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="61" t="s">
-        <v>1809</v>
+        <v>1813</v>
       </c>
       <c r="B16" s="45" t="n">
         <v>0</v>
@@ -16254,7 +16296,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="61" t="s">
-        <v>1810</v>
+        <v>1814</v>
       </c>
       <c r="B17" s="45" t="n">
         <v>125</v>
@@ -16283,7 +16325,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="61" t="s">
-        <v>1811</v>
+        <v>1815</v>
       </c>
       <c r="B18" s="45" t="n">
         <v>100</v>
@@ -16312,7 +16354,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="61" t="s">
-        <v>1812</v>
+        <v>1816</v>
       </c>
       <c r="B19" s="45" t="n">
         <v>100</v>
@@ -16341,7 +16383,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="61" t="s">
-        <v>1813</v>
+        <v>1817</v>
       </c>
       <c r="B20" s="45" t="n">
         <v>75</v>
@@ -16370,7 +16412,7 @@
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="61" t="s">
-        <v>1814</v>
+        <v>1818</v>
       </c>
       <c r="B21" s="45" t="n">
         <v>75</v>
@@ -16399,7 +16441,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="61" t="s">
-        <v>1815</v>
+        <v>1819</v>
       </c>
       <c r="B22" s="45" t="n">
         <v>75</v>
@@ -16428,7 +16470,7 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="62" t="s">
-        <v>1816</v>
+        <v>1820</v>
       </c>
       <c r="B23" s="47" t="n">
         <v>75</v>
@@ -16457,22 +16499,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1817</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>1818</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>1819</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>1820</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16480,10 +16522,10 @@
         <v>489</v>
       </c>
       <c r="B32" s="63" t="s">
-        <v>1821</v>
+        <v>1825</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>1822</v>
+        <v>1826</v>
       </c>
       <c r="D32" s="64"/>
       <c r="E32" s="64"/>
@@ -16493,13 +16535,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="45" t="s">
-        <v>1823</v>
+        <v>1827</v>
       </c>
       <c r="B33" s="37" t="s">
-        <v>1824</v>
+        <v>1828</v>
       </c>
       <c r="C33" s="65" t="s">
-        <v>1825</v>
+        <v>1829</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="65"/>
@@ -16509,13 +16551,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="45" t="s">
-        <v>1826</v>
+        <v>1830</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1824</v>
+        <v>1828</v>
       </c>
       <c r="C34" s="65" t="s">
-        <v>1825</v>
+        <v>1829</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="65"/>
@@ -16525,13 +16567,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="45" t="s">
-        <v>1827</v>
+        <v>1831</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1824</v>
+        <v>1828</v>
       </c>
       <c r="C35" s="65" t="s">
-        <v>1825</v>
+        <v>1829</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="65"/>
@@ -16541,13 +16583,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="45" t="s">
-        <v>1828</v>
+        <v>1832</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1810</v>
+        <v>1814</v>
       </c>
       <c r="C36" s="66" t="s">
-        <v>1829</v>
+        <v>1833</v>
       </c>
       <c r="D36" s="66"/>
       <c r="E36" s="66"/>
@@ -16557,13 +16599,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="45" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1812</v>
+        <v>1816</v>
       </c>
       <c r="C37" s="65" t="s">
-        <v>1831</v>
+        <v>1835</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65"/>
@@ -16573,13 +16615,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="45" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1810</v>
+        <v>1814</v>
       </c>
       <c r="C38" s="65" t="s">
-        <v>1831</v>
+        <v>1835</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -16589,13 +16631,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="45" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B39" s="37" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C39" s="66" t="s">
         <v>1833</v>
-      </c>
-      <c r="B39" s="37" t="s">
-        <v>1810</v>
-      </c>
-      <c r="C39" s="66" t="s">
-        <v>1829</v>
       </c>
       <c r="D39" s="66"/>
       <c r="E39" s="66"/>
@@ -16608,10 +16650,10 @@
         <v>546</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1810</v>
+        <v>1814</v>
       </c>
       <c r="C40" s="66" t="s">
-        <v>1829</v>
+        <v>1833</v>
       </c>
       <c r="D40" s="66"/>
       <c r="E40" s="66"/>
@@ -16621,13 +16663,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="45" t="s">
-        <v>1834</v>
+        <v>1838</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1813</v>
+        <v>1817</v>
       </c>
       <c r="C41" s="66" t="s">
-        <v>1835</v>
+        <v>1839</v>
       </c>
       <c r="D41" s="66"/>
       <c r="E41" s="66"/>
@@ -16637,13 +16679,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="45" t="s">
-        <v>1836</v>
+        <v>1840</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1814</v>
+        <v>1818</v>
       </c>
       <c r="C42" s="66" t="s">
-        <v>1837</v>
+        <v>1841</v>
       </c>
       <c r="D42" s="66"/>
       <c r="E42" s="66"/>
@@ -16653,13 +16695,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="45" t="s">
-        <v>1838</v>
+        <v>1842</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1815</v>
+        <v>1819</v>
       </c>
       <c r="C43" s="66" t="s">
-        <v>1839</v>
+        <v>1843</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -16669,13 +16711,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="45" t="s">
-        <v>1840</v>
+        <v>1844</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1816</v>
+        <v>1820</v>
       </c>
       <c r="C44" s="66" t="s">
-        <v>1841</v>
+        <v>1845</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -16685,7 +16727,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="67" t="s">
-        <v>1830</v>
+        <v>1834</v>
       </c>
       <c r="B48" s="67"/>
       <c r="C48" s="67"/>
@@ -16697,17 +16739,17 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>1842</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>1843</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="67" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="B52" s="67"/>
       <c r="C52" s="67"/>
@@ -16719,12 +16761,12 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>1844</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="67" t="s">
-        <v>1845</v>
+        <v>1849</v>
       </c>
       <c r="B57" s="67"/>
       <c r="C57" s="67"/>
@@ -16736,72 +16778,72 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>1846</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>1847</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>1848</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>1849</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>1850</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>1851</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>1852</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>1853</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="68" t="s">
-        <v>1854</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="68" t="s">
-        <v>1855</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="68" t="s">
-        <v>1856</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>1857</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>1858</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H73" s="67" t="s">
-        <v>1859</v>
+        <v>1863</v>
       </c>
       <c r="I73" s="67"/>
       <c r="J73" s="67"/>
@@ -16809,483 +16851,483 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="68" t="s">
-        <v>1860</v>
+        <v>1864</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>1861</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="68" t="s">
-        <v>1854</v>
+        <v>1858</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>1862</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="68" t="s">
-        <v>1855</v>
+        <v>1859</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>1863</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="68" t="s">
-        <v>1856</v>
+        <v>1860</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>1864</v>
+        <v>1868</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>1865</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="68" t="s">
-        <v>1866</v>
+        <v>1870</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>1867</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="68" t="s">
-        <v>1868</v>
+        <v>1872</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>1869</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="68" t="s">
-        <v>1870</v>
+        <v>1874</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>1871</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="68" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>1873</v>
+        <v>1877</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>1874</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="68" t="s">
-        <v>1868</v>
+        <v>1872</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>1869</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="68" t="s">
+        <v>1879</v>
+      </c>
+      <c r="H83" s="6" t="s">
         <v>1875</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>1871</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="68" t="s">
-        <v>1876</v>
+        <v>1880</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>1877</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="68" t="s">
-        <v>1878</v>
+        <v>1882</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>1879</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="68" t="s">
-        <v>1880</v>
+        <v>1884</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>1881</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="68" t="s">
-        <v>1882</v>
+        <v>1886</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>1883</v>
+        <v>1887</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>1884</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="68" t="s">
-        <v>1885</v>
+        <v>1889</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>1886</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="68" t="s">
-        <v>1887</v>
+        <v>1891</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>1888</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="68" t="s">
-        <v>1889</v>
+        <v>1893</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>1890</v>
+        <v>1894</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>1891</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="68" t="s">
-        <v>1892</v>
+        <v>1896</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>1893</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="68" t="s">
-        <v>1894</v>
+        <v>1898</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>1895</v>
+        <v>1899</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>1896</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="68" t="s">
-        <v>1897</v>
+        <v>1901</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>1898</v>
+        <v>1902</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>1899</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="68" t="s">
-        <v>1900</v>
+        <v>1904</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>1901</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="68" t="s">
-        <v>1902</v>
+        <v>1906</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="68" t="s">
-        <v>1904</v>
+        <v>1908</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>1905</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="68" t="s">
-        <v>1906</v>
+        <v>1910</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>1907</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="68" t="s">
-        <v>1908</v>
+        <v>1912</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>1909</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="68" t="s">
-        <v>1910</v>
+        <v>1914</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>1911</v>
+        <v>1915</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>1912</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="68" t="s">
-        <v>1913</v>
+        <v>1917</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>1915</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="68" t="s">
-        <v>1916</v>
+        <v>1920</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>1917</v>
+        <v>1921</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>1918</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="68" t="s">
-        <v>1919</v>
+        <v>1923</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>1871</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="68" t="s">
-        <v>1921</v>
+        <v>1925</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>1922</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="68" t="s">
-        <v>1923</v>
+        <v>1927</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>1924</v>
+        <v>1928</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>1925</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="68" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>1927</v>
+        <v>1931</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>1928</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="68" t="s">
-        <v>1929</v>
+        <v>1933</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>1930</v>
+        <v>1934</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>1931</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="68" t="s">
-        <v>1932</v>
+        <v>1936</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>1933</v>
+        <v>1937</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>1934</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="68" t="s">
-        <v>1935</v>
+        <v>1939</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>1922</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="68" t="s">
-        <v>1936</v>
+        <v>1940</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>1937</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="68" t="s">
-        <v>1938</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="68" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="68" t="s">
-        <v>1940</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="68" t="s">
-        <v>1941</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="68" t="s">
-        <v>1942</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="68" t="s">
-        <v>1943</v>
+        <v>1947</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>1944</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="68" t="s">
-        <v>1945</v>
+        <v>1949</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>1946</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="68" t="s">
-        <v>1947</v>
+        <v>1951</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>1948</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="68" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="68" t="s">
-        <v>1870</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="68" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>1950</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="68" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="68" t="s">
-        <v>1875</v>
+        <v>1879</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>1951</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="68" t="s">
-        <v>1952</v>
+        <v>1956</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>1953</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="68" t="s">
-        <v>1943</v>
+        <v>1947</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>1944</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="68" t="s">
-        <v>1954</v>
+        <v>1958</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>1955</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="68" t="s">
-        <v>1956</v>
+        <v>1960</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>1957</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="68" t="s">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="68" t="s">
-        <v>1960</v>
+        <v>1964</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="68" t="s">
-        <v>1962</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="68" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>1964</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="68" t="s">
-        <v>1965</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="68" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17296,78 +17338,78 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="6" t="s">
-        <v>1966</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="68" t="s">
-        <v>1967</v>
+        <v>1971</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>1968</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="68" t="s">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>1970</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="68" t="s">
-        <v>1971</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="68" t="s">
-        <v>1972</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="68" t="s">
-        <v>1973</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="68" t="s">
-        <v>1974</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="68" t="s">
-        <v>1975</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="68" t="s">
-        <v>1976</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="68" t="s">
-        <v>1977</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="68" t="s">
-        <v>1978</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="68" t="s">
-        <v>1979</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="68" t="s">
-        <v>1980</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="68" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
     </row>
   </sheetData>
@@ -17474,7 +17516,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="67" t="s">
-        <v>1981</v>
+        <v>1985</v>
       </c>
       <c r="B1" s="67"/>
       <c r="C1" s="67"/>
@@ -17492,10 +17534,10 @@
         <v>489</v>
       </c>
       <c r="D2" s="69" t="s">
-        <v>1982</v>
+        <v>1986</v>
       </c>
       <c r="E2" s="69" t="s">
-        <v>1682</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17506,7 +17548,7 @@
         <v>993</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>1983</v>
+        <v>1987</v>
       </c>
       <c r="D3" s="45" t="n">
         <v>7</v>
@@ -17523,10 +17565,10 @@
         <v>998</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>1984</v>
+        <v>1988</v>
       </c>
       <c r="D4" s="70" t="s">
-        <v>1985</v>
+        <v>1989</v>
       </c>
       <c r="E4" s="45" t="n">
         <v>6</v>
@@ -17540,10 +17582,10 @@
         <v>998</v>
       </c>
       <c r="C5" s="71" t="s">
-        <v>1986</v>
+        <v>1990</v>
       </c>
       <c r="D5" s="70" t="s">
-        <v>1985</v>
+        <v>1989</v>
       </c>
       <c r="E5" s="71" t="n">
         <v>6</v>
@@ -17557,10 +17599,10 @@
         <v>993</v>
       </c>
       <c r="C6" s="71" t="s">
-        <v>1987</v>
+        <v>1991</v>
       </c>
       <c r="D6" s="73" t="s">
-        <v>1988</v>
+        <v>1992</v>
       </c>
       <c r="E6" s="71" t="n">
         <v>1</v>
@@ -17590,52 +17632,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1989</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>1990</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>1991</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>1993</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>1994</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>1995</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1996</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>1997</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1998</v>
+        <v>2002</v>
       </c>
     </row>
   </sheetData>
@@ -17659,19 +17701,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="74" t="s">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="B1" s="74"/>
       <c r="C1" s="74"/>
       <c r="D1" s="74"/>
       <c r="E1" s="74" t="s">
-        <v>2000</v>
+        <v>2004</v>
       </c>
       <c r="F1" s="74"/>
       <c r="G1" s="74"/>
       <c r="H1" s="74"/>
       <c r="I1" s="74" t="s">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="J1" s="74"/>
       <c r="K1" s="74"/>
@@ -17687,16 +17729,16 @@
         <v>24</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="E2" s="6" t="n">
         <v>21</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>2004</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17704,10 +17746,10 @@
         <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>2006</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17715,10 +17757,10 @@
         <v>23</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>2008</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17726,35 +17768,35 @@
         <v>24</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>2010</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I6" s="6" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I7" s="6" t="s">
-        <v>2012</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I8" s="6" t="s">
-        <v>2013</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I9" s="6" t="s">
-        <v>2014</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I10" s="6" t="s">
-        <v>2015</v>
+        <v>2019</v>
       </c>
     </row>
   </sheetData>
@@ -17786,28 +17828,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>2022</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17821,7 +17863,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="H2" s="6" t="n">
         <v>85</v>
@@ -17851,7 +17893,7 @@
         <v>3</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="H3" s="6" t="n">
         <v>110</v>
@@ -17881,7 +17923,7 @@
         <v>9</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>115</v>
@@ -17911,7 +17953,7 @@
         <v>19</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>100</v>
@@ -17941,7 +17983,7 @@
         <v>34</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>105</v>
@@ -17971,7 +18013,7 @@
         <v>55</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>90</v>
@@ -18031,7 +18073,7 @@
         <v>119</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>90</v>
@@ -18061,7 +18103,7 @@
         <v>164</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>2023</v>
+        <v>2027</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>95</v>
@@ -18143,7 +18185,7 @@
         <v>559</v>
       </c>
       <c r="G15" s="75" t="s">
-        <v>2024</v>
+        <v>2028</v>
       </c>
       <c r="H15" s="76" t="n">
         <v>45</v>
@@ -18215,7 +18257,7 @@
         <v>1329</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>2025</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18244,10 +18286,10 @@
         <v>1770</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="H22" s="78" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18263,7 +18305,7 @@
         <v>2023</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>2027</v>
+        <v>2031</v>
       </c>
       <c r="H23" s="78" t="n">
         <f aca="false">J4</f>
@@ -18283,7 +18325,7 @@
         <v>2299</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>2028</v>
+        <v>2032</v>
       </c>
       <c r="H24" s="6" t="e">
         <f aca="false">levelfromexp(H23,VLOOKUP(H22,G2:H10,2,0))</f>
@@ -18667,7 +18709,7 @@
         <v>886</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2029</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18675,39 +18717,39 @@
         <v>870</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2030</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>2031</v>
+        <v>2035</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2032</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2033</v>
+        <v>2037</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2034</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2035</v>
+        <v>2039</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2036</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2037</v>
+        <v>2041</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>2038</v>
+        <v>2042</v>
       </c>
     </row>
   </sheetData>
@@ -18734,7 +18776,7 @@
         <v>103</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2039</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18742,7 +18784,7 @@
         <v>104</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2040</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18750,7 +18792,7 @@
         <v>105</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18758,7 +18800,7 @@
         <v>106</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>2041</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18766,7 +18808,7 @@
         <v>107</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18774,7 +18816,7 @@
         <v>108</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2042</v>
+        <v>2046</v>
       </c>
     </row>
   </sheetData>
@@ -18804,7 +18846,7 @@
         <v>840</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2043</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18812,7 +18854,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2044</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18828,7 +18870,7 @@
         <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2045</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18836,7 +18878,7 @@
         <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2046</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18844,7 +18886,7 @@
         <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2047</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18852,7 +18894,7 @@
         <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2048</v>
+        <v>2052</v>
       </c>
     </row>
   </sheetData>
@@ -18879,7 +18921,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2049</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18890,7 +18932,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>2050</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18901,29 +18943,29 @@
         <v>20</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>2051</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>2052</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>2049</v>
+        <v>2053</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>2054</v>
+        <v>2058</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>2055</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18950,7 +18992,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>2056</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18969,7 +19011,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18977,10 +19019,10 @@
         <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>2058</v>
+        <v>2062</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>2059</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18988,10 +19030,10 @@
         <v>37</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>2058</v>
+        <v>2062</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>2059</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18999,10 +19041,10 @@
         <v>45</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>2058</v>
+        <v>2062</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>2059</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19013,12 +19055,12 @@
         <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>2060</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19026,7 +19068,7 @@
         <v>470</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>2061</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19037,7 +19079,7 @@
         <v>33.34</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>2062</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19061,7 +19103,7 @@
         <v>457</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>2063</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19069,7 +19111,7 @@
         <v>472</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>2064</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19120,7 +19162,7 @@
         <v>0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>2065</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19136,12 +19178,12 @@
         <v>374</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>2066</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>2067</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19154,10 +19196,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>2068</v>
+        <v>2072</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19167,7 +19209,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>2069</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19221,12 +19263,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="79" t="s">
-        <v>2070</v>
+        <v>2074</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
       <c r="E1" s="14" t="s">
-        <v>2071</v>
+        <v>2075</v>
       </c>
       <c r="F1" s="14"/>
       <c r="G1" s="14"/>
@@ -19234,30 +19276,30 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>2072</v>
+        <v>2076</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
       <c r="E2" s="80" t="s">
         <v>489</v>
       </c>
       <c r="F2" s="80" t="s">
-        <v>2075</v>
+        <v>2079</v>
       </c>
       <c r="G2" s="80" t="s">
-        <v>2076</v>
+        <v>2080</v>
       </c>
       <c r="H2" s="80" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>1</v>
@@ -19266,7 +19308,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="71" t="s">
-        <v>2078</v>
+        <v>2082</v>
       </c>
       <c r="F3" s="71" t="n">
         <v>5</v>
@@ -19280,7 +19322,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>6</v>
@@ -19295,7 +19337,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2079</v>
+        <v>2083</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>5</v>
@@ -19310,7 +19352,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2080</v>
+        <v>2084</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>3</v>
@@ -19325,7 +19367,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>2075</v>
+        <v>2079</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>2</v>
@@ -19340,7 +19382,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>2076</v>
+        <v>2080</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>0</v>
@@ -19349,7 +19391,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="81" t="s">
-        <v>2081</v>
+        <v>2085</v>
       </c>
       <c r="F8" s="81" t="n">
         <f aca="false">SUM(F3:F7)</f>
@@ -19366,7 +19408,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>2082</v>
+        <v>2086</v>
       </c>
       <c r="B9" s="6" t="n">
         <v>5</v>
@@ -19377,7 +19419,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>5</v>
@@ -19388,7 +19430,7 @@
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>2083</v>
+        <v>2087</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>20</v>
@@ -19397,7 +19439,7 @@
         <v>25</v>
       </c>
       <c r="E11" s="81" t="s">
-        <v>2084</v>
+        <v>2088</v>
       </c>
       <c r="F11" s="81" t="n">
         <v>10</v>
@@ -19405,7 +19447,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>2085</v>
+        <v>2089</v>
       </c>
       <c r="B12" s="6" t="n">
         <v>135</v>
@@ -19414,7 +19456,7 @@
         <v>150</v>
       </c>
       <c r="E12" s="81" t="s">
-        <v>2086</v>
+        <v>2090</v>
       </c>
       <c r="F12" s="81" t="n">
         <v>7</v>
@@ -19422,7 +19464,7 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>2087</v>
+        <v>2091</v>
       </c>
       <c r="B13" s="6" t="n">
         <v>2</v>
@@ -19433,7 +19475,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>2088</v>
+        <v>2092</v>
       </c>
       <c r="B14" s="6" t="n">
         <v>5</v>
@@ -19444,7 +19486,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>2089</v>
+        <v>2093</v>
       </c>
       <c r="B15" s="6" t="n">
         <v>15</v>
@@ -19455,7 +19497,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>2090</v>
+        <v>2094</v>
       </c>
       <c r="B16" s="6" t="n">
         <v>0</v>
@@ -19466,7 +19508,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>2091</v>
+        <v>2095</v>
       </c>
       <c r="B17" s="6" t="n">
         <v>30</v>
@@ -19475,7 +19517,7 @@
         <v>85</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>2092</v>
+        <v>2096</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
@@ -19483,7 +19525,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>2093</v>
+        <v>2097</v>
       </c>
       <c r="B18" s="6" t="n">
         <v>0</v>
@@ -19492,21 +19534,21 @@
         <v>25</v>
       </c>
       <c r="E18" s="80" t="s">
-        <v>2072</v>
+        <v>2076</v>
       </c>
       <c r="F18" s="80" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="G18" s="80" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
       <c r="H18" s="80" t="s">
-        <v>2094</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>2095</v>
+        <v>2099</v>
       </c>
       <c r="B19" s="6" t="n">
         <v>0</v>
@@ -19515,7 +19557,7 @@
         <v>99</v>
       </c>
       <c r="E19" s="71" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="F19" s="71" t="n">
         <f aca="false">C3+C26+C34+C41+C48+C55+C63+C70+C77</f>
@@ -19532,7 +19574,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>2096</v>
+        <v>2100</v>
       </c>
       <c r="B20" s="6" t="n">
         <v>0</v>
@@ -19541,7 +19583,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="71" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="F20" s="71" t="n">
         <f aca="false">B4+B29+B66+B71+(F19-B3)*(F11/2)</f>
@@ -19556,12 +19598,12 @@
         <v>300</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>2097</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>2098</v>
+        <v>2102</v>
       </c>
       <c r="B21" s="6" t="n">
         <v>20</v>
@@ -19570,7 +19612,7 @@
         <v>60</v>
       </c>
       <c r="E21" s="71" t="s">
-        <v>2079</v>
+        <v>2083</v>
       </c>
       <c r="F21" s="71" t="n">
         <f aca="false">B5+B30+B81+(F19-B3)*(F12/2)</f>
@@ -19587,7 +19629,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>2099</v>
+        <v>2103</v>
       </c>
       <c r="B22" s="6" t="n">
         <v>0</v>
@@ -19596,7 +19638,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="71" t="s">
-        <v>2080</v>
+        <v>2084</v>
       </c>
       <c r="F22" s="71" t="n">
         <f aca="false">B6+B37+B50</f>
@@ -19613,7 +19655,7 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>2100</v>
+        <v>2104</v>
       </c>
       <c r="B23" s="6" t="n">
         <v>0</v>
@@ -19622,7 +19664,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="71" t="s">
-        <v>2075</v>
+        <v>2079</v>
       </c>
       <c r="F23" s="71" t="n">
         <f aca="false">B7+B36+B56+B65+ROUNDDOWN(F25/25,0)</f>
@@ -19637,12 +19679,12 @@
         <v>25</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>2097</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E24" s="71" t="s">
-        <v>2076</v>
+        <v>2080</v>
       </c>
       <c r="F24" s="71" t="n">
         <f aca="false">B8+B42+B57+ROUNDDOWN(F29/25,0)</f>
@@ -19657,21 +19699,21 @@
         <v>22</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>2097</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>2031</v>
+        <v>2035</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
       <c r="E25" s="71" t="s">
-        <v>2082</v>
+        <v>2086</v>
       </c>
       <c r="F25" s="71" t="n">
         <f aca="false">B9+B44+B64</f>
@@ -19688,7 +19730,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="B26" s="6" t="n">
         <v>4</v>
@@ -19697,7 +19739,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="71" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
       <c r="F26" s="71" t="n">
         <f aca="false">B10+B78</f>
@@ -19714,7 +19756,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>2087</v>
+        <v>2091</v>
       </c>
       <c r="B27" s="6" t="n">
         <v>10</v>
@@ -19723,7 +19765,7 @@
         <v>10</v>
       </c>
       <c r="E27" s="71" t="s">
-        <v>2083</v>
+        <v>2087</v>
       </c>
       <c r="F27" s="71" t="n">
         <f aca="false">B11+B79</f>
@@ -19740,7 +19782,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>2095</v>
+        <v>2099</v>
       </c>
       <c r="B28" s="6" t="n">
         <v>20</v>
@@ -19749,7 +19791,7 @@
         <v>20</v>
       </c>
       <c r="E28" s="71" t="s">
-        <v>2085</v>
+        <v>2089</v>
       </c>
       <c r="F28" s="71" t="n">
         <f aca="false">B12+B49</f>
@@ -19766,7 +19808,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="B29" s="6" t="n">
         <v>18</v>
@@ -19775,7 +19817,7 @@
         <v>22</v>
       </c>
       <c r="E29" s="71" t="s">
-        <v>2087</v>
+        <v>2091</v>
       </c>
       <c r="F29" s="71" t="n">
         <f aca="false">B13+B27+B58</f>
@@ -19792,7 +19834,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>2079</v>
+        <v>2083</v>
       </c>
       <c r="B30" s="6" t="n">
         <v>5</v>
@@ -19801,7 +19843,7 @@
         <v>5</v>
       </c>
       <c r="E30" s="71" t="s">
-        <v>2088</v>
+        <v>2092</v>
       </c>
       <c r="F30" s="71" t="n">
         <f aca="false">B14+B59+B80</f>
@@ -19818,7 +19860,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E31" s="71" t="s">
-        <v>2089</v>
+        <v>2093</v>
       </c>
       <c r="F31" s="71" t="n">
         <f aca="false">B15</f>
@@ -19835,7 +19877,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E32" s="71" t="s">
-        <v>2090</v>
+        <v>2094</v>
       </c>
       <c r="F32" s="71" t="n">
         <f aca="false">B16+B35+B43+B51</f>
@@ -19855,13 +19897,13 @@
         <v>870</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
       <c r="E33" s="71" t="s">
-        <v>2091</v>
+        <v>2095</v>
       </c>
       <c r="F33" s="71" t="n">
         <v>30</v>
@@ -19876,7 +19918,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="B34" s="6" t="n">
         <v>4</v>
@@ -19885,7 +19927,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="71" t="s">
-        <v>2093</v>
+        <v>2097</v>
       </c>
       <c r="F34" s="71" t="n">
         <v>0</v>
@@ -19900,7 +19942,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>2090</v>
+        <v>2094</v>
       </c>
       <c r="B35" s="6" t="n">
         <v>5</v>
@@ -19909,7 +19951,7 @@
         <v>5</v>
       </c>
       <c r="E35" s="71" t="s">
-        <v>2095</v>
+        <v>2099</v>
       </c>
       <c r="F35" s="71" t="n">
         <f aca="false">B19+B28</f>
@@ -19925,7 +19967,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>2075</v>
+        <v>2079</v>
       </c>
       <c r="B36" s="6" t="n">
         <v>4</v>
@@ -19934,7 +19976,7 @@
         <v>6</v>
       </c>
       <c r="E36" s="71" t="s">
-        <v>2096</v>
+        <v>2100</v>
       </c>
       <c r="F36" s="71" t="n">
         <v>0</v>
@@ -19950,7 +19992,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>2080</v>
+        <v>2084</v>
       </c>
       <c r="B37" s="6" t="n">
         <v>1</v>
@@ -19959,7 +20001,7 @@
         <v>1</v>
       </c>
       <c r="E37" s="71" t="s">
-        <v>2098</v>
+        <v>2102</v>
       </c>
       <c r="F37" s="71" t="n">
         <v>20</v>
@@ -19974,7 +20016,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E38" s="71" t="s">
-        <v>2099</v>
+        <v>2103</v>
       </c>
       <c r="F38" s="71" t="n">
         <f aca="false">B22+B45+B60+B84</f>
@@ -19991,7 +20033,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E39" s="71" t="s">
-        <v>2100</v>
+        <v>2104</v>
       </c>
       <c r="F39" s="71" t="n">
         <f aca="false">B23+B67+B72+B83</f>
@@ -20011,15 +20053,15 @@
         <v>886</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="B41" s="6" t="n">
         <v>4</v>
@@ -20030,7 +20072,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>2076</v>
+        <v>2080</v>
       </c>
       <c r="B42" s="6" t="n">
         <v>13</v>
@@ -20041,7 +20083,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>2090</v>
+        <v>2094</v>
       </c>
       <c r="B43" s="6" t="n">
         <v>5</v>
@@ -20052,7 +20094,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>2082</v>
+        <v>2086</v>
       </c>
       <c r="B44" s="6" t="n">
         <v>10</v>
@@ -20063,7 +20105,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
-        <v>2099</v>
+        <v>2103</v>
       </c>
       <c r="B45" s="6" t="n">
         <v>1</v>
@@ -20074,18 +20116,18 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>2033</v>
+        <v>2037</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="B48" s="6" t="n">
         <v>4</v>
@@ -20096,7 +20138,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>2085</v>
+        <v>2089</v>
       </c>
       <c r="B49" s="6" t="n">
         <v>10</v>
@@ -20107,7 +20149,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>2080</v>
+        <v>2084</v>
       </c>
       <c r="B50" s="6" t="n">
         <v>1</v>
@@ -20118,7 +20160,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>2090</v>
+        <v>2094</v>
       </c>
       <c r="B51" s="6" t="n">
         <v>5</v>
@@ -20129,18 +20171,18 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>2035</v>
+        <v>2039</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="B55" s="6" t="n">
         <v>4</v>
@@ -20151,7 +20193,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>2075</v>
+        <v>2079</v>
       </c>
       <c r="B56" s="6" t="n">
         <v>4</v>
@@ -20162,7 +20204,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>2076</v>
+        <v>2080</v>
       </c>
       <c r="B57" s="6" t="n">
         <v>4</v>
@@ -20173,7 +20215,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>2087</v>
+        <v>2091</v>
       </c>
       <c r="B58" s="6" t="n">
         <v>10</v>
@@ -20184,7 +20226,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>2088</v>
+        <v>2092</v>
       </c>
       <c r="B59" s="6" t="n">
         <v>10</v>
@@ -20195,7 +20237,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>2099</v>
+        <v>2103</v>
       </c>
       <c r="B60" s="6" t="n">
         <v>1</v>
@@ -20206,18 +20248,18 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>2037</v>
+        <v>2041</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="B63" s="6" t="n">
         <v>4</v>
@@ -20228,7 +20270,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>2082</v>
+        <v>2086</v>
       </c>
       <c r="B64" s="6" t="n">
         <v>10</v>
@@ -20239,7 +20281,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>2075</v>
+        <v>2079</v>
       </c>
       <c r="B65" s="6" t="n">
         <v>9</v>
@@ -20250,7 +20292,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="B66" s="6" t="n">
         <v>10</v>
@@ -20261,7 +20303,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>2100</v>
+        <v>2104</v>
       </c>
       <c r="B67" s="6" t="n">
         <v>1</v>
@@ -20272,18 +20314,18 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>2101</v>
+        <v>2105</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="B70" s="6" t="n">
         <v>3</v>
@@ -20294,7 +20336,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="B71" s="6" t="n">
         <v>15</v>
@@ -20305,7 +20347,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>2100</v>
+        <v>2104</v>
       </c>
       <c r="B72" s="6" t="n">
         <v>1</v>
@@ -20316,18 +20358,18 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>2073</v>
+        <v>2077</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="B77" s="6" t="n">
         <v>5</v>
@@ -20338,7 +20380,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>1805</v>
+        <v>1809</v>
       </c>
       <c r="B78" s="6" t="n">
         <v>10</v>
@@ -20349,7 +20391,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="s">
-        <v>2083</v>
+        <v>2087</v>
       </c>
       <c r="B79" s="6" t="n">
         <v>10</v>
@@ -20360,7 +20402,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>2088</v>
+        <v>2092</v>
       </c>
       <c r="B80" s="6" t="n">
         <v>10</v>
@@ -20371,7 +20413,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="s">
-        <v>2079</v>
+        <v>2083</v>
       </c>
       <c r="B81" s="6" t="n">
         <v>25</v>
@@ -20382,7 +20424,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>2103</v>
+        <v>2107</v>
       </c>
       <c r="B82" s="6" t="n">
         <v>5</v>
@@ -20393,7 +20435,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>2100</v>
+        <v>2104</v>
       </c>
       <c r="B83" s="6" t="n">
         <v>1</v>
@@ -20404,7 +20446,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>2099</v>
+        <v>2103</v>
       </c>
       <c r="B84" s="6" t="n">
         <v>1</v>
@@ -20439,55 +20481,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2104</v>
+        <v>2108</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2105</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>2106</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>2107</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2108</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2109</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2110</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>2111</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>2112</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>2113</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>2114</v>
+        <v>2118</v>
       </c>
     </row>
   </sheetData>
@@ -21033,10 +21075,10 @@
         <v>488</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2115</v>
+        <v>2119</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2116</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21044,7 +21086,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2117</v>
+        <v>2121</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>998</v>
@@ -21056,7 +21098,7 @@
         <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>2118</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21064,7 +21106,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>998</v>
@@ -21076,7 +21118,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>2120</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21084,7 +21126,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2121</v>
+        <v>2125</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>998</v>
@@ -21093,7 +21135,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>2122</v>
+        <v>2126</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>1100</v>
@@ -21131,189 +21173,189 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>2123</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>2124</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>2125</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>2126</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>2127</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>2128</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>2129</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>2130</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>2131</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>2132</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>2133</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>2134</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>2135</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>2136</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>2137</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>2138</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>2139</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>2140</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>2141</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>2142</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>2143</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>2144</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>2145</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>2146</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>2147</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>2148</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>2149</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>2150</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>2151</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>2152</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>2153</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>2154</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>2155</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>2156</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>2157</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>2158</v>
+        <v>2162</v>
       </c>
     </row>
   </sheetData>
@@ -21341,18 +21383,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="79" t="s">
-        <v>2159</v>
+        <v>2163</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
       <c r="E1" s="79" t="s">
-        <v>2160</v>
+        <v>2164</v>
       </c>
       <c r="F1" s="79"/>
       <c r="G1" s="79"/>
       <c r="H1" s="79"/>
       <c r="J1" s="79" t="s">
-        <v>2161</v>
+        <v>2165</v>
       </c>
       <c r="K1" s="79"/>
       <c r="L1" s="79"/>
@@ -21365,7 +21407,7 @@
         <v>489</v>
       </c>
       <c r="C2" s="82" t="s">
-        <v>2162</v>
+        <v>2166</v>
       </c>
       <c r="E2" s="82" t="s">
         <v>840</v>
@@ -21374,19 +21416,19 @@
         <v>489</v>
       </c>
       <c r="G2" s="82" t="s">
-        <v>2162</v>
+        <v>2166</v>
       </c>
       <c r="H2" s="82" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="J2" s="82" t="s">
         <v>840</v>
       </c>
       <c r="K2" s="82" t="s">
-        <v>2163</v>
+        <v>2167</v>
       </c>
       <c r="L2" s="82" t="s">
-        <v>2162</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21394,22 +21436,22 @@
         <v>73</v>
       </c>
       <c r="B3" s="82" t="s">
-        <v>2164</v>
+        <v>2168</v>
       </c>
       <c r="C3" s="82" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="82" t="s">
-        <v>2165</v>
+        <v>2169</v>
       </c>
       <c r="F3" s="82" t="s">
-        <v>2166</v>
+        <v>2170</v>
       </c>
       <c r="G3" s="82" t="n">
         <v>5</v>
       </c>
       <c r="H3" s="82" t="s">
-        <v>2167</v>
+        <v>2171</v>
       </c>
       <c r="J3" s="82"/>
       <c r="K3" s="82"/>
@@ -21438,7 +21480,7 @@
         <v>106</v>
       </c>
       <c r="B5" s="82" t="s">
-        <v>2168</v>
+        <v>2172</v>
       </c>
       <c r="C5" s="82" t="n">
         <v>1</v>
@@ -21456,7 +21498,7 @@
         <v>107</v>
       </c>
       <c r="B6" s="82" t="s">
-        <v>2169</v>
+        <v>2173</v>
       </c>
       <c r="C6" s="82" t="n">
         <v>2</v>
@@ -21474,7 +21516,7 @@
         <v>108</v>
       </c>
       <c r="B7" s="82" t="s">
-        <v>2170</v>
+        <v>2174</v>
       </c>
       <c r="C7" s="82" t="n">
         <v>3</v>
@@ -21492,7 +21534,7 @@
         <v>109</v>
       </c>
       <c r="B8" s="82" t="s">
-        <v>2171</v>
+        <v>2175</v>
       </c>
       <c r="C8" s="82" t="n">
         <v>4</v>
@@ -21510,7 +21552,7 @@
         <v>110</v>
       </c>
       <c r="B9" s="82" t="s">
-        <v>2172</v>
+        <v>2176</v>
       </c>
       <c r="C9" s="82" t="n">
         <v>5</v>
@@ -21528,7 +21570,7 @@
         <v>111</v>
       </c>
       <c r="B10" s="82" t="s">
-        <v>2173</v>
+        <v>2177</v>
       </c>
       <c r="C10" s="82" t="n">
         <v>7</v>
